--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Education\Extra\Machine Learning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A39BA0DC-C0F4-4C91-BCBE-318A9BD5B87F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7262ACE4-67EC-4B98-AF53-0150B128628F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4D8002EB-CBDD-47B0-992C-4D0A104441BC}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="895" uniqueCount="462">
   <si>
     <t>Schedule for Machine Learning</t>
   </si>
@@ -1422,6 +1422,9 @@
   </si>
   <si>
     <t>Friday</t>
+  </si>
+  <si>
+    <t>Saturday</t>
   </si>
 </sst>
 </file>
@@ -1618,24 +1621,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1646,7 +1631,25 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1979,61 +1982,61 @@
   </cols>
   <sheetData>
     <row r="4" spans="7:18" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G4" s="18" t="s">
+      <c r="G4" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="H4" s="19"/>
-      <c r="I4" s="19"/>
-      <c r="J4" s="19"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="19"/>
-      <c r="M4" s="19"/>
-      <c r="N4" s="19"/>
-      <c r="O4" s="19"/>
+      <c r="H4" s="22"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="22"/>
+      <c r="K4" s="22"/>
+      <c r="L4" s="22"/>
+      <c r="M4" s="22"/>
+      <c r="N4" s="22"/>
+      <c r="O4" s="22"/>
     </row>
     <row r="5" spans="7:18" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
-      <c r="I5" s="19"/>
-      <c r="J5" s="19"/>
-      <c r="K5" s="19"/>
-      <c r="L5" s="19"/>
-      <c r="M5" s="19"/>
-      <c r="N5" s="19"/>
-      <c r="O5" s="19"/>
+      <c r="G5" s="22"/>
+      <c r="H5" s="22"/>
+      <c r="I5" s="22"/>
+      <c r="J5" s="22"/>
+      <c r="K5" s="22"/>
+      <c r="L5" s="22"/>
+      <c r="M5" s="22"/>
+      <c r="N5" s="22"/>
+      <c r="O5" s="22"/>
     </row>
     <row r="6" spans="7:18" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G6" s="19"/>
-      <c r="H6" s="19"/>
-      <c r="I6" s="19"/>
-      <c r="J6" s="19"/>
-      <c r="K6" s="19"/>
-      <c r="L6" s="19"/>
-      <c r="M6" s="19"/>
-      <c r="N6" s="19"/>
-      <c r="O6" s="19"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="22"/>
+      <c r="J6" s="22"/>
+      <c r="K6" s="22"/>
+      <c r="L6" s="22"/>
+      <c r="M6" s="22"/>
+      <c r="N6" s="22"/>
+      <c r="O6" s="22"/>
     </row>
     <row r="7" spans="7:18" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
-      <c r="I7" s="19"/>
-      <c r="J7" s="19"/>
-      <c r="K7" s="19"/>
-      <c r="L7" s="19"/>
-      <c r="M7" s="19"/>
-      <c r="N7" s="19"/>
-      <c r="O7" s="19"/>
+      <c r="G7" s="22"/>
+      <c r="H7" s="22"/>
+      <c r="I7" s="22"/>
+      <c r="J7" s="22"/>
+      <c r="K7" s="22"/>
+      <c r="L7" s="22"/>
+      <c r="M7" s="22"/>
+      <c r="N7" s="22"/>
+      <c r="O7" s="22"/>
     </row>
     <row r="8" spans="7:18" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
-      <c r="I8" s="19"/>
-      <c r="J8" s="19"/>
-      <c r="K8" s="19"/>
-      <c r="L8" s="19"/>
-      <c r="M8" s="19"/>
-      <c r="N8" s="19"/>
-      <c r="O8" s="19"/>
+      <c r="G8" s="22"/>
+      <c r="H8" s="22"/>
+      <c r="I8" s="22"/>
+      <c r="J8" s="22"/>
+      <c r="K8" s="22"/>
+      <c r="L8" s="22"/>
+      <c r="M8" s="22"/>
+      <c r="N8" s="22"/>
+      <c r="O8" s="22"/>
     </row>
     <row r="12" spans="7:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="G12" s="11" t="s">
@@ -2054,11 +2057,11 @@
       <c r="L12" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="M12" s="17" t="s">
+      <c r="M12" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="N12" s="17"/>
-      <c r="O12" s="17"/>
+      <c r="N12" s="24"/>
+      <c r="O12" s="24"/>
       <c r="R12" s="6" t="s">
         <v>10</v>
       </c>
@@ -2083,9 +2086,9 @@
       <c r="L13" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M13" s="15"/>
-      <c r="N13" s="15"/>
-      <c r="O13" s="15"/>
+      <c r="M13" s="18"/>
+      <c r="N13" s="18"/>
+      <c r="O13" s="18"/>
       <c r="R13" s="8" t="s">
         <v>9</v>
       </c>
@@ -2110,9 +2113,9 @@
       <c r="L14" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M14" s="15"/>
-      <c r="N14" s="15"/>
-      <c r="O14" s="15"/>
+      <c r="M14" s="18"/>
+      <c r="N14" s="18"/>
+      <c r="O14" s="18"/>
       <c r="R14" s="3" t="s">
         <v>7</v>
       </c>
@@ -2137,9 +2140,9 @@
       <c r="L15" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M15" s="15"/>
-      <c r="N15" s="15"/>
-      <c r="O15" s="15"/>
+      <c r="M15" s="18"/>
+      <c r="N15" s="18"/>
+      <c r="O15" s="18"/>
     </row>
     <row r="16" spans="7:18" x14ac:dyDescent="0.3">
       <c r="G16" s="2">
@@ -2161,11 +2164,11 @@
       <c r="L16" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M16" s="15" t="s">
+      <c r="M16" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="N16" s="15"/>
-      <c r="O16" s="15"/>
+      <c r="N16" s="18"/>
+      <c r="O16" s="18"/>
     </row>
     <row r="17" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G17" s="2">
@@ -2187,9 +2190,9 @@
       <c r="L17" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M17" s="15"/>
-      <c r="N17" s="15"/>
-      <c r="O17" s="15"/>
+      <c r="M17" s="18"/>
+      <c r="N17" s="18"/>
+      <c r="O17" s="18"/>
     </row>
     <row r="18" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G18" s="2">
@@ -2211,9 +2214,9 @@
       <c r="L18" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M18" s="15"/>
-      <c r="N18" s="15"/>
-      <c r="O18" s="15"/>
+      <c r="M18" s="18"/>
+      <c r="N18" s="18"/>
+      <c r="O18" s="18"/>
     </row>
     <row r="19" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G19" s="2">
@@ -2235,9 +2238,9 @@
       <c r="L19" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M19" s="15"/>
-      <c r="N19" s="15"/>
-      <c r="O19" s="15"/>
+      <c r="M19" s="18"/>
+      <c r="N19" s="18"/>
+      <c r="O19" s="18"/>
     </row>
     <row r="20" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G20" s="2">
@@ -2259,9 +2262,9 @@
       <c r="L20" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M20" s="15"/>
-      <c r="N20" s="15"/>
-      <c r="O20" s="15"/>
+      <c r="M20" s="18"/>
+      <c r="N20" s="18"/>
+      <c r="O20" s="18"/>
     </row>
     <row r="21" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G21" s="2">
@@ -2283,9 +2286,9 @@
       <c r="L21" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M21" s="15"/>
-      <c r="N21" s="15"/>
-      <c r="O21" s="15"/>
+      <c r="M21" s="18"/>
+      <c r="N21" s="18"/>
+      <c r="O21" s="18"/>
     </row>
     <row r="22" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G22" s="2">
@@ -2307,11 +2310,11 @@
       <c r="L22" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M22" s="15" t="s">
+      <c r="M22" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="N22" s="15"/>
-      <c r="O22" s="15"/>
+      <c r="N22" s="18"/>
+      <c r="O22" s="18"/>
     </row>
     <row r="23" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G23" s="2">
@@ -2333,9 +2336,9 @@
       <c r="L23" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M23" s="15"/>
-      <c r="N23" s="15"/>
-      <c r="O23" s="15"/>
+      <c r="M23" s="18"/>
+      <c r="N23" s="18"/>
+      <c r="O23" s="18"/>
     </row>
     <row r="24" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G24" s="2">
@@ -2357,9 +2360,9 @@
       <c r="L24" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M24" s="15"/>
-      <c r="N24" s="15"/>
-      <c r="O24" s="15"/>
+      <c r="M24" s="18"/>
+      <c r="N24" s="18"/>
+      <c r="O24" s="18"/>
     </row>
     <row r="25" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G25" s="2">
@@ -2381,9 +2384,9 @@
       <c r="L25" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M25" s="15"/>
-      <c r="N25" s="15"/>
-      <c r="O25" s="15"/>
+      <c r="M25" s="18"/>
+      <c r="N25" s="18"/>
+      <c r="O25" s="18"/>
     </row>
     <row r="26" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G26" s="2">
@@ -2405,9 +2408,9 @@
       <c r="L26" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M26" s="15"/>
-      <c r="N26" s="15"/>
-      <c r="O26" s="15"/>
+      <c r="M26" s="18"/>
+      <c r="N26" s="18"/>
+      <c r="O26" s="18"/>
     </row>
     <row r="27" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G27" s="2">
@@ -2429,9 +2432,9 @@
       <c r="L27" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M27" s="15"/>
-      <c r="N27" s="15"/>
-      <c r="O27" s="15"/>
+      <c r="M27" s="18"/>
+      <c r="N27" s="18"/>
+      <c r="O27" s="18"/>
     </row>
     <row r="28" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G28" s="2">
@@ -2453,9 +2456,9 @@
       <c r="L28" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M28" s="15"/>
-      <c r="N28" s="15"/>
-      <c r="O28" s="15"/>
+      <c r="M28" s="18"/>
+      <c r="N28" s="18"/>
+      <c r="O28" s="18"/>
     </row>
     <row r="29" spans="7:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="G29" s="2">
@@ -2477,9 +2480,9 @@
       <c r="L29" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M29" s="15"/>
-      <c r="N29" s="15"/>
-      <c r="O29" s="15"/>
+      <c r="M29" s="18"/>
+      <c r="N29" s="18"/>
+      <c r="O29" s="18"/>
     </row>
     <row r="30" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G30" s="3">
@@ -2501,11 +2504,11 @@
       <c r="L30" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M30" s="16" t="s">
+      <c r="M30" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="N30" s="16"/>
-      <c r="O30" s="16"/>
+      <c r="N30" s="23"/>
+      <c r="O30" s="23"/>
     </row>
     <row r="31" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G31" s="2">
@@ -2527,9 +2530,9 @@
       <c r="L31" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M31" s="15"/>
-      <c r="N31" s="15"/>
-      <c r="O31" s="15"/>
+      <c r="M31" s="18"/>
+      <c r="N31" s="18"/>
+      <c r="O31" s="18"/>
     </row>
     <row r="32" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G32" s="2">
@@ -2551,9 +2554,9 @@
       <c r="L32" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M32" s="15"/>
-      <c r="N32" s="15"/>
-      <c r="O32" s="15"/>
+      <c r="M32" s="18"/>
+      <c r="N32" s="18"/>
+      <c r="O32" s="18"/>
     </row>
     <row r="33" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G33" s="2">
@@ -2575,9 +2578,9 @@
       <c r="L33" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M33" s="15"/>
-      <c r="N33" s="15"/>
-      <c r="O33" s="15"/>
+      <c r="M33" s="18"/>
+      <c r="N33" s="18"/>
+      <c r="O33" s="18"/>
     </row>
     <row r="34" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G34" s="2">
@@ -2599,9 +2602,9 @@
       <c r="L34" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M34" s="15"/>
-      <c r="N34" s="15"/>
-      <c r="O34" s="15"/>
+      <c r="M34" s="18"/>
+      <c r="N34" s="18"/>
+      <c r="O34" s="18"/>
     </row>
     <row r="35" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G35" s="2">
@@ -2623,9 +2626,9 @@
       <c r="L35" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M35" s="15"/>
-      <c r="N35" s="15"/>
-      <c r="O35" s="15"/>
+      <c r="M35" s="18"/>
+      <c r="N35" s="18"/>
+      <c r="O35" s="18"/>
     </row>
     <row r="36" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G36" s="2">
@@ -2647,9 +2650,9 @@
       <c r="L36" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M36" s="15"/>
-      <c r="N36" s="15"/>
-      <c r="O36" s="15"/>
+      <c r="M36" s="18"/>
+      <c r="N36" s="18"/>
+      <c r="O36" s="18"/>
     </row>
     <row r="37" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G37" s="2">
@@ -2671,9 +2674,9 @@
       <c r="L37" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M37" s="21"/>
-      <c r="N37" s="22"/>
-      <c r="O37" s="23"/>
+      <c r="M37" s="15"/>
+      <c r="N37" s="16"/>
+      <c r="O37" s="17"/>
     </row>
     <row r="38" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G38" s="2">
@@ -2695,9 +2698,9 @@
       <c r="L38" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M38" s="15"/>
-      <c r="N38" s="15"/>
-      <c r="O38" s="15"/>
+      <c r="M38" s="18"/>
+      <c r="N38" s="18"/>
+      <c r="O38" s="18"/>
     </row>
     <row r="39" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G39" s="2">
@@ -2719,9 +2722,9 @@
       <c r="L39" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M39" s="15"/>
-      <c r="N39" s="15"/>
-      <c r="O39" s="15"/>
+      <c r="M39" s="18"/>
+      <c r="N39" s="18"/>
+      <c r="O39" s="18"/>
     </row>
     <row r="40" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G40" s="2">
@@ -2743,9 +2746,9 @@
       <c r="L40" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M40" s="15"/>
-      <c r="N40" s="15"/>
-      <c r="O40" s="15"/>
+      <c r="M40" s="18"/>
+      <c r="N40" s="18"/>
+      <c r="O40" s="18"/>
     </row>
     <row r="41" spans="7:15" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G41" s="2">
@@ -2767,11 +2770,11 @@
       <c r="L41" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M41" s="15" t="s">
+      <c r="M41" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="N41" s="15"/>
-      <c r="O41" s="15"/>
+      <c r="N41" s="18"/>
+      <c r="O41" s="18"/>
     </row>
     <row r="42" spans="7:15" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G42" s="2">
@@ -2793,11 +2796,11 @@
       <c r="L42" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M42" s="15" t="s">
+      <c r="M42" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="N42" s="15"/>
-      <c r="O42" s="15"/>
+      <c r="N42" s="18"/>
+      <c r="O42" s="18"/>
     </row>
     <row r="43" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G43" s="2">
@@ -2819,9 +2822,9 @@
       <c r="L43" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M43" s="15"/>
-      <c r="N43" s="15"/>
-      <c r="O43" s="15"/>
+      <c r="M43" s="18"/>
+      <c r="N43" s="18"/>
+      <c r="O43" s="18"/>
     </row>
     <row r="44" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G44" s="6">
@@ -2843,9 +2846,9 @@
       <c r="L44" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M44" s="20"/>
-      <c r="N44" s="20"/>
-      <c r="O44" s="20"/>
+      <c r="M44" s="19"/>
+      <c r="N44" s="19"/>
+      <c r="O44" s="19"/>
     </row>
     <row r="45" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G45" s="6">
@@ -2867,9 +2870,9 @@
       <c r="L45" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M45" s="20"/>
-      <c r="N45" s="20"/>
-      <c r="O45" s="20"/>
+      <c r="M45" s="19"/>
+      <c r="N45" s="19"/>
+      <c r="O45" s="19"/>
     </row>
     <row r="46" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G46" s="2">
@@ -2891,9 +2894,9 @@
       <c r="L46" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M46" s="15"/>
-      <c r="N46" s="15"/>
-      <c r="O46" s="15"/>
+      <c r="M46" s="18"/>
+      <c r="N46" s="18"/>
+      <c r="O46" s="18"/>
     </row>
     <row r="47" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G47" s="2">
@@ -2915,9 +2918,9 @@
       <c r="L47" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M47" s="15"/>
-      <c r="N47" s="15"/>
-      <c r="O47" s="15"/>
+      <c r="M47" s="18"/>
+      <c r="N47" s="18"/>
+      <c r="O47" s="18"/>
     </row>
     <row r="48" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G48" s="2">
@@ -2939,9 +2942,9 @@
       <c r="L48" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M48" s="15"/>
-      <c r="N48" s="15"/>
-      <c r="O48" s="15"/>
+      <c r="M48" s="18"/>
+      <c r="N48" s="18"/>
+      <c r="O48" s="18"/>
     </row>
     <row r="49" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G49" s="2">
@@ -2963,9 +2966,9 @@
       <c r="L49" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M49" s="15"/>
-      <c r="N49" s="15"/>
-      <c r="O49" s="15"/>
+      <c r="M49" s="18"/>
+      <c r="N49" s="18"/>
+      <c r="O49" s="18"/>
     </row>
     <row r="50" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G50" s="2">
@@ -2987,9 +2990,9 @@
       <c r="L50" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M50" s="15"/>
-      <c r="N50" s="15"/>
-      <c r="O50" s="15"/>
+      <c r="M50" s="18"/>
+      <c r="N50" s="18"/>
+      <c r="O50" s="18"/>
     </row>
     <row r="51" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G51" s="2">
@@ -3011,11 +3014,11 @@
       <c r="L51" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M51" s="15" t="s">
+      <c r="M51" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="N51" s="15"/>
-      <c r="O51" s="15"/>
+      <c r="N51" s="18"/>
+      <c r="O51" s="18"/>
     </row>
     <row r="52" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G52" s="2">
@@ -3037,9 +3040,9 @@
       <c r="L52" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M52" s="15"/>
-      <c r="N52" s="15"/>
-      <c r="O52" s="15"/>
+      <c r="M52" s="18"/>
+      <c r="N52" s="18"/>
+      <c r="O52" s="18"/>
     </row>
     <row r="53" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G53" s="2">
@@ -3061,9 +3064,9 @@
       <c r="L53" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M53" s="15"/>
-      <c r="N53" s="15"/>
-      <c r="O53" s="15"/>
+      <c r="M53" s="18"/>
+      <c r="N53" s="18"/>
+      <c r="O53" s="18"/>
     </row>
     <row r="54" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G54" s="2">
@@ -3085,9 +3088,9 @@
       <c r="L54" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M54" s="15"/>
-      <c r="N54" s="15"/>
-      <c r="O54" s="15"/>
+      <c r="M54" s="18"/>
+      <c r="N54" s="18"/>
+      <c r="O54" s="18"/>
     </row>
     <row r="55" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G55" s="2">
@@ -3109,9 +3112,9 @@
       <c r="L55" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M55" s="15"/>
-      <c r="N55" s="15"/>
-      <c r="O55" s="15"/>
+      <c r="M55" s="18"/>
+      <c r="N55" s="18"/>
+      <c r="O55" s="18"/>
     </row>
     <row r="56" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G56" s="2">
@@ -3133,9 +3136,9 @@
       <c r="L56" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M56" s="15"/>
-      <c r="N56" s="15"/>
-      <c r="O56" s="15"/>
+      <c r="M56" s="18"/>
+      <c r="N56" s="18"/>
+      <c r="O56" s="18"/>
     </row>
     <row r="57" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G57" s="3">
@@ -3153,11 +3156,11 @@
       <c r="L57" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M57" s="16" t="s">
+      <c r="M57" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="N57" s="16"/>
-      <c r="O57" s="16"/>
+      <c r="N57" s="23"/>
+      <c r="O57" s="23"/>
     </row>
     <row r="58" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G58" s="2">
@@ -3179,9 +3182,9 @@
       <c r="L58" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M58" s="15"/>
-      <c r="N58" s="15"/>
-      <c r="O58" s="15"/>
+      <c r="M58" s="18"/>
+      <c r="N58" s="18"/>
+      <c r="O58" s="18"/>
     </row>
     <row r="59" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G59" s="2">
@@ -3203,9 +3206,9 @@
       <c r="L59" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M59" s="15"/>
-      <c r="N59" s="15"/>
-      <c r="O59" s="15"/>
+      <c r="M59" s="18"/>
+      <c r="N59" s="18"/>
+      <c r="O59" s="18"/>
     </row>
     <row r="60" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G60" s="2">
@@ -3227,11 +3230,11 @@
       <c r="L60" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M60" s="15" t="s">
+      <c r="M60" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="N60" s="15"/>
-      <c r="O60" s="15"/>
+      <c r="N60" s="18"/>
+      <c r="O60" s="18"/>
     </row>
     <row r="61" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G61" s="2">
@@ -3253,9 +3256,9 @@
       <c r="L61" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M61" s="15"/>
-      <c r="N61" s="15"/>
-      <c r="O61" s="15"/>
+      <c r="M61" s="18"/>
+      <c r="N61" s="18"/>
+      <c r="O61" s="18"/>
     </row>
     <row r="62" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G62" s="2">
@@ -3277,9 +3280,9 @@
       <c r="L62" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M62" s="15"/>
-      <c r="N62" s="15"/>
-      <c r="O62" s="15"/>
+      <c r="M62" s="18"/>
+      <c r="N62" s="18"/>
+      <c r="O62" s="18"/>
     </row>
     <row r="63" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G63" s="2">
@@ -3301,9 +3304,9 @@
       <c r="L63" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M63" s="15"/>
-      <c r="N63" s="15"/>
-      <c r="O63" s="15"/>
+      <c r="M63" s="18"/>
+      <c r="N63" s="18"/>
+      <c r="O63" s="18"/>
     </row>
     <row r="64" spans="7:15" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G64" s="2">
@@ -3325,11 +3328,11 @@
       <c r="L64" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M64" s="15" t="s">
+      <c r="M64" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="N64" s="15"/>
-      <c r="O64" s="15"/>
+      <c r="N64" s="18"/>
+      <c r="O64" s="18"/>
     </row>
     <row r="65" spans="7:15" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G65" s="2">
@@ -3351,9 +3354,9 @@
       <c r="L65" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M65" s="24"/>
-      <c r="N65" s="24"/>
-      <c r="O65" s="24"/>
+      <c r="M65" s="20"/>
+      <c r="N65" s="20"/>
+      <c r="O65" s="20"/>
     </row>
     <row r="66" spans="7:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="G66" s="2">
@@ -3375,9 +3378,9 @@
       <c r="L66" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M66" s="15"/>
-      <c r="N66" s="15"/>
-      <c r="O66" s="15"/>
+      <c r="M66" s="18"/>
+      <c r="N66" s="18"/>
+      <c r="O66" s="18"/>
     </row>
     <row r="67" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G67" s="2">
@@ -3399,9 +3402,9 @@
       <c r="L67" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M67" s="15"/>
-      <c r="N67" s="15"/>
-      <c r="O67" s="15"/>
+      <c r="M67" s="18"/>
+      <c r="N67" s="18"/>
+      <c r="O67" s="18"/>
     </row>
     <row r="68" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G68" s="2">
@@ -3423,9 +3426,9 @@
       <c r="L68" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M68" s="15"/>
-      <c r="N68" s="15"/>
-      <c r="O68" s="15"/>
+      <c r="M68" s="18"/>
+      <c r="N68" s="18"/>
+      <c r="O68" s="18"/>
     </row>
     <row r="69" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G69" s="2">
@@ -3447,9 +3450,9 @@
       <c r="L69" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M69" s="15"/>
-      <c r="N69" s="15"/>
-      <c r="O69" s="15"/>
+      <c r="M69" s="18"/>
+      <c r="N69" s="18"/>
+      <c r="O69" s="18"/>
     </row>
     <row r="70" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G70" s="2">
@@ -3471,9 +3474,9 @@
       <c r="L70" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M70" s="15"/>
-      <c r="N70" s="15"/>
-      <c r="O70" s="15"/>
+      <c r="M70" s="18"/>
+      <c r="N70" s="18"/>
+      <c r="O70" s="18"/>
     </row>
     <row r="71" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G71" s="2">
@@ -3495,9 +3498,9 @@
       <c r="L71" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M71" s="15"/>
-      <c r="N71" s="15"/>
-      <c r="O71" s="15"/>
+      <c r="M71" s="18"/>
+      <c r="N71" s="18"/>
+      <c r="O71" s="18"/>
     </row>
     <row r="72" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G72" s="2">
@@ -3519,9 +3522,9 @@
       <c r="L72" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M72" s="15"/>
-      <c r="N72" s="15"/>
-      <c r="O72" s="15"/>
+      <c r="M72" s="18"/>
+      <c r="N72" s="18"/>
+      <c r="O72" s="18"/>
     </row>
     <row r="73" spans="7:15" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G73" s="2">
@@ -3543,11 +3546,11 @@
       <c r="L73" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M73" s="15" t="s">
+      <c r="M73" s="18" t="s">
         <v>237</v>
       </c>
-      <c r="N73" s="15"/>
-      <c r="O73" s="15"/>
+      <c r="N73" s="18"/>
+      <c r="O73" s="18"/>
     </row>
     <row r="74" spans="7:15" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G74" s="2">
@@ -3569,11 +3572,11 @@
       <c r="L74" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M74" s="15" t="s">
+      <c r="M74" s="18" t="s">
         <v>238</v>
       </c>
-      <c r="N74" s="15"/>
-      <c r="O74" s="15"/>
+      <c r="N74" s="18"/>
+      <c r="O74" s="18"/>
     </row>
     <row r="75" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G75" s="2">
@@ -3595,9 +3598,9 @@
       <c r="L75" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M75" s="15"/>
-      <c r="N75" s="15"/>
-      <c r="O75" s="15"/>
+      <c r="M75" s="18"/>
+      <c r="N75" s="18"/>
+      <c r="O75" s="18"/>
     </row>
     <row r="76" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G76" s="2">
@@ -3619,11 +3622,11 @@
       <c r="L76" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M76" s="15" t="s">
+      <c r="M76" s="18" t="s">
         <v>239</v>
       </c>
-      <c r="N76" s="15"/>
-      <c r="O76" s="15"/>
+      <c r="N76" s="18"/>
+      <c r="O76" s="18"/>
     </row>
     <row r="77" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G77" s="2">
@@ -3645,11 +3648,11 @@
       <c r="L77" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M77" s="15" t="s">
+      <c r="M77" s="18" t="s">
         <v>243</v>
       </c>
-      <c r="N77" s="15"/>
-      <c r="O77" s="15"/>
+      <c r="N77" s="18"/>
+      <c r="O77" s="18"/>
     </row>
     <row r="78" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G78" s="2">
@@ -3671,11 +3674,11 @@
       <c r="L78" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M78" s="15" t="s">
+      <c r="M78" s="18" t="s">
         <v>242</v>
       </c>
-      <c r="N78" s="15"/>
-      <c r="O78" s="15"/>
+      <c r="N78" s="18"/>
+      <c r="O78" s="18"/>
     </row>
     <row r="79" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G79" s="2">
@@ -3697,9 +3700,9 @@
       <c r="L79" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M79" s="15"/>
-      <c r="N79" s="15"/>
-      <c r="O79" s="15"/>
+      <c r="M79" s="18"/>
+      <c r="N79" s="18"/>
+      <c r="O79" s="18"/>
     </row>
     <row r="80" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G80" s="2">
@@ -3721,11 +3724,11 @@
       <c r="L80" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M80" s="15" t="s">
+      <c r="M80" s="18" t="s">
         <v>241</v>
       </c>
-      <c r="N80" s="15"/>
-      <c r="O80" s="15"/>
+      <c r="N80" s="18"/>
+      <c r="O80" s="18"/>
     </row>
     <row r="81" spans="7:17" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G81" s="2">
@@ -3747,11 +3750,11 @@
       <c r="L81" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M81" s="15" t="s">
+      <c r="M81" s="18" t="s">
         <v>240</v>
       </c>
-      <c r="N81" s="15"/>
-      <c r="O81" s="15"/>
+      <c r="N81" s="18"/>
+      <c r="O81" s="18"/>
       <c r="Q81" s="13" t="s">
         <v>447</v>
       </c>
@@ -3776,9 +3779,9 @@
       <c r="L82" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M82" s="15"/>
-      <c r="N82" s="15"/>
-      <c r="O82" s="15"/>
+      <c r="M82" s="18"/>
+      <c r="N82" s="18"/>
+      <c r="O82" s="18"/>
     </row>
     <row r="83" spans="7:17" x14ac:dyDescent="0.3">
       <c r="G83" s="6">
@@ -3800,11 +3803,11 @@
       <c r="L83" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M83" s="15" t="s">
+      <c r="M83" s="18" t="s">
         <v>448</v>
       </c>
-      <c r="N83" s="15"/>
-      <c r="O83" s="15"/>
+      <c r="N83" s="18"/>
+      <c r="O83" s="18"/>
     </row>
     <row r="84" spans="7:17" x14ac:dyDescent="0.3">
       <c r="G84" s="6">
@@ -3826,11 +3829,11 @@
       <c r="L84" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M84" s="15" t="s">
+      <c r="M84" s="18" t="s">
         <v>449</v>
       </c>
-      <c r="N84" s="15"/>
-      <c r="O84" s="15"/>
+      <c r="N84" s="18"/>
+      <c r="O84" s="18"/>
     </row>
     <row r="85" spans="7:17" x14ac:dyDescent="0.3">
       <c r="G85" s="6">
@@ -3852,11 +3855,11 @@
       <c r="L85" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M85" s="15" t="s">
+      <c r="M85" s="18" t="s">
         <v>450</v>
       </c>
-      <c r="N85" s="15"/>
-      <c r="O85" s="15"/>
+      <c r="N85" s="18"/>
+      <c r="O85" s="18"/>
     </row>
     <row r="86" spans="7:17" x14ac:dyDescent="0.3">
       <c r="G86" s="6">
@@ -3878,11 +3881,11 @@
       <c r="L86" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M86" s="15" t="s">
+      <c r="M86" s="18" t="s">
         <v>454</v>
       </c>
-      <c r="N86" s="15"/>
-      <c r="O86" s="15"/>
+      <c r="N86" s="18"/>
+      <c r="O86" s="18"/>
     </row>
     <row r="87" spans="7:17" x14ac:dyDescent="0.3">
       <c r="G87" s="6">
@@ -3904,9 +3907,9 @@
       <c r="L87" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M87" s="15"/>
-      <c r="N87" s="15"/>
-      <c r="O87" s="15"/>
+      <c r="M87" s="18"/>
+      <c r="N87" s="18"/>
+      <c r="O87" s="18"/>
     </row>
     <row r="88" spans="7:17" x14ac:dyDescent="0.3">
       <c r="G88" s="6">
@@ -3928,9 +3931,9 @@
       <c r="L88" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M88" s="15"/>
-      <c r="N88" s="15"/>
-      <c r="O88" s="15"/>
+      <c r="M88" s="18"/>
+      <c r="N88" s="18"/>
+      <c r="O88" s="18"/>
     </row>
     <row r="89" spans="7:17" x14ac:dyDescent="0.3">
       <c r="G89" s="6">
@@ -3952,9 +3955,9 @@
       <c r="L89" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M89" s="15"/>
-      <c r="N89" s="15"/>
-      <c r="O89" s="15"/>
+      <c r="M89" s="18"/>
+      <c r="N89" s="18"/>
+      <c r="O89" s="18"/>
     </row>
     <row r="90" spans="7:17" x14ac:dyDescent="0.3">
       <c r="G90" s="6">
@@ -3976,9 +3979,9 @@
       <c r="L90" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M90" s="15"/>
-      <c r="N90" s="15"/>
-      <c r="O90" s="15"/>
+      <c r="M90" s="18"/>
+      <c r="N90" s="18"/>
+      <c r="O90" s="18"/>
     </row>
     <row r="91" spans="7:17" x14ac:dyDescent="0.3">
       <c r="G91" s="6">
@@ -4000,9 +4003,9 @@
       <c r="L91" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M91" s="15"/>
-      <c r="N91" s="15"/>
-      <c r="O91" s="15"/>
+      <c r="M91" s="18"/>
+      <c r="N91" s="18"/>
+      <c r="O91" s="18"/>
     </row>
     <row r="92" spans="7:17" x14ac:dyDescent="0.3">
       <c r="G92" s="6">
@@ -4024,9 +4027,9 @@
       <c r="L92" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M92" s="15"/>
-      <c r="N92" s="15"/>
-      <c r="O92" s="15"/>
+      <c r="M92" s="18"/>
+      <c r="N92" s="18"/>
+      <c r="O92" s="18"/>
     </row>
     <row r="93" spans="7:17" x14ac:dyDescent="0.3">
       <c r="G93" s="6">
@@ -4048,9 +4051,9 @@
       <c r="L93" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M93" s="15"/>
-      <c r="N93" s="15"/>
-      <c r="O93" s="15"/>
+      <c r="M93" s="18"/>
+      <c r="N93" s="18"/>
+      <c r="O93" s="18"/>
     </row>
     <row r="94" spans="7:17" x14ac:dyDescent="0.3">
       <c r="G94" s="6">
@@ -4072,9 +4075,9 @@
       <c r="L94" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M94" s="15"/>
-      <c r="N94" s="15"/>
-      <c r="O94" s="15"/>
+      <c r="M94" s="18"/>
+      <c r="N94" s="18"/>
+      <c r="O94" s="18"/>
     </row>
     <row r="95" spans="7:17" x14ac:dyDescent="0.3">
       <c r="G95" s="6">
@@ -4096,9 +4099,9 @@
       <c r="L95" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M95" s="15"/>
-      <c r="N95" s="15"/>
-      <c r="O95" s="15"/>
+      <c r="M95" s="18"/>
+      <c r="N95" s="18"/>
+      <c r="O95" s="18"/>
     </row>
     <row r="96" spans="7:17" x14ac:dyDescent="0.3">
       <c r="G96" s="6">
@@ -4120,9 +4123,9 @@
       <c r="L96" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M96" s="15"/>
-      <c r="N96" s="15"/>
-      <c r="O96" s="15"/>
+      <c r="M96" s="18"/>
+      <c r="N96" s="18"/>
+      <c r="O96" s="18"/>
     </row>
     <row r="97" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G97" s="6">
@@ -4144,9 +4147,9 @@
       <c r="L97" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M97" s="15"/>
-      <c r="N97" s="15"/>
-      <c r="O97" s="15"/>
+      <c r="M97" s="18"/>
+      <c r="N97" s="18"/>
+      <c r="O97" s="18"/>
     </row>
     <row r="98" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G98" s="6">
@@ -4168,9 +4171,9 @@
       <c r="L98" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M98" s="15"/>
-      <c r="N98" s="15"/>
-      <c r="O98" s="15"/>
+      <c r="M98" s="18"/>
+      <c r="N98" s="18"/>
+      <c r="O98" s="18"/>
     </row>
     <row r="99" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G99" s="2">
@@ -4192,9 +4195,9 @@
       <c r="L99" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M99" s="15"/>
-      <c r="N99" s="15"/>
-      <c r="O99" s="15"/>
+      <c r="M99" s="18"/>
+      <c r="N99" s="18"/>
+      <c r="O99" s="18"/>
     </row>
     <row r="100" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G100" s="2">
@@ -4216,9 +4219,9 @@
       <c r="L100" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M100" s="15"/>
-      <c r="N100" s="15"/>
-      <c r="O100" s="15"/>
+      <c r="M100" s="18"/>
+      <c r="N100" s="18"/>
+      <c r="O100" s="18"/>
     </row>
     <row r="101" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G101" s="2">
@@ -4240,9 +4243,9 @@
       <c r="L101" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M101" s="15"/>
-      <c r="N101" s="15"/>
-      <c r="O101" s="15"/>
+      <c r="M101" s="18"/>
+      <c r="N101" s="18"/>
+      <c r="O101" s="18"/>
     </row>
     <row r="102" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G102" s="2">
@@ -4264,9 +4267,9 @@
       <c r="L102" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M102" s="15"/>
-      <c r="N102" s="15"/>
-      <c r="O102" s="15"/>
+      <c r="M102" s="18"/>
+      <c r="N102" s="18"/>
+      <c r="O102" s="18"/>
     </row>
     <row r="103" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G103" s="6">
@@ -4288,9 +4291,9 @@
       <c r="L103" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M103" s="15"/>
-      <c r="N103" s="15"/>
-      <c r="O103" s="15"/>
+      <c r="M103" s="18"/>
+      <c r="N103" s="18"/>
+      <c r="O103" s="18"/>
     </row>
     <row r="104" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G104" s="2">
@@ -4312,9 +4315,9 @@
       <c r="L104" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M104" s="15"/>
-      <c r="N104" s="15"/>
-      <c r="O104" s="15"/>
+      <c r="M104" s="18"/>
+      <c r="N104" s="18"/>
+      <c r="O104" s="18"/>
     </row>
     <row r="105" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G105" s="2">
@@ -4336,9 +4339,9 @@
       <c r="L105" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M105" s="15"/>
-      <c r="N105" s="15"/>
-      <c r="O105" s="15"/>
+      <c r="M105" s="18"/>
+      <c r="N105" s="18"/>
+      <c r="O105" s="18"/>
     </row>
     <row r="106" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G106" s="2">
@@ -4360,9 +4363,9 @@
       <c r="L106" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M106" s="15"/>
-      <c r="N106" s="15"/>
-      <c r="O106" s="15"/>
+      <c r="M106" s="18"/>
+      <c r="N106" s="18"/>
+      <c r="O106" s="18"/>
     </row>
     <row r="107" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G107" s="2">
@@ -4384,9 +4387,9 @@
       <c r="L107" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M107" s="15"/>
-      <c r="N107" s="15"/>
-      <c r="O107" s="15"/>
+      <c r="M107" s="18"/>
+      <c r="N107" s="18"/>
+      <c r="O107" s="18"/>
     </row>
     <row r="108" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G108" s="2">
@@ -4408,9 +4411,9 @@
       <c r="L108" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M108" s="15"/>
-      <c r="N108" s="15"/>
-      <c r="O108" s="15"/>
+      <c r="M108" s="18"/>
+      <c r="N108" s="18"/>
+      <c r="O108" s="18"/>
     </row>
     <row r="109" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G109" s="2">
@@ -4432,9 +4435,9 @@
       <c r="L109" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M109" s="15"/>
-      <c r="N109" s="15"/>
-      <c r="O109" s="15"/>
+      <c r="M109" s="18"/>
+      <c r="N109" s="18"/>
+      <c r="O109" s="18"/>
     </row>
     <row r="110" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G110" s="2">
@@ -4456,9 +4459,9 @@
       <c r="L110" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M110" s="15"/>
-      <c r="N110" s="15"/>
-      <c r="O110" s="15"/>
+      <c r="M110" s="18"/>
+      <c r="N110" s="18"/>
+      <c r="O110" s="18"/>
     </row>
     <row r="111" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G111" s="2">
@@ -4480,9 +4483,9 @@
       <c r="L111" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M111" s="15"/>
-      <c r="N111" s="15"/>
-      <c r="O111" s="15"/>
+      <c r="M111" s="18"/>
+      <c r="N111" s="18"/>
+      <c r="O111" s="18"/>
     </row>
     <row r="112" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G112" s="2">
@@ -4504,9 +4507,9 @@
       <c r="L112" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M112" s="15"/>
-      <c r="N112" s="15"/>
-      <c r="O112" s="15"/>
+      <c r="M112" s="18"/>
+      <c r="N112" s="18"/>
+      <c r="O112" s="18"/>
     </row>
     <row r="113" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G113" s="2">
@@ -4528,9 +4531,9 @@
       <c r="L113" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M113" s="15"/>
-      <c r="N113" s="15"/>
-      <c r="O113" s="15"/>
+      <c r="M113" s="18"/>
+      <c r="N113" s="18"/>
+      <c r="O113" s="18"/>
     </row>
     <row r="114" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G114" s="2">
@@ -4552,9 +4555,9 @@
       <c r="L114" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M114" s="15"/>
-      <c r="N114" s="15"/>
-      <c r="O114" s="15"/>
+      <c r="M114" s="18"/>
+      <c r="N114" s="18"/>
+      <c r="O114" s="18"/>
     </row>
     <row r="115" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G115" s="2">
@@ -4576,9 +4579,9 @@
       <c r="L115" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M115" s="15"/>
-      <c r="N115" s="15"/>
-      <c r="O115" s="15"/>
+      <c r="M115" s="18"/>
+      <c r="N115" s="18"/>
+      <c r="O115" s="18"/>
     </row>
     <row r="116" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G116" s="2">
@@ -4600,9 +4603,9 @@
       <c r="L116" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M116" s="15"/>
-      <c r="N116" s="15"/>
-      <c r="O116" s="15"/>
+      <c r="M116" s="18"/>
+      <c r="N116" s="18"/>
+      <c r="O116" s="18"/>
     </row>
     <row r="117" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G117" s="2">
@@ -4624,9 +4627,9 @@
       <c r="L117" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M117" s="15"/>
-      <c r="N117" s="15"/>
-      <c r="O117" s="15"/>
+      <c r="M117" s="18"/>
+      <c r="N117" s="18"/>
+      <c r="O117" s="18"/>
     </row>
     <row r="118" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G118" s="2">
@@ -4648,9 +4651,9 @@
       <c r="L118" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M118" s="15"/>
-      <c r="N118" s="15"/>
-      <c r="O118" s="15"/>
+      <c r="M118" s="18"/>
+      <c r="N118" s="18"/>
+      <c r="O118" s="18"/>
     </row>
     <row r="119" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G119" s="2">
@@ -4672,9 +4675,9 @@
       <c r="L119" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M119" s="15"/>
-      <c r="N119" s="15"/>
-      <c r="O119" s="15"/>
+      <c r="M119" s="18"/>
+      <c r="N119" s="18"/>
+      <c r="O119" s="18"/>
     </row>
     <row r="120" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G120" s="2">
@@ -4696,9 +4699,9 @@
       <c r="L120" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M120" s="15"/>
-      <c r="N120" s="15"/>
-      <c r="O120" s="15"/>
+      <c r="M120" s="18"/>
+      <c r="N120" s="18"/>
+      <c r="O120" s="18"/>
     </row>
     <row r="121" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G121" s="2">
@@ -4720,9 +4723,9 @@
       <c r="L121" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M121" s="15"/>
-      <c r="N121" s="15"/>
-      <c r="O121" s="15"/>
+      <c r="M121" s="18"/>
+      <c r="N121" s="18"/>
+      <c r="O121" s="18"/>
     </row>
     <row r="122" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G122" s="2">
@@ -4743,9 +4746,9 @@
       <c r="L122" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M122" s="15"/>
-      <c r="N122" s="15"/>
-      <c r="O122" s="15"/>
+      <c r="M122" s="18"/>
+      <c r="N122" s="18"/>
+      <c r="O122" s="18"/>
     </row>
     <row r="123" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G123" s="2">
@@ -4766,9 +4769,9 @@
       <c r="L123" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M123" s="15"/>
-      <c r="N123" s="15"/>
-      <c r="O123" s="15"/>
+      <c r="M123" s="18"/>
+      <c r="N123" s="18"/>
+      <c r="O123" s="18"/>
     </row>
     <row r="124" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G124" s="2">
@@ -4789,9 +4792,9 @@
       <c r="L124" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M124" s="15"/>
-      <c r="N124" s="15"/>
-      <c r="O124" s="15"/>
+      <c r="M124" s="18"/>
+      <c r="N124" s="18"/>
+      <c r="O124" s="18"/>
     </row>
     <row r="125" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G125" s="2">
@@ -4812,9 +4815,9 @@
       <c r="L125" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M125" s="15"/>
-      <c r="N125" s="15"/>
-      <c r="O125" s="15"/>
+      <c r="M125" s="18"/>
+      <c r="N125" s="18"/>
+      <c r="O125" s="18"/>
     </row>
     <row r="126" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G126" s="2">
@@ -4835,9 +4838,9 @@
       <c r="L126" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M126" s="15"/>
-      <c r="N126" s="15"/>
-      <c r="O126" s="15"/>
+      <c r="M126" s="18"/>
+      <c r="N126" s="18"/>
+      <c r="O126" s="18"/>
     </row>
     <row r="127" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G127" s="2">
@@ -4858,9 +4861,9 @@
       <c r="L127" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M127" s="15"/>
-      <c r="N127" s="15"/>
-      <c r="O127" s="15"/>
+      <c r="M127" s="18"/>
+      <c r="N127" s="18"/>
+      <c r="O127" s="18"/>
     </row>
     <row r="128" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G128" s="2">
@@ -4881,9 +4884,9 @@
       <c r="L128" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M128" s="15"/>
-      <c r="N128" s="15"/>
-      <c r="O128" s="15"/>
+      <c r="M128" s="18"/>
+      <c r="N128" s="18"/>
+      <c r="O128" s="18"/>
     </row>
     <row r="129" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G129" s="2">
@@ -4904,9 +4907,9 @@
       <c r="L129" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M129" s="15"/>
-      <c r="N129" s="15"/>
-      <c r="O129" s="15"/>
+      <c r="M129" s="18"/>
+      <c r="N129" s="18"/>
+      <c r="O129" s="18"/>
     </row>
     <row r="130" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G130" s="2">
@@ -4927,9 +4930,9 @@
       <c r="L130" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M130" s="15"/>
-      <c r="N130" s="15"/>
-      <c r="O130" s="15"/>
+      <c r="M130" s="18"/>
+      <c r="N130" s="18"/>
+      <c r="O130" s="18"/>
     </row>
     <row r="131" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G131" s="2">
@@ -4950,9 +4953,9 @@
       <c r="L131" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M131" s="15"/>
-      <c r="N131" s="15"/>
-      <c r="O131" s="15"/>
+      <c r="M131" s="18"/>
+      <c r="N131" s="18"/>
+      <c r="O131" s="18"/>
     </row>
     <row r="132" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G132" s="2">
@@ -4973,9 +4976,9 @@
       <c r="L132" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M132" s="15"/>
-      <c r="N132" s="15"/>
-      <c r="O132" s="15"/>
+      <c r="M132" s="18"/>
+      <c r="N132" s="18"/>
+      <c r="O132" s="18"/>
     </row>
     <row r="133" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G133" s="2">
@@ -4996,9 +4999,9 @@
       <c r="L133" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M133" s="15"/>
-      <c r="N133" s="15"/>
-      <c r="O133" s="15"/>
+      <c r="M133" s="18"/>
+      <c r="N133" s="18"/>
+      <c r="O133" s="18"/>
     </row>
     <row r="134" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G134" s="2">
@@ -5019,9 +5022,9 @@
       <c r="L134" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M134" s="15"/>
-      <c r="N134" s="15"/>
-      <c r="O134" s="15"/>
+      <c r="M134" s="18"/>
+      <c r="N134" s="18"/>
+      <c r="O134" s="18"/>
     </row>
     <row r="135" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G135" s="2">
@@ -5042,9 +5045,9 @@
       <c r="L135" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M135" s="15"/>
-      <c r="N135" s="15"/>
-      <c r="O135" s="15"/>
+      <c r="M135" s="18"/>
+      <c r="N135" s="18"/>
+      <c r="O135" s="18"/>
     </row>
     <row r="136" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G136" s="2">
@@ -5062,12 +5065,12 @@
       <c r="K136" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="L136" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="M136" s="15"/>
-      <c r="N136" s="15"/>
-      <c r="O136" s="15"/>
+      <c r="L136" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="M136" s="18"/>
+      <c r="N136" s="18"/>
+      <c r="O136" s="18"/>
     </row>
     <row r="137" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G137" s="2">
@@ -5076,10 +5079,12 @@
       <c r="H137" s="7">
         <v>46007</v>
       </c>
-      <c r="I137" s="7"/>
+      <c r="I137" s="7">
+        <v>46044</v>
+      </c>
       <c r="J137" s="2" t="str">
         <f t="shared" si="7"/>
-        <v>Saturday</v>
+        <v>dddd</v>
       </c>
       <c r="K137" s="2" t="s">
         <v>166</v>
@@ -5087,9 +5092,9 @@
       <c r="L137" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M137" s="15"/>
-      <c r="N137" s="15"/>
-      <c r="O137" s="15"/>
+      <c r="M137" s="18"/>
+      <c r="N137" s="18"/>
+      <c r="O137" s="18"/>
     </row>
     <row r="138" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G138" s="2">
@@ -5107,12 +5112,12 @@
       <c r="K138" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="L138" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="M138" s="15"/>
-      <c r="N138" s="15"/>
-      <c r="O138" s="15"/>
+      <c r="L138" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="M138" s="18"/>
+      <c r="N138" s="18"/>
+      <c r="O138" s="18"/>
     </row>
     <row r="139" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G139" s="2">
@@ -5121,20 +5126,21 @@
       <c r="H139" s="7">
         <v>46009</v>
       </c>
-      <c r="I139" s="7"/>
-      <c r="J139" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v>Saturday</v>
+      <c r="I139" s="7">
+        <v>46045</v>
+      </c>
+      <c r="J139" s="2" t="s">
+        <v>460</v>
       </c>
       <c r="K139" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="L139" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="M139" s="15"/>
-      <c r="N139" s="15"/>
-      <c r="O139" s="15"/>
+      <c r="L139" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="M139" s="18"/>
+      <c r="N139" s="18"/>
+      <c r="O139" s="18"/>
     </row>
     <row r="140" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G140" s="2">
@@ -5143,20 +5149,21 @@
       <c r="H140" s="7">
         <v>46010</v>
       </c>
-      <c r="I140" s="7"/>
-      <c r="J140" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v>Saturday</v>
+      <c r="I140" s="7">
+        <v>46045</v>
+      </c>
+      <c r="J140" s="2" t="s">
+        <v>460</v>
       </c>
       <c r="K140" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="L140" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="M140" s="15"/>
-      <c r="N140" s="15"/>
-      <c r="O140" s="15"/>
+      <c r="L140" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="M140" s="18"/>
+      <c r="N140" s="18"/>
+      <c r="O140" s="18"/>
     </row>
     <row r="141" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G141" s="2">
@@ -5165,20 +5172,21 @@
       <c r="H141" s="7">
         <v>46011</v>
       </c>
-      <c r="I141" s="7"/>
-      <c r="J141" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v>Saturday</v>
+      <c r="I141" s="7">
+        <v>46045</v>
+      </c>
+      <c r="J141" s="2" t="s">
+        <v>460</v>
       </c>
       <c r="K141" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="L141" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="M141" s="15"/>
-      <c r="N141" s="15"/>
-      <c r="O141" s="15"/>
+      <c r="L141" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="M141" s="18"/>
+      <c r="N141" s="18"/>
+      <c r="O141" s="18"/>
     </row>
     <row r="142" spans="7:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="G142" s="2">
@@ -5187,20 +5195,21 @@
       <c r="H142" s="7">
         <v>46012</v>
       </c>
-      <c r="I142" s="7"/>
-      <c r="J142" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v>Saturday</v>
+      <c r="I142" s="7">
+        <v>46046</v>
+      </c>
+      <c r="J142" s="2" t="s">
+        <v>461</v>
       </c>
       <c r="K142" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="L142" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="M142" s="15"/>
-      <c r="N142" s="15"/>
-      <c r="O142" s="15"/>
+      <c r="L142" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="M142" s="18"/>
+      <c r="N142" s="18"/>
+      <c r="O142" s="18"/>
     </row>
     <row r="143" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G143" s="2">
@@ -5209,20 +5218,21 @@
       <c r="H143" s="7">
         <v>46013</v>
       </c>
-      <c r="I143" s="7"/>
-      <c r="J143" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v>Saturday</v>
+      <c r="I143" s="7">
+        <v>46046</v>
+      </c>
+      <c r="J143" s="2" t="s">
+        <v>461</v>
       </c>
       <c r="K143" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="L143" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="M143" s="15"/>
-      <c r="N143" s="15"/>
-      <c r="O143" s="15"/>
+      <c r="L143" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="M143" s="18"/>
+      <c r="N143" s="18"/>
+      <c r="O143" s="18"/>
     </row>
     <row r="144" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G144" s="2">
@@ -5231,20 +5241,21 @@
       <c r="H144" s="7">
         <v>46014</v>
       </c>
-      <c r="I144" s="7"/>
-      <c r="J144" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v>Saturday</v>
+      <c r="I144" s="7">
+        <v>46046</v>
+      </c>
+      <c r="J144" s="2" t="s">
+        <v>461</v>
       </c>
       <c r="K144" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="L144" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="M144" s="15"/>
-      <c r="N144" s="15"/>
-      <c r="O144" s="15"/>
+      <c r="L144" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="M144" s="18"/>
+      <c r="N144" s="18"/>
+      <c r="O144" s="18"/>
     </row>
     <row r="145" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G145" s="2">
@@ -5253,20 +5264,21 @@
       <c r="H145" s="7">
         <v>46015</v>
       </c>
-      <c r="I145" s="7"/>
-      <c r="J145" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v>Saturday</v>
+      <c r="I145" s="7">
+        <v>46046</v>
+      </c>
+      <c r="J145" s="2" t="s">
+        <v>461</v>
       </c>
       <c r="K145" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="L145" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="M145" s="15"/>
-      <c r="N145" s="15"/>
-      <c r="O145" s="15"/>
+      <c r="L145" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="M145" s="18"/>
+      <c r="N145" s="18"/>
+      <c r="O145" s="18"/>
     </row>
     <row r="146" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G146" s="2">
@@ -5275,20 +5287,21 @@
       <c r="H146" s="7">
         <v>46016</v>
       </c>
-      <c r="I146" s="7"/>
-      <c r="J146" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v>Saturday</v>
+      <c r="I146" s="7">
+        <v>46046</v>
+      </c>
+      <c r="J146" s="2" t="s">
+        <v>461</v>
       </c>
       <c r="K146" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="L146" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="M146" s="15"/>
-      <c r="N146" s="15"/>
-      <c r="O146" s="15"/>
+      <c r="L146" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="M146" s="18"/>
+      <c r="N146" s="18"/>
+      <c r="O146" s="18"/>
     </row>
     <row r="147" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G147" s="2">
@@ -5297,20 +5310,21 @@
       <c r="H147" s="7">
         <v>46017</v>
       </c>
-      <c r="I147" s="7"/>
-      <c r="J147" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v>Saturday</v>
+      <c r="I147" s="7">
+        <v>46046</v>
+      </c>
+      <c r="J147" s="2" t="s">
+        <v>461</v>
       </c>
       <c r="K147" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="L147" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="M147" s="15"/>
-      <c r="N147" s="15"/>
-      <c r="O147" s="15"/>
+      <c r="L147" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="M147" s="18"/>
+      <c r="N147" s="18"/>
+      <c r="O147" s="18"/>
     </row>
     <row r="148" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G148" s="2">
@@ -5319,20 +5333,21 @@
       <c r="H148" s="7">
         <v>46018</v>
       </c>
-      <c r="I148" s="7"/>
-      <c r="J148" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v>Saturday</v>
+      <c r="I148" s="7">
+        <v>46047</v>
+      </c>
+      <c r="J148" s="2" t="s">
+        <v>458</v>
       </c>
       <c r="K148" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="L148" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="M148" s="15"/>
-      <c r="N148" s="15"/>
-      <c r="O148" s="15"/>
+      <c r="L148" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="M148" s="18"/>
+      <c r="N148" s="18"/>
+      <c r="O148" s="18"/>
     </row>
     <row r="149" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G149" s="2">
@@ -5341,20 +5356,21 @@
       <c r="H149" s="7">
         <v>46019</v>
       </c>
-      <c r="I149" s="7"/>
-      <c r="J149" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v>Saturday</v>
+      <c r="I149" s="7">
+        <v>46047</v>
+      </c>
+      <c r="J149" s="2" t="s">
+        <v>458</v>
       </c>
       <c r="K149" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="L149" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="M149" s="15"/>
-      <c r="N149" s="15"/>
-      <c r="O149" s="15"/>
+      <c r="L149" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="M149" s="18"/>
+      <c r="N149" s="18"/>
+      <c r="O149" s="18"/>
     </row>
     <row r="150" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G150" s="2">
@@ -5363,20 +5379,21 @@
       <c r="H150" s="7">
         <v>46020</v>
       </c>
-      <c r="I150" s="7"/>
-      <c r="J150" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v>Saturday</v>
+      <c r="I150" s="7">
+        <v>46047</v>
+      </c>
+      <c r="J150" s="2" t="s">
+        <v>458</v>
       </c>
       <c r="K150" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="L150" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="M150" s="15"/>
-      <c r="N150" s="15"/>
-      <c r="O150" s="15"/>
+      <c r="L150" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="M150" s="18"/>
+      <c r="N150" s="18"/>
+      <c r="O150" s="18"/>
     </row>
     <row r="151" spans="7:15" s="14" customFormat="1" x14ac:dyDescent="0.3">
       <c r="G151" s="6">
@@ -5385,20 +5402,21 @@
       <c r="H151" s="10">
         <v>46021</v>
       </c>
-      <c r="I151" s="10"/>
-      <c r="J151" s="6" t="str">
-        <f t="shared" si="7"/>
-        <v>Saturday</v>
+      <c r="I151" s="7">
+        <v>46048</v>
+      </c>
+      <c r="J151" s="6" t="s">
+        <v>457</v>
       </c>
       <c r="K151" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="L151" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="M151" s="20"/>
-      <c r="N151" s="20"/>
-      <c r="O151" s="20"/>
+      <c r="L151" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="M151" s="19"/>
+      <c r="N151" s="19"/>
+      <c r="O151" s="19"/>
     </row>
     <row r="152" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G152" s="2">
@@ -5407,20 +5425,21 @@
       <c r="H152" s="7">
         <v>46022</v>
       </c>
-      <c r="I152" s="7"/>
-      <c r="J152" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v>Saturday</v>
+      <c r="I152" s="7">
+        <v>46048</v>
+      </c>
+      <c r="J152" s="2" t="s">
+        <v>457</v>
       </c>
       <c r="K152" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="L152" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="M152" s="15"/>
-      <c r="N152" s="15"/>
-      <c r="O152" s="15"/>
+      <c r="L152" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="M152" s="18"/>
+      <c r="N152" s="18"/>
+      <c r="O152" s="18"/>
     </row>
     <row r="153" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G153" s="2">
@@ -5429,20 +5448,21 @@
       <c r="H153" s="7">
         <v>46023</v>
       </c>
-      <c r="I153" s="7"/>
-      <c r="J153" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v>Saturday</v>
+      <c r="I153" s="7">
+        <v>46058</v>
+      </c>
+      <c r="J153" s="2" t="s">
+        <v>455</v>
       </c>
       <c r="K153" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="L153" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="M153" s="15"/>
-      <c r="N153" s="15"/>
-      <c r="O153" s="15"/>
+      <c r="L153" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="M153" s="18"/>
+      <c r="N153" s="18"/>
+      <c r="O153" s="18"/>
     </row>
     <row r="154" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G154" s="2">
@@ -5451,20 +5471,21 @@
       <c r="H154" s="7">
         <v>46024</v>
       </c>
-      <c r="I154" s="7"/>
-      <c r="J154" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v>Saturday</v>
+      <c r="I154" s="7">
+        <v>46060</v>
+      </c>
+      <c r="J154" s="2" t="s">
+        <v>461</v>
       </c>
       <c r="K154" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="L154" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="M154" s="15"/>
-      <c r="N154" s="15"/>
-      <c r="O154" s="15"/>
+      <c r="L154" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="M154" s="18"/>
+      <c r="N154" s="18"/>
+      <c r="O154" s="18"/>
     </row>
     <row r="155" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G155" s="2">
@@ -5473,20 +5494,21 @@
       <c r="H155" s="7">
         <v>46025</v>
       </c>
-      <c r="I155" s="7"/>
-      <c r="J155" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v>Saturday</v>
+      <c r="I155" s="7">
+        <v>46060</v>
+      </c>
+      <c r="J155" s="2" t="s">
+        <v>461</v>
       </c>
       <c r="K155" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="L155" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="M155" s="15"/>
-      <c r="N155" s="15"/>
-      <c r="O155" s="15"/>
+      <c r="L155" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="M155" s="18"/>
+      <c r="N155" s="18"/>
+      <c r="O155" s="18"/>
     </row>
     <row r="156" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G156" s="2">
@@ -5495,20 +5517,21 @@
       <c r="H156" s="7">
         <v>46026</v>
       </c>
-      <c r="I156" s="7"/>
-      <c r="J156" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v>Saturday</v>
+      <c r="I156" s="7">
+        <v>46062</v>
+      </c>
+      <c r="J156" s="2" t="s">
+        <v>458</v>
       </c>
       <c r="K156" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="L156" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="M156" s="15"/>
-      <c r="N156" s="15"/>
-      <c r="O156" s="15"/>
+      <c r="L156" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="M156" s="18"/>
+      <c r="N156" s="18"/>
+      <c r="O156" s="18"/>
     </row>
     <row r="157" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G157" s="2">
@@ -5517,20 +5540,21 @@
       <c r="H157" s="7">
         <v>46027</v>
       </c>
-      <c r="I157" s="7"/>
-      <c r="J157" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v>Saturday</v>
+      <c r="I157" s="7">
+        <v>46063</v>
+      </c>
+      <c r="J157" s="2" t="s">
+        <v>458</v>
       </c>
       <c r="K157" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="L157" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="M157" s="15"/>
-      <c r="N157" s="15"/>
-      <c r="O157" s="15"/>
+      <c r="L157" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="M157" s="18"/>
+      <c r="N157" s="18"/>
+      <c r="O157" s="18"/>
     </row>
     <row r="158" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G158" s="2">
@@ -5539,20 +5563,22 @@
       <c r="H158" s="7">
         <v>46028</v>
       </c>
-      <c r="I158" s="7"/>
+      <c r="I158" s="7">
+        <v>46066</v>
+      </c>
       <c r="J158" s="2" t="str">
         <f t="shared" si="7"/>
-        <v>Saturday</v>
+        <v>dddd</v>
       </c>
       <c r="K158" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="L158" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="M158" s="15"/>
-      <c r="N158" s="15"/>
-      <c r="O158" s="15"/>
+      <c r="L158" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="M158" s="18"/>
+      <c r="N158" s="18"/>
+      <c r="O158" s="18"/>
     </row>
     <row r="159" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G159" s="2">
@@ -5561,20 +5587,22 @@
       <c r="H159" s="7">
         <v>46029</v>
       </c>
-      <c r="I159" s="7"/>
+      <c r="I159" s="7">
+        <v>46067</v>
+      </c>
       <c r="J159" s="2" t="str">
         <f t="shared" si="7"/>
-        <v>Saturday</v>
+        <v>dddd</v>
       </c>
       <c r="K159" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="L159" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="M159" s="15"/>
-      <c r="N159" s="15"/>
-      <c r="O159" s="15"/>
+      <c r="L159" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="M159" s="18"/>
+      <c r="N159" s="18"/>
+      <c r="O159" s="18"/>
     </row>
     <row r="160" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G160" s="2">
@@ -5583,20 +5611,22 @@
       <c r="H160" s="7">
         <v>46030</v>
       </c>
-      <c r="I160" s="7"/>
+      <c r="I160" s="7">
+        <v>46067</v>
+      </c>
       <c r="J160" s="2" t="str">
         <f t="shared" si="7"/>
-        <v>Saturday</v>
+        <v>dddd</v>
       </c>
       <c r="K160" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="L160" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="M160" s="15"/>
-      <c r="N160" s="15"/>
-      <c r="O160" s="15"/>
+      <c r="L160" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="M160" s="18"/>
+      <c r="N160" s="18"/>
+      <c r="O160" s="18"/>
     </row>
     <row r="161" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G161" s="2">
@@ -5605,20 +5635,22 @@
       <c r="H161" s="7">
         <v>46031</v>
       </c>
-      <c r="I161" s="7"/>
+      <c r="I161" s="7">
+        <v>46074</v>
+      </c>
       <c r="J161" s="2" t="str">
         <f t="shared" si="7"/>
-        <v>Saturday</v>
+        <v>dddd</v>
       </c>
       <c r="K161" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="L161" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="M161" s="15"/>
-      <c r="N161" s="15"/>
-      <c r="O161" s="15"/>
+      <c r="L161" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="M161" s="18"/>
+      <c r="N161" s="18"/>
+      <c r="O161" s="18"/>
     </row>
     <row r="162" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G162" s="2">
@@ -5627,20 +5659,22 @@
       <c r="H162" s="7">
         <v>46032</v>
       </c>
-      <c r="I162" s="7"/>
+      <c r="I162" s="7">
+        <v>46074</v>
+      </c>
       <c r="J162" s="2" t="str">
         <f t="shared" si="7"/>
-        <v>Saturday</v>
+        <v>dddd</v>
       </c>
       <c r="K162" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="L162" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="M162" s="15"/>
-      <c r="N162" s="15"/>
-      <c r="O162" s="15"/>
+      <c r="L162" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="M162" s="18"/>
+      <c r="N162" s="18"/>
+      <c r="O162" s="18"/>
     </row>
     <row r="163" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G163" s="2">
@@ -5649,20 +5683,22 @@
       <c r="H163" s="7">
         <v>46033</v>
       </c>
-      <c r="I163" s="7"/>
+      <c r="I163" s="7">
+        <v>46074</v>
+      </c>
       <c r="J163" s="2" t="str">
         <f t="shared" si="7"/>
-        <v>Saturday</v>
+        <v>dddd</v>
       </c>
       <c r="K163" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="L163" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="M163" s="15"/>
-      <c r="N163" s="15"/>
-      <c r="O163" s="15"/>
+      <c r="L163" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="M163" s="18"/>
+      <c r="N163" s="18"/>
+      <c r="O163" s="18"/>
     </row>
     <row r="164" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G164" s="2">
@@ -5671,10 +5707,12 @@
       <c r="H164" s="7">
         <v>46034</v>
       </c>
-      <c r="I164" s="7"/>
+      <c r="I164" s="7">
+        <v>46075</v>
+      </c>
       <c r="J164" s="2" t="str">
         <f t="shared" ref="J164:J227" si="8">TEXT(I164, "dddd")</f>
-        <v>Saturday</v>
+        <v>dddd</v>
       </c>
       <c r="K164" s="2" t="s">
         <v>193</v>
@@ -5682,9 +5720,9 @@
       <c r="L164" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M164" s="15"/>
-      <c r="N164" s="15"/>
-      <c r="O164" s="15"/>
+      <c r="M164" s="18"/>
+      <c r="N164" s="18"/>
+      <c r="O164" s="18"/>
     </row>
     <row r="165" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G165" s="2">
@@ -5693,10 +5731,12 @@
       <c r="H165" s="7">
         <v>46035</v>
       </c>
-      <c r="I165" s="7"/>
+      <c r="I165" s="7">
+        <v>46075</v>
+      </c>
       <c r="J165" s="2" t="str">
         <f t="shared" si="8"/>
-        <v>Saturday</v>
+        <v>dddd</v>
       </c>
       <c r="K165" s="2" t="s">
         <v>194</v>
@@ -5704,9 +5744,9 @@
       <c r="L165" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M165" s="15"/>
-      <c r="N165" s="15"/>
-      <c r="O165" s="15"/>
+      <c r="M165" s="18"/>
+      <c r="N165" s="18"/>
+      <c r="O165" s="18"/>
     </row>
     <row r="166" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G166" s="2">
@@ -5726,9 +5766,9 @@
       <c r="L166" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M166" s="15"/>
-      <c r="N166" s="15"/>
-      <c r="O166" s="15"/>
+      <c r="M166" s="18"/>
+      <c r="N166" s="18"/>
+      <c r="O166" s="18"/>
     </row>
     <row r="167" spans="7:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="G167" s="2">
@@ -5748,9 +5788,9 @@
       <c r="L167" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M167" s="15"/>
-      <c r="N167" s="15"/>
-      <c r="O167" s="15"/>
+      <c r="M167" s="18"/>
+      <c r="N167" s="18"/>
+      <c r="O167" s="18"/>
     </row>
     <row r="168" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G168" s="2">
@@ -5770,9 +5810,9 @@
       <c r="L168" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M168" s="15"/>
-      <c r="N168" s="15"/>
-      <c r="O168" s="15"/>
+      <c r="M168" s="18"/>
+      <c r="N168" s="18"/>
+      <c r="O168" s="18"/>
     </row>
     <row r="169" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G169" s="2">
@@ -5792,9 +5832,9 @@
       <c r="L169" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M169" s="15"/>
-      <c r="N169" s="15"/>
-      <c r="O169" s="15"/>
+      <c r="M169" s="18"/>
+      <c r="N169" s="18"/>
+      <c r="O169" s="18"/>
     </row>
     <row r="170" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G170" s="2">
@@ -5814,9 +5854,9 @@
       <c r="L170" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M170" s="15"/>
-      <c r="N170" s="15"/>
-      <c r="O170" s="15"/>
+      <c r="M170" s="18"/>
+      <c r="N170" s="18"/>
+      <c r="O170" s="18"/>
     </row>
     <row r="171" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G171" s="2">
@@ -5836,9 +5876,9 @@
       <c r="L171" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M171" s="15"/>
-      <c r="N171" s="15"/>
-      <c r="O171" s="15"/>
+      <c r="M171" s="18"/>
+      <c r="N171" s="18"/>
+      <c r="O171" s="18"/>
     </row>
     <row r="172" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G172" s="2">
@@ -5858,9 +5898,9 @@
       <c r="L172" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M172" s="15"/>
-      <c r="N172" s="15"/>
-      <c r="O172" s="15"/>
+      <c r="M172" s="18"/>
+      <c r="N172" s="18"/>
+      <c r="O172" s="18"/>
     </row>
     <row r="173" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G173" s="2">
@@ -5880,9 +5920,9 @@
       <c r="L173" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M173" s="15"/>
-      <c r="N173" s="15"/>
-      <c r="O173" s="15"/>
+      <c r="M173" s="18"/>
+      <c r="N173" s="18"/>
+      <c r="O173" s="18"/>
     </row>
     <row r="174" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G174" s="2">
@@ -5902,9 +5942,9 @@
       <c r="L174" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M174" s="15"/>
-      <c r="N174" s="15"/>
-      <c r="O174" s="15"/>
+      <c r="M174" s="18"/>
+      <c r="N174" s="18"/>
+      <c r="O174" s="18"/>
     </row>
     <row r="175" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G175" s="2">
@@ -5924,9 +5964,9 @@
       <c r="L175" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M175" s="15"/>
-      <c r="N175" s="15"/>
-      <c r="O175" s="15"/>
+      <c r="M175" s="18"/>
+      <c r="N175" s="18"/>
+      <c r="O175" s="18"/>
     </row>
     <row r="176" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G176" s="2">
@@ -5946,9 +5986,9 @@
       <c r="L176" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M176" s="15"/>
-      <c r="N176" s="15"/>
-      <c r="O176" s="15"/>
+      <c r="M176" s="18"/>
+      <c r="N176" s="18"/>
+      <c r="O176" s="18"/>
     </row>
     <row r="177" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G177" s="2">
@@ -5968,9 +6008,9 @@
       <c r="L177" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M177" s="15"/>
-      <c r="N177" s="15"/>
-      <c r="O177" s="15"/>
+      <c r="M177" s="18"/>
+      <c r="N177" s="18"/>
+      <c r="O177" s="18"/>
     </row>
     <row r="178" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G178" s="2">
@@ -5990,9 +6030,9 @@
       <c r="L178" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M178" s="15"/>
-      <c r="N178" s="15"/>
-      <c r="O178" s="15"/>
+      <c r="M178" s="18"/>
+      <c r="N178" s="18"/>
+      <c r="O178" s="18"/>
     </row>
     <row r="179" spans="7:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="G179" s="2">
@@ -6012,9 +6052,9 @@
       <c r="L179" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M179" s="15"/>
-      <c r="N179" s="15"/>
-      <c r="O179" s="15"/>
+      <c r="M179" s="18"/>
+      <c r="N179" s="18"/>
+      <c r="O179" s="18"/>
     </row>
     <row r="180" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G180" s="2">
@@ -6034,9 +6074,9 @@
       <c r="L180" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M180" s="15"/>
-      <c r="N180" s="15"/>
-      <c r="O180" s="15"/>
+      <c r="M180" s="18"/>
+      <c r="N180" s="18"/>
+      <c r="O180" s="18"/>
     </row>
     <row r="181" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G181" s="2">
@@ -6056,9 +6096,9 @@
       <c r="L181" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M181" s="15"/>
-      <c r="N181" s="15"/>
-      <c r="O181" s="15"/>
+      <c r="M181" s="18"/>
+      <c r="N181" s="18"/>
+      <c r="O181" s="18"/>
     </row>
     <row r="182" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G182" s="2">
@@ -6078,9 +6118,9 @@
       <c r="L182" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M182" s="15"/>
-      <c r="N182" s="15"/>
-      <c r="O182" s="15"/>
+      <c r="M182" s="18"/>
+      <c r="N182" s="18"/>
+      <c r="O182" s="18"/>
     </row>
     <row r="183" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G183" s="2">
@@ -6100,9 +6140,9 @@
       <c r="L183" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M183" s="15"/>
-      <c r="N183" s="15"/>
-      <c r="O183" s="15"/>
+      <c r="M183" s="18"/>
+      <c r="N183" s="18"/>
+      <c r="O183" s="18"/>
     </row>
     <row r="184" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G184" s="2">
@@ -6122,9 +6162,9 @@
       <c r="L184" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M184" s="15"/>
-      <c r="N184" s="15"/>
-      <c r="O184" s="15"/>
+      <c r="M184" s="18"/>
+      <c r="N184" s="18"/>
+      <c r="O184" s="18"/>
     </row>
     <row r="185" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G185" s="2">
@@ -6144,9 +6184,9 @@
       <c r="L185" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M185" s="15"/>
-      <c r="N185" s="15"/>
-      <c r="O185" s="15"/>
+      <c r="M185" s="18"/>
+      <c r="N185" s="18"/>
+      <c r="O185" s="18"/>
     </row>
     <row r="186" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G186" s="2">
@@ -6166,9 +6206,9 @@
       <c r="L186" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M186" s="15"/>
-      <c r="N186" s="15"/>
-      <c r="O186" s="15"/>
+      <c r="M186" s="18"/>
+      <c r="N186" s="18"/>
+      <c r="O186" s="18"/>
     </row>
     <row r="187" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G187" s="2">
@@ -6188,9 +6228,9 @@
       <c r="L187" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M187" s="15"/>
-      <c r="N187" s="15"/>
-      <c r="O187" s="15"/>
+      <c r="M187" s="18"/>
+      <c r="N187" s="18"/>
+      <c r="O187" s="18"/>
     </row>
     <row r="188" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G188" s="2">
@@ -6210,9 +6250,9 @@
       <c r="L188" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M188" s="15"/>
-      <c r="N188" s="15"/>
-      <c r="O188" s="15"/>
+      <c r="M188" s="18"/>
+      <c r="N188" s="18"/>
+      <c r="O188" s="18"/>
     </row>
     <row r="189" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G189" s="2">
@@ -6232,9 +6272,9 @@
       <c r="L189" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M189" s="15"/>
-      <c r="N189" s="15"/>
-      <c r="O189" s="15"/>
+      <c r="M189" s="18"/>
+      <c r="N189" s="18"/>
+      <c r="O189" s="18"/>
     </row>
     <row r="190" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G190" s="2">
@@ -6254,9 +6294,9 @@
       <c r="L190" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M190" s="15"/>
-      <c r="N190" s="15"/>
-      <c r="O190" s="15"/>
+      <c r="M190" s="18"/>
+      <c r="N190" s="18"/>
+      <c r="O190" s="18"/>
     </row>
     <row r="191" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G191" s="2">
@@ -6276,9 +6316,9 @@
       <c r="L191" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M191" s="15"/>
-      <c r="N191" s="15"/>
-      <c r="O191" s="15"/>
+      <c r="M191" s="18"/>
+      <c r="N191" s="18"/>
+      <c r="O191" s="18"/>
     </row>
     <row r="192" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G192" s="2">
@@ -6298,9 +6338,9 @@
       <c r="L192" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M192" s="15"/>
-      <c r="N192" s="15"/>
-      <c r="O192" s="15"/>
+      <c r="M192" s="18"/>
+      <c r="N192" s="18"/>
+      <c r="O192" s="18"/>
     </row>
     <row r="193" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G193" s="2">
@@ -6320,9 +6360,9 @@
       <c r="L193" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M193" s="15"/>
-      <c r="N193" s="15"/>
-      <c r="O193" s="15"/>
+      <c r="M193" s="18"/>
+      <c r="N193" s="18"/>
+      <c r="O193" s="18"/>
     </row>
     <row r="194" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G194" s="2">
@@ -6342,9 +6382,9 @@
       <c r="L194" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M194" s="15"/>
-      <c r="N194" s="15"/>
-      <c r="O194" s="15"/>
+      <c r="M194" s="18"/>
+      <c r="N194" s="18"/>
+      <c r="O194" s="18"/>
     </row>
     <row r="195" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G195" s="2">
@@ -6364,9 +6404,9 @@
       <c r="L195" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M195" s="15"/>
-      <c r="N195" s="15"/>
-      <c r="O195" s="15"/>
+      <c r="M195" s="18"/>
+      <c r="N195" s="18"/>
+      <c r="O195" s="18"/>
     </row>
     <row r="196" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G196" s="2">
@@ -6386,9 +6426,9 @@
       <c r="L196" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M196" s="15"/>
-      <c r="N196" s="15"/>
-      <c r="O196" s="15"/>
+      <c r="M196" s="18"/>
+      <c r="N196" s="18"/>
+      <c r="O196" s="18"/>
     </row>
     <row r="197" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G197" s="2">
@@ -6408,9 +6448,9 @@
       <c r="L197" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M197" s="15"/>
-      <c r="N197" s="15"/>
-      <c r="O197" s="15"/>
+      <c r="M197" s="18"/>
+      <c r="N197" s="18"/>
+      <c r="O197" s="18"/>
     </row>
     <row r="198" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G198" s="2">
@@ -6430,9 +6470,9 @@
       <c r="L198" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M198" s="15"/>
-      <c r="N198" s="15"/>
-      <c r="O198" s="15"/>
+      <c r="M198" s="18"/>
+      <c r="N198" s="18"/>
+      <c r="O198" s="18"/>
     </row>
     <row r="199" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G199" s="2">
@@ -6452,9 +6492,9 @@
       <c r="L199" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M199" s="15"/>
-      <c r="N199" s="15"/>
-      <c r="O199" s="15"/>
+      <c r="M199" s="18"/>
+      <c r="N199" s="18"/>
+      <c r="O199" s="18"/>
     </row>
     <row r="200" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G200" s="2">
@@ -6474,9 +6514,9 @@
       <c r="L200" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M200" s="15"/>
-      <c r="N200" s="15"/>
-      <c r="O200" s="15"/>
+      <c r="M200" s="18"/>
+      <c r="N200" s="18"/>
+      <c r="O200" s="18"/>
     </row>
     <row r="201" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G201" s="2">
@@ -6496,9 +6536,9 @@
       <c r="L201" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M201" s="15"/>
-      <c r="N201" s="15"/>
-      <c r="O201" s="15"/>
+      <c r="M201" s="18"/>
+      <c r="N201" s="18"/>
+      <c r="O201" s="18"/>
     </row>
     <row r="202" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G202" s="2">
@@ -6518,9 +6558,9 @@
       <c r="L202" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M202" s="15"/>
-      <c r="N202" s="15"/>
-      <c r="O202" s="15"/>
+      <c r="M202" s="18"/>
+      <c r="N202" s="18"/>
+      <c r="O202" s="18"/>
     </row>
     <row r="203" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G203" s="2">
@@ -6540,9 +6580,9 @@
       <c r="L203" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M203" s="15"/>
-      <c r="N203" s="15"/>
-      <c r="O203" s="15"/>
+      <c r="M203" s="18"/>
+      <c r="N203" s="18"/>
+      <c r="O203" s="18"/>
     </row>
     <row r="204" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G204" s="2">
@@ -6562,9 +6602,9 @@
       <c r="L204" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M204" s="15"/>
-      <c r="N204" s="15"/>
-      <c r="O204" s="15"/>
+      <c r="M204" s="18"/>
+      <c r="N204" s="18"/>
+      <c r="O204" s="18"/>
     </row>
     <row r="205" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G205" s="2">
@@ -6584,9 +6624,9 @@
       <c r="L205" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M205" s="15"/>
-      <c r="N205" s="15"/>
-      <c r="O205" s="15"/>
+      <c r="M205" s="18"/>
+      <c r="N205" s="18"/>
+      <c r="O205" s="18"/>
     </row>
     <row r="206" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G206" s="2">
@@ -6606,9 +6646,9 @@
       <c r="L206" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M206" s="15"/>
-      <c r="N206" s="15"/>
-      <c r="O206" s="15"/>
+      <c r="M206" s="18"/>
+      <c r="N206" s="18"/>
+      <c r="O206" s="18"/>
     </row>
     <row r="207" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G207" s="2">
@@ -6628,9 +6668,9 @@
       <c r="L207" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M207" s="15"/>
-      <c r="N207" s="15"/>
-      <c r="O207" s="15"/>
+      <c r="M207" s="18"/>
+      <c r="N207" s="18"/>
+      <c r="O207" s="18"/>
     </row>
     <row r="208" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G208" s="3">
@@ -6650,9 +6690,9 @@
       <c r="L208" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M208" s="15"/>
-      <c r="N208" s="15"/>
-      <c r="O208" s="15"/>
+      <c r="M208" s="18"/>
+      <c r="N208" s="18"/>
+      <c r="O208" s="18"/>
     </row>
     <row r="209" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G209" s="2">
@@ -6672,9 +6712,9 @@
       <c r="L209" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M209" s="15"/>
-      <c r="N209" s="15"/>
-      <c r="O209" s="15"/>
+      <c r="M209" s="18"/>
+      <c r="N209" s="18"/>
+      <c r="O209" s="18"/>
     </row>
     <row r="210" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G210" s="2">
@@ -6694,9 +6734,9 @@
       <c r="L210" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M210" s="15"/>
-      <c r="N210" s="15"/>
-      <c r="O210" s="15"/>
+      <c r="M210" s="18"/>
+      <c r="N210" s="18"/>
+      <c r="O210" s="18"/>
     </row>
     <row r="211" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G211" s="2">
@@ -6716,9 +6756,9 @@
       <c r="L211" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M211" s="15"/>
-      <c r="N211" s="15"/>
-      <c r="O211" s="15"/>
+      <c r="M211" s="18"/>
+      <c r="N211" s="18"/>
+      <c r="O211" s="18"/>
     </row>
     <row r="212" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G212" s="2">
@@ -6738,9 +6778,9 @@
       <c r="L212" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M212" s="15"/>
-      <c r="N212" s="15"/>
-      <c r="O212" s="15"/>
+      <c r="M212" s="18"/>
+      <c r="N212" s="18"/>
+      <c r="O212" s="18"/>
     </row>
     <row r="213" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G213" s="2">
@@ -6760,9 +6800,9 @@
       <c r="L213" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M213" s="15"/>
-      <c r="N213" s="15"/>
-      <c r="O213" s="15"/>
+      <c r="M213" s="18"/>
+      <c r="N213" s="18"/>
+      <c r="O213" s="18"/>
     </row>
     <row r="214" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G214" s="2">
@@ -6782,9 +6822,9 @@
       <c r="L214" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M214" s="15"/>
-      <c r="N214" s="15"/>
-      <c r="O214" s="15"/>
+      <c r="M214" s="18"/>
+      <c r="N214" s="18"/>
+      <c r="O214" s="18"/>
     </row>
     <row r="215" spans="7:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="G215" s="2">
@@ -6804,9 +6844,9 @@
       <c r="L215" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M215" s="15"/>
-      <c r="N215" s="15"/>
-      <c r="O215" s="15"/>
+      <c r="M215" s="18"/>
+      <c r="N215" s="18"/>
+      <c r="O215" s="18"/>
     </row>
     <row r="216" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G216" s="2">
@@ -6826,9 +6866,9 @@
       <c r="L216" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M216" s="15"/>
-      <c r="N216" s="15"/>
-      <c r="O216" s="15"/>
+      <c r="M216" s="18"/>
+      <c r="N216" s="18"/>
+      <c r="O216" s="18"/>
     </row>
     <row r="217" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G217" s="2">
@@ -6848,9 +6888,9 @@
       <c r="L217" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M217" s="15"/>
-      <c r="N217" s="15"/>
-      <c r="O217" s="15"/>
+      <c r="M217" s="18"/>
+      <c r="N217" s="18"/>
+      <c r="O217" s="18"/>
     </row>
     <row r="218" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G218" s="2">
@@ -6870,9 +6910,9 @@
       <c r="L218" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M218" s="15"/>
-      <c r="N218" s="15"/>
-      <c r="O218" s="15"/>
+      <c r="M218" s="18"/>
+      <c r="N218" s="18"/>
+      <c r="O218" s="18"/>
     </row>
     <row r="219" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G219" s="2">
@@ -6892,9 +6932,9 @@
       <c r="L219" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M219" s="15"/>
-      <c r="N219" s="15"/>
-      <c r="O219" s="15"/>
+      <c r="M219" s="18"/>
+      <c r="N219" s="18"/>
+      <c r="O219" s="18"/>
     </row>
     <row r="220" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G220" s="2">
@@ -6914,9 +6954,9 @@
       <c r="L220" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M220" s="15"/>
-      <c r="N220" s="15"/>
-      <c r="O220" s="15"/>
+      <c r="M220" s="18"/>
+      <c r="N220" s="18"/>
+      <c r="O220" s="18"/>
     </row>
     <row r="221" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G221" s="2">
@@ -6936,9 +6976,9 @@
       <c r="L221" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M221" s="15"/>
-      <c r="N221" s="15"/>
-      <c r="O221" s="15"/>
+      <c r="M221" s="18"/>
+      <c r="N221" s="18"/>
+      <c r="O221" s="18"/>
     </row>
     <row r="222" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G222" s="2">
@@ -6958,9 +6998,9 @@
       <c r="L222" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M222" s="15"/>
-      <c r="N222" s="15"/>
-      <c r="O222" s="15"/>
+      <c r="M222" s="18"/>
+      <c r="N222" s="18"/>
+      <c r="O222" s="18"/>
     </row>
     <row r="223" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G223" s="2">
@@ -6980,9 +7020,9 @@
       <c r="L223" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M223" s="15"/>
-      <c r="N223" s="15"/>
-      <c r="O223" s="15"/>
+      <c r="M223" s="18"/>
+      <c r="N223" s="18"/>
+      <c r="O223" s="18"/>
     </row>
     <row r="224" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G224" s="2">
@@ -7002,9 +7042,9 @@
       <c r="L224" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M224" s="15"/>
-      <c r="N224" s="15"/>
-      <c r="O224" s="15"/>
+      <c r="M224" s="18"/>
+      <c r="N224" s="18"/>
+      <c r="O224" s="18"/>
     </row>
     <row r="225" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G225" s="2">
@@ -7024,9 +7064,9 @@
       <c r="L225" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M225" s="15"/>
-      <c r="N225" s="15"/>
-      <c r="O225" s="15"/>
+      <c r="M225" s="18"/>
+      <c r="N225" s="18"/>
+      <c r="O225" s="18"/>
     </row>
     <row r="226" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G226" s="2">
@@ -7046,9 +7086,9 @@
       <c r="L226" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M226" s="15"/>
-      <c r="N226" s="15"/>
-      <c r="O226" s="15"/>
+      <c r="M226" s="18"/>
+      <c r="N226" s="18"/>
+      <c r="O226" s="18"/>
     </row>
     <row r="227" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G227" s="2">
@@ -7068,9 +7108,9 @@
       <c r="L227" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M227" s="15"/>
-      <c r="N227" s="15"/>
-      <c r="O227" s="15"/>
+      <c r="M227" s="18"/>
+      <c r="N227" s="18"/>
+      <c r="O227" s="18"/>
     </row>
     <row r="228" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G228" s="2">
@@ -7090,9 +7130,9 @@
       <c r="L228" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M228" s="15"/>
-      <c r="N228" s="15"/>
-      <c r="O228" s="15"/>
+      <c r="M228" s="18"/>
+      <c r="N228" s="18"/>
+      <c r="O228" s="18"/>
     </row>
     <row r="229" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G229" s="2">
@@ -7112,9 +7152,9 @@
       <c r="L229" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M229" s="15"/>
-      <c r="N229" s="15"/>
-      <c r="O229" s="15"/>
+      <c r="M229" s="18"/>
+      <c r="N229" s="18"/>
+      <c r="O229" s="18"/>
     </row>
     <row r="230" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G230" s="2">
@@ -7134,9 +7174,9 @@
       <c r="L230" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M230" s="15"/>
-      <c r="N230" s="15"/>
-      <c r="O230" s="15"/>
+      <c r="M230" s="18"/>
+      <c r="N230" s="18"/>
+      <c r="O230" s="18"/>
     </row>
     <row r="231" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G231" s="2">
@@ -7156,9 +7196,9 @@
       <c r="L231" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M231" s="15"/>
-      <c r="N231" s="15"/>
-      <c r="O231" s="15"/>
+      <c r="M231" s="18"/>
+      <c r="N231" s="18"/>
+      <c r="O231" s="18"/>
     </row>
     <row r="232" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G232" s="2">
@@ -7178,9 +7218,9 @@
       <c r="L232" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M232" s="15"/>
-      <c r="N232" s="15"/>
-      <c r="O232" s="15"/>
+      <c r="M232" s="18"/>
+      <c r="N232" s="18"/>
+      <c r="O232" s="18"/>
     </row>
     <row r="233" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G233" s="2">
@@ -7200,9 +7240,9 @@
       <c r="L233" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M233" s="15"/>
-      <c r="N233" s="15"/>
-      <c r="O233" s="15"/>
+      <c r="M233" s="18"/>
+      <c r="N233" s="18"/>
+      <c r="O233" s="18"/>
     </row>
     <row r="234" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G234" s="2">
@@ -7222,9 +7262,9 @@
       <c r="L234" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M234" s="15"/>
-      <c r="N234" s="15"/>
-      <c r="O234" s="15"/>
+      <c r="M234" s="18"/>
+      <c r="N234" s="18"/>
+      <c r="O234" s="18"/>
     </row>
     <row r="235" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G235" s="2">
@@ -7244,9 +7284,9 @@
       <c r="L235" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M235" s="15"/>
-      <c r="N235" s="15"/>
-      <c r="O235" s="15"/>
+      <c r="M235" s="18"/>
+      <c r="N235" s="18"/>
+      <c r="O235" s="18"/>
     </row>
     <row r="236" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G236" s="2">
@@ -7266,9 +7306,9 @@
       <c r="L236" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M236" s="15"/>
-      <c r="N236" s="15"/>
-      <c r="O236" s="15"/>
+      <c r="M236" s="18"/>
+      <c r="N236" s="18"/>
+      <c r="O236" s="18"/>
     </row>
     <row r="237" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G237" s="2">
@@ -7288,9 +7328,9 @@
       <c r="L237" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M237" s="15"/>
-      <c r="N237" s="15"/>
-      <c r="O237" s="15"/>
+      <c r="M237" s="18"/>
+      <c r="N237" s="18"/>
+      <c r="O237" s="18"/>
     </row>
     <row r="238" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G238" s="2">
@@ -7310,9 +7350,9 @@
       <c r="L238" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M238" s="15"/>
-      <c r="N238" s="15"/>
-      <c r="O238" s="15"/>
+      <c r="M238" s="18"/>
+      <c r="N238" s="18"/>
+      <c r="O238" s="18"/>
     </row>
     <row r="239" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G239" s="2">
@@ -7332,9 +7372,9 @@
       <c r="L239" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M239" s="15"/>
-      <c r="N239" s="15"/>
-      <c r="O239" s="15"/>
+      <c r="M239" s="18"/>
+      <c r="N239" s="18"/>
+      <c r="O239" s="18"/>
     </row>
     <row r="240" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G240" s="2">
@@ -7354,9 +7394,9 @@
       <c r="L240" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M240" s="15"/>
-      <c r="N240" s="15"/>
-      <c r="O240" s="15"/>
+      <c r="M240" s="18"/>
+      <c r="N240" s="18"/>
+      <c r="O240" s="18"/>
     </row>
     <row r="241" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G241" s="2">
@@ -7376,9 +7416,9 @@
       <c r="L241" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M241" s="15"/>
-      <c r="N241" s="15"/>
-      <c r="O241" s="15"/>
+      <c r="M241" s="18"/>
+      <c r="N241" s="18"/>
+      <c r="O241" s="18"/>
     </row>
     <row r="242" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G242" s="2">
@@ -7398,9 +7438,9 @@
       <c r="L242" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M242" s="15"/>
-      <c r="N242" s="15"/>
-      <c r="O242" s="15"/>
+      <c r="M242" s="18"/>
+      <c r="N242" s="18"/>
+      <c r="O242" s="18"/>
     </row>
     <row r="243" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G243" s="2">
@@ -7420,9 +7460,9 @@
       <c r="L243" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M243" s="15"/>
-      <c r="N243" s="15"/>
-      <c r="O243" s="15"/>
+      <c r="M243" s="18"/>
+      <c r="N243" s="18"/>
+      <c r="O243" s="18"/>
     </row>
     <row r="244" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G244" s="2">
@@ -7442,9 +7482,9 @@
       <c r="L244" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M244" s="15"/>
-      <c r="N244" s="15"/>
-      <c r="O244" s="15"/>
+      <c r="M244" s="18"/>
+      <c r="N244" s="18"/>
+      <c r="O244" s="18"/>
     </row>
     <row r="245" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G245" s="2">
@@ -7464,9 +7504,9 @@
       <c r="L245" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M245" s="15"/>
-      <c r="N245" s="15"/>
-      <c r="O245" s="15"/>
+      <c r="M245" s="18"/>
+      <c r="N245" s="18"/>
+      <c r="O245" s="18"/>
     </row>
     <row r="246" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G246" s="2">
@@ -7486,9 +7526,9 @@
       <c r="L246" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M246" s="15"/>
-      <c r="N246" s="15"/>
-      <c r="O246" s="15"/>
+      <c r="M246" s="18"/>
+      <c r="N246" s="18"/>
+      <c r="O246" s="18"/>
     </row>
     <row r="247" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G247" s="2">
@@ -7508,9 +7548,9 @@
       <c r="L247" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M247" s="15"/>
-      <c r="N247" s="15"/>
-      <c r="O247" s="15"/>
+      <c r="M247" s="18"/>
+      <c r="N247" s="18"/>
+      <c r="O247" s="18"/>
     </row>
     <row r="248" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G248" s="2">
@@ -7530,9 +7570,9 @@
       <c r="L248" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M248" s="15"/>
-      <c r="N248" s="15"/>
-      <c r="O248" s="15"/>
+      <c r="M248" s="18"/>
+      <c r="N248" s="18"/>
+      <c r="O248" s="18"/>
     </row>
     <row r="249" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G249" s="2">
@@ -7552,9 +7592,9 @@
       <c r="L249" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M249" s="15"/>
-      <c r="N249" s="15"/>
-      <c r="O249" s="15"/>
+      <c r="M249" s="18"/>
+      <c r="N249" s="18"/>
+      <c r="O249" s="18"/>
     </row>
     <row r="250" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G250" s="2">
@@ -7574,9 +7614,9 @@
       <c r="L250" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M250" s="15"/>
-      <c r="N250" s="15"/>
-      <c r="O250" s="15"/>
+      <c r="M250" s="18"/>
+      <c r="N250" s="18"/>
+      <c r="O250" s="18"/>
     </row>
     <row r="251" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G251" s="2">
@@ -7596,9 +7636,9 @@
       <c r="L251" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M251" s="15"/>
-      <c r="N251" s="15"/>
-      <c r="O251" s="15"/>
+      <c r="M251" s="18"/>
+      <c r="N251" s="18"/>
+      <c r="O251" s="18"/>
     </row>
     <row r="252" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G252" s="2">
@@ -7618,9 +7658,9 @@
       <c r="L252" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M252" s="15"/>
-      <c r="N252" s="15"/>
-      <c r="O252" s="15"/>
+      <c r="M252" s="18"/>
+      <c r="N252" s="18"/>
+      <c r="O252" s="18"/>
     </row>
     <row r="253" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G253" s="2">
@@ -7640,9 +7680,9 @@
       <c r="L253" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M253" s="15"/>
-      <c r="N253" s="15"/>
-      <c r="O253" s="15"/>
+      <c r="M253" s="18"/>
+      <c r="N253" s="18"/>
+      <c r="O253" s="18"/>
     </row>
     <row r="254" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G254" s="2">
@@ -7662,9 +7702,9 @@
       <c r="L254" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M254" s="15"/>
-      <c r="N254" s="15"/>
-      <c r="O254" s="15"/>
+      <c r="M254" s="18"/>
+      <c r="N254" s="18"/>
+      <c r="O254" s="18"/>
     </row>
     <row r="255" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G255" s="2">
@@ -7684,9 +7724,9 @@
       <c r="L255" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M255" s="15"/>
-      <c r="N255" s="15"/>
-      <c r="O255" s="15"/>
+      <c r="M255" s="18"/>
+      <c r="N255" s="18"/>
+      <c r="O255" s="18"/>
     </row>
     <row r="256" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G256" s="2">
@@ -7706,9 +7746,9 @@
       <c r="L256" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M256" s="15"/>
-      <c r="N256" s="15"/>
-      <c r="O256" s="15"/>
+      <c r="M256" s="18"/>
+      <c r="N256" s="18"/>
+      <c r="O256" s="18"/>
     </row>
     <row r="257" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G257" s="2">
@@ -7728,9 +7768,9 @@
       <c r="L257" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M257" s="15"/>
-      <c r="N257" s="15"/>
-      <c r="O257" s="15"/>
+      <c r="M257" s="18"/>
+      <c r="N257" s="18"/>
+      <c r="O257" s="18"/>
     </row>
     <row r="258" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G258" s="2">
@@ -7750,9 +7790,9 @@
       <c r="L258" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M258" s="15"/>
-      <c r="N258" s="15"/>
-      <c r="O258" s="15"/>
+      <c r="M258" s="18"/>
+      <c r="N258" s="18"/>
+      <c r="O258" s="18"/>
     </row>
     <row r="259" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G259" s="2">
@@ -7772,9 +7812,9 @@
       <c r="L259" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M259" s="15"/>
-      <c r="N259" s="15"/>
-      <c r="O259" s="15"/>
+      <c r="M259" s="18"/>
+      <c r="N259" s="18"/>
+      <c r="O259" s="18"/>
     </row>
     <row r="260" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G260" s="2">
@@ -7794,9 +7834,9 @@
       <c r="L260" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M260" s="15"/>
-      <c r="N260" s="15"/>
-      <c r="O260" s="15"/>
+      <c r="M260" s="18"/>
+      <c r="N260" s="18"/>
+      <c r="O260" s="18"/>
     </row>
     <row r="261" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G261" s="2">
@@ -7816,9 +7856,9 @@
       <c r="L261" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M261" s="15"/>
-      <c r="N261" s="15"/>
-      <c r="O261" s="15"/>
+      <c r="M261" s="18"/>
+      <c r="N261" s="18"/>
+      <c r="O261" s="18"/>
     </row>
     <row r="262" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G262" s="2">
@@ -7838,9 +7878,9 @@
       <c r="L262" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M262" s="15"/>
-      <c r="N262" s="15"/>
-      <c r="O262" s="15"/>
+      <c r="M262" s="18"/>
+      <c r="N262" s="18"/>
+      <c r="O262" s="18"/>
     </row>
     <row r="263" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G263" s="2">
@@ -7860,9 +7900,9 @@
       <c r="L263" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M263" s="15"/>
-      <c r="N263" s="15"/>
-      <c r="O263" s="15"/>
+      <c r="M263" s="18"/>
+      <c r="N263" s="18"/>
+      <c r="O263" s="18"/>
     </row>
     <row r="264" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G264" s="2">
@@ -7882,9 +7922,9 @@
       <c r="L264" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M264" s="15"/>
-      <c r="N264" s="15"/>
-      <c r="O264" s="15"/>
+      <c r="M264" s="18"/>
+      <c r="N264" s="18"/>
+      <c r="O264" s="18"/>
     </row>
     <row r="265" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G265" s="2">
@@ -7904,9 +7944,9 @@
       <c r="L265" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M265" s="15"/>
-      <c r="N265" s="15"/>
-      <c r="O265" s="15"/>
+      <c r="M265" s="18"/>
+      <c r="N265" s="18"/>
+      <c r="O265" s="18"/>
     </row>
     <row r="266" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G266" s="2">
@@ -7926,9 +7966,9 @@
       <c r="L266" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M266" s="15"/>
-      <c r="N266" s="15"/>
-      <c r="O266" s="15"/>
+      <c r="M266" s="18"/>
+      <c r="N266" s="18"/>
+      <c r="O266" s="18"/>
     </row>
     <row r="267" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G267" s="2">
@@ -7948,9 +7988,9 @@
       <c r="L267" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M267" s="15"/>
-      <c r="N267" s="15"/>
-      <c r="O267" s="15"/>
+      <c r="M267" s="18"/>
+      <c r="N267" s="18"/>
+      <c r="O267" s="18"/>
     </row>
     <row r="268" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G268" s="2">
@@ -7970,9 +8010,9 @@
       <c r="L268" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M268" s="15"/>
-      <c r="N268" s="15"/>
-      <c r="O268" s="15"/>
+      <c r="M268" s="18"/>
+      <c r="N268" s="18"/>
+      <c r="O268" s="18"/>
     </row>
     <row r="269" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G269" s="2">
@@ -7992,9 +8032,9 @@
       <c r="L269" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M269" s="15"/>
-      <c r="N269" s="15"/>
-      <c r="O269" s="15"/>
+      <c r="M269" s="18"/>
+      <c r="N269" s="18"/>
+      <c r="O269" s="18"/>
     </row>
     <row r="270" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G270" s="2">
@@ -8014,9 +8054,9 @@
       <c r="L270" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M270" s="15"/>
-      <c r="N270" s="15"/>
-      <c r="O270" s="15"/>
+      <c r="M270" s="18"/>
+      <c r="N270" s="18"/>
+      <c r="O270" s="18"/>
     </row>
     <row r="271" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G271" s="2">
@@ -8036,9 +8076,9 @@
       <c r="L271" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M271" s="15"/>
-      <c r="N271" s="15"/>
-      <c r="O271" s="15"/>
+      <c r="M271" s="18"/>
+      <c r="N271" s="18"/>
+      <c r="O271" s="18"/>
     </row>
     <row r="272" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G272" s="2">
@@ -8058,9 +8098,9 @@
       <c r="L272" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M272" s="15"/>
-      <c r="N272" s="15"/>
-      <c r="O272" s="15"/>
+      <c r="M272" s="18"/>
+      <c r="N272" s="18"/>
+      <c r="O272" s="18"/>
     </row>
     <row r="273" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G273" s="2">
@@ -8080,9 +8120,9 @@
       <c r="L273" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M273" s="15"/>
-      <c r="N273" s="15"/>
-      <c r="O273" s="15"/>
+      <c r="M273" s="18"/>
+      <c r="N273" s="18"/>
+      <c r="O273" s="18"/>
     </row>
     <row r="274" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G274" s="2">
@@ -8102,9 +8142,9 @@
       <c r="L274" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M274" s="15"/>
-      <c r="N274" s="15"/>
-      <c r="O274" s="15"/>
+      <c r="M274" s="18"/>
+      <c r="N274" s="18"/>
+      <c r="O274" s="18"/>
     </row>
     <row r="275" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G275" s="2">
@@ -8124,9 +8164,9 @@
       <c r="L275" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M275" s="15"/>
-      <c r="N275" s="15"/>
-      <c r="O275" s="15"/>
+      <c r="M275" s="18"/>
+      <c r="N275" s="18"/>
+      <c r="O275" s="18"/>
     </row>
     <row r="276" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G276" s="2">
@@ -8146,9 +8186,9 @@
       <c r="L276" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M276" s="15"/>
-      <c r="N276" s="15"/>
-      <c r="O276" s="15"/>
+      <c r="M276" s="18"/>
+      <c r="N276" s="18"/>
+      <c r="O276" s="18"/>
     </row>
     <row r="277" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G277" s="2">
@@ -8168,9 +8208,9 @@
       <c r="L277" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M277" s="15"/>
-      <c r="N277" s="15"/>
-      <c r="O277" s="15"/>
+      <c r="M277" s="18"/>
+      <c r="N277" s="18"/>
+      <c r="O277" s="18"/>
     </row>
     <row r="278" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G278" s="2">
@@ -8190,9 +8230,9 @@
       <c r="L278" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M278" s="15"/>
-      <c r="N278" s="15"/>
-      <c r="O278" s="15"/>
+      <c r="M278" s="18"/>
+      <c r="N278" s="18"/>
+      <c r="O278" s="18"/>
     </row>
     <row r="279" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G279" s="2">
@@ -8212,9 +8252,9 @@
       <c r="L279" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M279" s="15"/>
-      <c r="N279" s="15"/>
-      <c r="O279" s="15"/>
+      <c r="M279" s="18"/>
+      <c r="N279" s="18"/>
+      <c r="O279" s="18"/>
     </row>
     <row r="280" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G280" s="2">
@@ -8234,9 +8274,9 @@
       <c r="L280" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M280" s="15"/>
-      <c r="N280" s="15"/>
-      <c r="O280" s="15"/>
+      <c r="M280" s="18"/>
+      <c r="N280" s="18"/>
+      <c r="O280" s="18"/>
     </row>
     <row r="281" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G281" s="2">
@@ -8256,9 +8296,9 @@
       <c r="L281" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M281" s="15"/>
-      <c r="N281" s="15"/>
-      <c r="O281" s="15"/>
+      <c r="M281" s="18"/>
+      <c r="N281" s="18"/>
+      <c r="O281" s="18"/>
     </row>
     <row r="282" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G282" s="2">
@@ -8278,9 +8318,9 @@
       <c r="L282" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M282" s="15"/>
-      <c r="N282" s="15"/>
-      <c r="O282" s="15"/>
+      <c r="M282" s="18"/>
+      <c r="N282" s="18"/>
+      <c r="O282" s="18"/>
     </row>
     <row r="283" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G283" s="2">
@@ -8300,9 +8340,9 @@
       <c r="L283" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M283" s="15"/>
-      <c r="N283" s="15"/>
-      <c r="O283" s="15"/>
+      <c r="M283" s="18"/>
+      <c r="N283" s="18"/>
+      <c r="O283" s="18"/>
     </row>
     <row r="284" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G284" s="2">
@@ -8322,9 +8362,9 @@
       <c r="L284" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M284" s="15"/>
-      <c r="N284" s="15"/>
-      <c r="O284" s="15"/>
+      <c r="M284" s="18"/>
+      <c r="N284" s="18"/>
+      <c r="O284" s="18"/>
     </row>
     <row r="285" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G285" s="2">
@@ -8344,9 +8384,9 @@
       <c r="L285" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M285" s="15"/>
-      <c r="N285" s="15"/>
-      <c r="O285" s="15"/>
+      <c r="M285" s="18"/>
+      <c r="N285" s="18"/>
+      <c r="O285" s="18"/>
     </row>
     <row r="286" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G286" s="2">
@@ -8366,9 +8406,9 @@
       <c r="L286" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M286" s="15"/>
-      <c r="N286" s="15"/>
-      <c r="O286" s="15"/>
+      <c r="M286" s="18"/>
+      <c r="N286" s="18"/>
+      <c r="O286" s="18"/>
     </row>
     <row r="287" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G287" s="2">
@@ -8388,9 +8428,9 @@
       <c r="L287" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M287" s="15"/>
-      <c r="N287" s="15"/>
-      <c r="O287" s="15"/>
+      <c r="M287" s="18"/>
+      <c r="N287" s="18"/>
+      <c r="O287" s="18"/>
     </row>
     <row r="288" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G288" s="2">
@@ -8410,9 +8450,9 @@
       <c r="L288" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M288" s="15"/>
-      <c r="N288" s="15"/>
-      <c r="O288" s="15"/>
+      <c r="M288" s="18"/>
+      <c r="N288" s="18"/>
+      <c r="O288" s="18"/>
     </row>
     <row r="289" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G289" s="2">
@@ -8432,9 +8472,9 @@
       <c r="L289" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M289" s="15"/>
-      <c r="N289" s="15"/>
-      <c r="O289" s="15"/>
+      <c r="M289" s="18"/>
+      <c r="N289" s="18"/>
+      <c r="O289" s="18"/>
     </row>
     <row r="290" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G290" s="2">
@@ -8454,9 +8494,9 @@
       <c r="L290" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M290" s="15"/>
-      <c r="N290" s="15"/>
-      <c r="O290" s="15"/>
+      <c r="M290" s="18"/>
+      <c r="N290" s="18"/>
+      <c r="O290" s="18"/>
     </row>
     <row r="291" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G291" s="2">
@@ -8476,9 +8516,9 @@
       <c r="L291" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M291" s="15"/>
-      <c r="N291" s="15"/>
-      <c r="O291" s="15"/>
+      <c r="M291" s="18"/>
+      <c r="N291" s="18"/>
+      <c r="O291" s="18"/>
     </row>
     <row r="292" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G292" s="2">
@@ -8498,9 +8538,9 @@
       <c r="L292" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M292" s="15"/>
-      <c r="N292" s="15"/>
-      <c r="O292" s="15"/>
+      <c r="M292" s="18"/>
+      <c r="N292" s="18"/>
+      <c r="O292" s="18"/>
     </row>
     <row r="293" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G293" s="2">
@@ -8520,9 +8560,9 @@
       <c r="L293" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M293" s="15"/>
-      <c r="N293" s="15"/>
-      <c r="O293" s="15"/>
+      <c r="M293" s="18"/>
+      <c r="N293" s="18"/>
+      <c r="O293" s="18"/>
     </row>
     <row r="294" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G294" s="2">
@@ -8542,9 +8582,9 @@
       <c r="L294" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M294" s="15"/>
-      <c r="N294" s="15"/>
-      <c r="O294" s="15"/>
+      <c r="M294" s="18"/>
+      <c r="N294" s="18"/>
+      <c r="O294" s="18"/>
     </row>
     <row r="295" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G295" s="2">
@@ -8564,9 +8604,9 @@
       <c r="L295" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M295" s="15"/>
-      <c r="N295" s="15"/>
-      <c r="O295" s="15"/>
+      <c r="M295" s="18"/>
+      <c r="N295" s="18"/>
+      <c r="O295" s="18"/>
     </row>
     <row r="296" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G296" s="2">
@@ -8586,9 +8626,9 @@
       <c r="L296" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M296" s="15"/>
-      <c r="N296" s="15"/>
-      <c r="O296" s="15"/>
+      <c r="M296" s="18"/>
+      <c r="N296" s="18"/>
+      <c r="O296" s="18"/>
     </row>
     <row r="297" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G297" s="2">
@@ -8608,9 +8648,9 @@
       <c r="L297" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M297" s="15"/>
-      <c r="N297" s="15"/>
-      <c r="O297" s="15"/>
+      <c r="M297" s="18"/>
+      <c r="N297" s="18"/>
+      <c r="O297" s="18"/>
     </row>
     <row r="298" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G298" s="2">
@@ -8630,9 +8670,9 @@
       <c r="L298" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M298" s="15"/>
-      <c r="N298" s="15"/>
-      <c r="O298" s="15"/>
+      <c r="M298" s="18"/>
+      <c r="N298" s="18"/>
+      <c r="O298" s="18"/>
     </row>
     <row r="299" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G299" s="2">
@@ -8652,9 +8692,9 @@
       <c r="L299" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M299" s="15"/>
-      <c r="N299" s="15"/>
-      <c r="O299" s="15"/>
+      <c r="M299" s="18"/>
+      <c r="N299" s="18"/>
+      <c r="O299" s="18"/>
     </row>
     <row r="300" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G300" s="2">
@@ -8674,9 +8714,9 @@
       <c r="L300" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M300" s="15"/>
-      <c r="N300" s="15"/>
-      <c r="O300" s="15"/>
+      <c r="M300" s="18"/>
+      <c r="N300" s="18"/>
+      <c r="O300" s="18"/>
     </row>
     <row r="301" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G301" s="2">
@@ -8696,9 +8736,9 @@
       <c r="L301" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M301" s="15"/>
-      <c r="N301" s="15"/>
-      <c r="O301" s="15"/>
+      <c r="M301" s="18"/>
+      <c r="N301" s="18"/>
+      <c r="O301" s="18"/>
     </row>
     <row r="302" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G302" s="2">
@@ -8718,9 +8758,9 @@
       <c r="L302" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M302" s="15"/>
-      <c r="N302" s="15"/>
-      <c r="O302" s="15"/>
+      <c r="M302" s="18"/>
+      <c r="N302" s="18"/>
+      <c r="O302" s="18"/>
     </row>
     <row r="303" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G303" s="2">
@@ -8740,9 +8780,9 @@
       <c r="L303" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M303" s="15"/>
-      <c r="N303" s="15"/>
-      <c r="O303" s="15"/>
+      <c r="M303" s="18"/>
+      <c r="N303" s="18"/>
+      <c r="O303" s="18"/>
     </row>
     <row r="304" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G304" s="2">
@@ -8762,9 +8802,9 @@
       <c r="L304" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M304" s="15"/>
-      <c r="N304" s="15"/>
-      <c r="O304" s="15"/>
+      <c r="M304" s="18"/>
+      <c r="N304" s="18"/>
+      <c r="O304" s="18"/>
     </row>
     <row r="305" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G305" s="2">
@@ -8784,9 +8824,9 @@
       <c r="L305" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M305" s="15"/>
-      <c r="N305" s="15"/>
-      <c r="O305" s="15"/>
+      <c r="M305" s="18"/>
+      <c r="N305" s="18"/>
+      <c r="O305" s="18"/>
     </row>
     <row r="306" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G306" s="2">
@@ -8806,9 +8846,9 @@
       <c r="L306" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M306" s="15"/>
-      <c r="N306" s="15"/>
-      <c r="O306" s="15"/>
+      <c r="M306" s="18"/>
+      <c r="N306" s="18"/>
+      <c r="O306" s="18"/>
     </row>
     <row r="307" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G307" s="2">
@@ -8828,9 +8868,9 @@
       <c r="L307" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M307" s="15"/>
-      <c r="N307" s="15"/>
-      <c r="O307" s="15"/>
+      <c r="M307" s="18"/>
+      <c r="N307" s="18"/>
+      <c r="O307" s="18"/>
     </row>
     <row r="308" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G308" s="2">
@@ -8850,9 +8890,9 @@
       <c r="L308" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M308" s="15"/>
-      <c r="N308" s="15"/>
-      <c r="O308" s="15"/>
+      <c r="M308" s="18"/>
+      <c r="N308" s="18"/>
+      <c r="O308" s="18"/>
     </row>
     <row r="309" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G309" s="2">
@@ -8872,9 +8912,9 @@
       <c r="L309" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M309" s="15"/>
-      <c r="N309" s="15"/>
-      <c r="O309" s="15"/>
+      <c r="M309" s="18"/>
+      <c r="N309" s="18"/>
+      <c r="O309" s="18"/>
     </row>
     <row r="310" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G310" s="2">
@@ -8894,9 +8934,9 @@
       <c r="L310" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M310" s="15"/>
-      <c r="N310" s="15"/>
-      <c r="O310" s="15"/>
+      <c r="M310" s="18"/>
+      <c r="N310" s="18"/>
+      <c r="O310" s="18"/>
     </row>
     <row r="311" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G311" s="2">
@@ -8916,9 +8956,9 @@
       <c r="L311" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M311" s="15"/>
-      <c r="N311" s="15"/>
-      <c r="O311" s="15"/>
+      <c r="M311" s="18"/>
+      <c r="N311" s="18"/>
+      <c r="O311" s="18"/>
     </row>
     <row r="312" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G312" s="2">
@@ -8938,9 +8978,9 @@
       <c r="L312" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M312" s="15"/>
-      <c r="N312" s="15"/>
-      <c r="O312" s="15"/>
+      <c r="M312" s="18"/>
+      <c r="N312" s="18"/>
+      <c r="O312" s="18"/>
     </row>
     <row r="313" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G313" s="2">
@@ -8960,9 +9000,9 @@
       <c r="L313" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M313" s="15"/>
-      <c r="N313" s="15"/>
-      <c r="O313" s="15"/>
+      <c r="M313" s="18"/>
+      <c r="N313" s="18"/>
+      <c r="O313" s="18"/>
     </row>
     <row r="314" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G314" s="2">
@@ -8982,9 +9022,9 @@
       <c r="L314" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M314" s="15"/>
-      <c r="N314" s="15"/>
-      <c r="O314" s="15"/>
+      <c r="M314" s="18"/>
+      <c r="N314" s="18"/>
+      <c r="O314" s="18"/>
     </row>
     <row r="315" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G315" s="2">
@@ -9004,9 +9044,9 @@
       <c r="L315" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M315" s="15"/>
-      <c r="N315" s="15"/>
-      <c r="O315" s="15"/>
+      <c r="M315" s="18"/>
+      <c r="N315" s="18"/>
+      <c r="O315" s="18"/>
     </row>
     <row r="316" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G316" s="2">
@@ -9026,9 +9066,9 @@
       <c r="L316" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M316" s="15"/>
-      <c r="N316" s="15"/>
-      <c r="O316" s="15"/>
+      <c r="M316" s="18"/>
+      <c r="N316" s="18"/>
+      <c r="O316" s="18"/>
     </row>
     <row r="317" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G317" s="2">
@@ -9048,9 +9088,9 @@
       <c r="L317" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M317" s="15"/>
-      <c r="N317" s="15"/>
-      <c r="O317" s="15"/>
+      <c r="M317" s="18"/>
+      <c r="N317" s="18"/>
+      <c r="O317" s="18"/>
     </row>
     <row r="318" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G318" s="2">
@@ -9070,9 +9110,9 @@
       <c r="L318" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M318" s="15"/>
-      <c r="N318" s="15"/>
-      <c r="O318" s="15"/>
+      <c r="M318" s="18"/>
+      <c r="N318" s="18"/>
+      <c r="O318" s="18"/>
     </row>
     <row r="319" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G319" s="2">
@@ -9092,9 +9132,9 @@
       <c r="L319" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M319" s="15"/>
-      <c r="N319" s="15"/>
-      <c r="O319" s="15"/>
+      <c r="M319" s="18"/>
+      <c r="N319" s="18"/>
+      <c r="O319" s="18"/>
     </row>
     <row r="320" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G320" s="2">
@@ -9114,9 +9154,9 @@
       <c r="L320" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M320" s="15"/>
-      <c r="N320" s="15"/>
-      <c r="O320" s="15"/>
+      <c r="M320" s="18"/>
+      <c r="N320" s="18"/>
+      <c r="O320" s="18"/>
     </row>
     <row r="321" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G321" s="2">
@@ -9136,9 +9176,9 @@
       <c r="L321" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M321" s="15"/>
-      <c r="N321" s="15"/>
-      <c r="O321" s="15"/>
+      <c r="M321" s="18"/>
+      <c r="N321" s="18"/>
+      <c r="O321" s="18"/>
     </row>
     <row r="322" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G322" s="2">
@@ -9158,9 +9198,9 @@
       <c r="L322" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M322" s="15"/>
-      <c r="N322" s="15"/>
-      <c r="O322" s="15"/>
+      <c r="M322" s="18"/>
+      <c r="N322" s="18"/>
+      <c r="O322" s="18"/>
     </row>
     <row r="323" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G323" s="2">
@@ -9180,9 +9220,9 @@
       <c r="L323" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M323" s="15"/>
-      <c r="N323" s="15"/>
-      <c r="O323" s="15"/>
+      <c r="M323" s="18"/>
+      <c r="N323" s="18"/>
+      <c r="O323" s="18"/>
     </row>
     <row r="324" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G324" s="2">
@@ -9202,9 +9242,9 @@
       <c r="L324" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M324" s="15"/>
-      <c r="N324" s="15"/>
-      <c r="O324" s="15"/>
+      <c r="M324" s="18"/>
+      <c r="N324" s="18"/>
+      <c r="O324" s="18"/>
     </row>
     <row r="325" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G325" s="2">
@@ -9224,9 +9264,9 @@
       <c r="L325" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M325" s="15"/>
-      <c r="N325" s="15"/>
-      <c r="O325" s="15"/>
+      <c r="M325" s="18"/>
+      <c r="N325" s="18"/>
+      <c r="O325" s="18"/>
     </row>
     <row r="326" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G326" s="2">
@@ -9246,9 +9286,9 @@
       <c r="L326" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M326" s="15"/>
-      <c r="N326" s="15"/>
-      <c r="O326" s="15"/>
+      <c r="M326" s="18"/>
+      <c r="N326" s="18"/>
+      <c r="O326" s="18"/>
     </row>
     <row r="327" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G327" s="2">
@@ -9268,9 +9308,9 @@
       <c r="L327" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M327" s="15"/>
-      <c r="N327" s="15"/>
-      <c r="O327" s="15"/>
+      <c r="M327" s="18"/>
+      <c r="N327" s="18"/>
+      <c r="O327" s="18"/>
     </row>
     <row r="328" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G328" s="2">
@@ -9290,9 +9330,9 @@
       <c r="L328" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M328" s="15"/>
-      <c r="N328" s="15"/>
-      <c r="O328" s="15"/>
+      <c r="M328" s="18"/>
+      <c r="N328" s="18"/>
+      <c r="O328" s="18"/>
     </row>
     <row r="329" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G329" s="2">
@@ -9312,9 +9352,9 @@
       <c r="L329" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M329" s="15"/>
-      <c r="N329" s="15"/>
-      <c r="O329" s="15"/>
+      <c r="M329" s="18"/>
+      <c r="N329" s="18"/>
+      <c r="O329" s="18"/>
     </row>
     <row r="330" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G330" s="2">
@@ -9334,9 +9374,9 @@
       <c r="L330" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M330" s="15"/>
-      <c r="N330" s="15"/>
-      <c r="O330" s="15"/>
+      <c r="M330" s="18"/>
+      <c r="N330" s="18"/>
+      <c r="O330" s="18"/>
     </row>
     <row r="331" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G331" s="2">
@@ -9356,9 +9396,9 @@
       <c r="L331" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M331" s="15"/>
-      <c r="N331" s="15"/>
-      <c r="O331" s="15"/>
+      <c r="M331" s="18"/>
+      <c r="N331" s="18"/>
+      <c r="O331" s="18"/>
     </row>
     <row r="332" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G332" s="2">
@@ -9378,9 +9418,9 @@
       <c r="L332" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M332" s="15"/>
-      <c r="N332" s="15"/>
-      <c r="O332" s="15"/>
+      <c r="M332" s="18"/>
+      <c r="N332" s="18"/>
+      <c r="O332" s="18"/>
     </row>
     <row r="333" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G333" s="2">
@@ -9400,9 +9440,9 @@
       <c r="L333" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M333" s="15"/>
-      <c r="N333" s="15"/>
-      <c r="O333" s="15"/>
+      <c r="M333" s="18"/>
+      <c r="N333" s="18"/>
+      <c r="O333" s="18"/>
     </row>
     <row r="334" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G334" s="2">
@@ -9422,9 +9462,9 @@
       <c r="L334" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M334" s="15"/>
-      <c r="N334" s="15"/>
-      <c r="O334" s="15"/>
+      <c r="M334" s="18"/>
+      <c r="N334" s="18"/>
+      <c r="O334" s="18"/>
     </row>
     <row r="335" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G335" s="2">
@@ -9444,9 +9484,9 @@
       <c r="L335" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M335" s="15"/>
-      <c r="N335" s="15"/>
-      <c r="O335" s="15"/>
+      <c r="M335" s="18"/>
+      <c r="N335" s="18"/>
+      <c r="O335" s="18"/>
     </row>
     <row r="336" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G336" s="2">
@@ -9466,9 +9506,9 @@
       <c r="L336" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M336" s="15"/>
-      <c r="N336" s="15"/>
-      <c r="O336" s="15"/>
+      <c r="M336" s="18"/>
+      <c r="N336" s="18"/>
+      <c r="O336" s="18"/>
     </row>
     <row r="337" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G337" s="2">
@@ -9488,9 +9528,9 @@
       <c r="L337" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M337" s="15"/>
-      <c r="N337" s="15"/>
-      <c r="O337" s="15"/>
+      <c r="M337" s="18"/>
+      <c r="N337" s="18"/>
+      <c r="O337" s="18"/>
     </row>
     <row r="338" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G338" s="2">
@@ -9510,9 +9550,9 @@
       <c r="L338" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M338" s="15"/>
-      <c r="N338" s="15"/>
-      <c r="O338" s="15"/>
+      <c r="M338" s="18"/>
+      <c r="N338" s="18"/>
+      <c r="O338" s="18"/>
     </row>
     <row r="339" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G339" s="2">
@@ -9532,9 +9572,9 @@
       <c r="L339" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M339" s="15"/>
-      <c r="N339" s="15"/>
-      <c r="O339" s="15"/>
+      <c r="M339" s="18"/>
+      <c r="N339" s="18"/>
+      <c r="O339" s="18"/>
     </row>
     <row r="340" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G340" s="2">
@@ -9554,9 +9594,9 @@
       <c r="L340" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M340" s="15"/>
-      <c r="N340" s="15"/>
-      <c r="O340" s="15"/>
+      <c r="M340" s="18"/>
+      <c r="N340" s="18"/>
+      <c r="O340" s="18"/>
     </row>
     <row r="341" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G341" s="2">
@@ -9576,9 +9616,9 @@
       <c r="L341" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M341" s="15"/>
-      <c r="N341" s="15"/>
-      <c r="O341" s="15"/>
+      <c r="M341" s="18"/>
+      <c r="N341" s="18"/>
+      <c r="O341" s="18"/>
     </row>
     <row r="342" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G342" s="2">
@@ -9598,9 +9638,9 @@
       <c r="L342" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M342" s="15"/>
-      <c r="N342" s="15"/>
-      <c r="O342" s="15"/>
+      <c r="M342" s="18"/>
+      <c r="N342" s="18"/>
+      <c r="O342" s="18"/>
     </row>
     <row r="343" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G343" s="2">
@@ -9620,9 +9660,9 @@
       <c r="L343" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M343" s="15"/>
-      <c r="N343" s="15"/>
-      <c r="O343" s="15"/>
+      <c r="M343" s="18"/>
+      <c r="N343" s="18"/>
+      <c r="O343" s="18"/>
     </row>
     <row r="344" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G344" s="2">
@@ -9642,9 +9682,9 @@
       <c r="L344" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M344" s="15"/>
-      <c r="N344" s="15"/>
-      <c r="O344" s="15"/>
+      <c r="M344" s="18"/>
+      <c r="N344" s="18"/>
+      <c r="O344" s="18"/>
     </row>
     <row r="345" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G345" s="12">
@@ -9664,9 +9704,9 @@
       <c r="L345" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M345" s="15"/>
-      <c r="N345" s="15"/>
-      <c r="O345" s="15"/>
+      <c r="M345" s="18"/>
+      <c r="N345" s="18"/>
+      <c r="O345" s="18"/>
     </row>
     <row r="346" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G346" s="2">
@@ -9686,9 +9726,9 @@
       <c r="L346" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M346" s="21"/>
-      <c r="N346" s="22"/>
-      <c r="O346" s="23"/>
+      <c r="M346" s="15"/>
+      <c r="N346" s="16"/>
+      <c r="O346" s="17"/>
     </row>
     <row r="347" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G347" s="2">
@@ -9708,9 +9748,9 @@
       <c r="L347" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M347" s="21"/>
-      <c r="N347" s="22"/>
-      <c r="O347" s="23"/>
+      <c r="M347" s="15"/>
+      <c r="N347" s="16"/>
+      <c r="O347" s="17"/>
     </row>
     <row r="348" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G348" s="2">
@@ -9730,9 +9770,9 @@
       <c r="L348" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M348" s="21"/>
-      <c r="N348" s="22"/>
-      <c r="O348" s="23"/>
+      <c r="M348" s="15"/>
+      <c r="N348" s="16"/>
+      <c r="O348" s="17"/>
     </row>
     <row r="349" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G349" s="2">
@@ -9752,9 +9792,9 @@
       <c r="L349" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M349" s="21"/>
-      <c r="N349" s="22"/>
-      <c r="O349" s="23"/>
+      <c r="M349" s="15"/>
+      <c r="N349" s="16"/>
+      <c r="O349" s="17"/>
     </row>
     <row r="350" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G350" s="2">
@@ -9774,9 +9814,9 @@
       <c r="L350" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M350" s="21"/>
-      <c r="N350" s="22"/>
-      <c r="O350" s="23"/>
+      <c r="M350" s="15"/>
+      <c r="N350" s="16"/>
+      <c r="O350" s="17"/>
     </row>
     <row r="351" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G351" s="2">
@@ -9796,9 +9836,9 @@
       <c r="L351" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M351" s="21"/>
-      <c r="N351" s="22"/>
-      <c r="O351" s="23"/>
+      <c r="M351" s="15"/>
+      <c r="N351" s="16"/>
+      <c r="O351" s="17"/>
     </row>
     <row r="352" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G352" s="2">
@@ -9818,9 +9858,9 @@
       <c r="L352" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M352" s="21"/>
-      <c r="N352" s="22"/>
-      <c r="O352" s="23"/>
+      <c r="M352" s="15"/>
+      <c r="N352" s="16"/>
+      <c r="O352" s="17"/>
     </row>
     <row r="353" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G353" s="2">
@@ -9840,9 +9880,9 @@
       <c r="L353" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M353" s="21"/>
-      <c r="N353" s="22"/>
-      <c r="O353" s="23"/>
+      <c r="M353" s="15"/>
+      <c r="N353" s="16"/>
+      <c r="O353" s="17"/>
     </row>
     <row r="354" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G354" s="2">
@@ -9862,9 +9902,9 @@
       <c r="L354" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M354" s="21"/>
-      <c r="N354" s="22"/>
-      <c r="O354" s="23"/>
+      <c r="M354" s="15"/>
+      <c r="N354" s="16"/>
+      <c r="O354" s="17"/>
     </row>
     <row r="355" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G355" s="2">
@@ -9884,9 +9924,9 @@
       <c r="L355" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M355" s="21"/>
-      <c r="N355" s="22"/>
-      <c r="O355" s="23"/>
+      <c r="M355" s="15"/>
+      <c r="N355" s="16"/>
+      <c r="O355" s="17"/>
     </row>
     <row r="356" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G356" s="2">
@@ -9906,9 +9946,9 @@
       <c r="L356" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M356" s="21"/>
-      <c r="N356" s="22"/>
-      <c r="O356" s="23"/>
+      <c r="M356" s="15"/>
+      <c r="N356" s="16"/>
+      <c r="O356" s="17"/>
     </row>
     <row r="357" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G357" s="2">
@@ -9928,9 +9968,9 @@
       <c r="L357" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M357" s="21"/>
-      <c r="N357" s="22"/>
-      <c r="O357" s="23"/>
+      <c r="M357" s="15"/>
+      <c r="N357" s="16"/>
+      <c r="O357" s="17"/>
     </row>
     <row r="358" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G358" s="2">
@@ -9950,9 +9990,9 @@
       <c r="L358" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M358" s="21"/>
-      <c r="N358" s="22"/>
-      <c r="O358" s="23"/>
+      <c r="M358" s="15"/>
+      <c r="N358" s="16"/>
+      <c r="O358" s="17"/>
     </row>
     <row r="359" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G359" s="2">
@@ -9972,9 +10012,9 @@
       <c r="L359" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M359" s="21"/>
-      <c r="N359" s="22"/>
-      <c r="O359" s="23"/>
+      <c r="M359" s="15"/>
+      <c r="N359" s="16"/>
+      <c r="O359" s="17"/>
     </row>
     <row r="360" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G360" s="2">
@@ -9994,9 +10034,9 @@
       <c r="L360" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M360" s="21"/>
-      <c r="N360" s="22"/>
-      <c r="O360" s="23"/>
+      <c r="M360" s="15"/>
+      <c r="N360" s="16"/>
+      <c r="O360" s="17"/>
     </row>
     <row r="361" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G361" s="2">
@@ -10016,9 +10056,9 @@
       <c r="L361" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M361" s="21"/>
-      <c r="N361" s="22"/>
-      <c r="O361" s="23"/>
+      <c r="M361" s="15"/>
+      <c r="N361" s="16"/>
+      <c r="O361" s="17"/>
     </row>
     <row r="362" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G362" s="2">
@@ -10038,9 +10078,9 @@
       <c r="L362" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M362" s="21"/>
-      <c r="N362" s="22"/>
-      <c r="O362" s="23"/>
+      <c r="M362" s="15"/>
+      <c r="N362" s="16"/>
+      <c r="O362" s="17"/>
     </row>
     <row r="363" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G363" s="2">
@@ -10060,9 +10100,9 @@
       <c r="L363" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M363" s="21"/>
-      <c r="N363" s="22"/>
-      <c r="O363" s="23"/>
+      <c r="M363" s="15"/>
+      <c r="N363" s="16"/>
+      <c r="O363" s="17"/>
     </row>
     <row r="364" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G364" s="2">
@@ -10082,9 +10122,9 @@
       <c r="L364" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M364" s="21"/>
-      <c r="N364" s="22"/>
-      <c r="O364" s="23"/>
+      <c r="M364" s="15"/>
+      <c r="N364" s="16"/>
+      <c r="O364" s="17"/>
     </row>
     <row r="365" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G365" s="2">
@@ -10104,9 +10144,9 @@
       <c r="L365" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M365" s="21"/>
-      <c r="N365" s="22"/>
-      <c r="O365" s="23"/>
+      <c r="M365" s="15"/>
+      <c r="N365" s="16"/>
+      <c r="O365" s="17"/>
     </row>
     <row r="366" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G366" s="2">
@@ -10126,9 +10166,9 @@
       <c r="L366" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M366" s="21"/>
-      <c r="N366" s="22"/>
-      <c r="O366" s="23"/>
+      <c r="M366" s="15"/>
+      <c r="N366" s="16"/>
+      <c r="O366" s="17"/>
     </row>
     <row r="367" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G367" s="2">
@@ -10148,9 +10188,9 @@
       <c r="L367" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M367" s="21"/>
-      <c r="N367" s="22"/>
-      <c r="O367" s="23"/>
+      <c r="M367" s="15"/>
+      <c r="N367" s="16"/>
+      <c r="O367" s="17"/>
     </row>
     <row r="368" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G368" s="2">
@@ -10170,9 +10210,9 @@
       <c r="L368" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M368" s="21"/>
-      <c r="N368" s="22"/>
-      <c r="O368" s="23"/>
+      <c r="M368" s="15"/>
+      <c r="N368" s="16"/>
+      <c r="O368" s="17"/>
     </row>
     <row r="369" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G369" s="2">
@@ -10192,9 +10232,9 @@
       <c r="L369" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M369" s="21"/>
-      <c r="N369" s="22"/>
-      <c r="O369" s="23"/>
+      <c r="M369" s="15"/>
+      <c r="N369" s="16"/>
+      <c r="O369" s="17"/>
     </row>
     <row r="370" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G370" s="2">
@@ -10214,9 +10254,9 @@
       <c r="L370" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M370" s="21"/>
-      <c r="N370" s="22"/>
-      <c r="O370" s="23"/>
+      <c r="M370" s="15"/>
+      <c r="N370" s="16"/>
+      <c r="O370" s="17"/>
     </row>
     <row r="371" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G371" s="2">
@@ -10236,9 +10276,9 @@
       <c r="L371" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M371" s="21"/>
-      <c r="N371" s="22"/>
-      <c r="O371" s="23"/>
+      <c r="M371" s="15"/>
+      <c r="N371" s="16"/>
+      <c r="O371" s="17"/>
     </row>
     <row r="372" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G372" s="2">
@@ -10258,9 +10298,9 @@
       <c r="L372" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M372" s="21"/>
-      <c r="N372" s="22"/>
-      <c r="O372" s="23"/>
+      <c r="M372" s="15"/>
+      <c r="N372" s="16"/>
+      <c r="O372" s="17"/>
     </row>
     <row r="373" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G373" s="2">
@@ -10280,9 +10320,9 @@
       <c r="L373" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M373" s="21"/>
-      <c r="N373" s="22"/>
-      <c r="O373" s="23"/>
+      <c r="M373" s="15"/>
+      <c r="N373" s="16"/>
+      <c r="O373" s="17"/>
     </row>
     <row r="374" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G374" s="2">
@@ -10302,9 +10342,9 @@
       <c r="L374" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M374" s="21"/>
-      <c r="N374" s="22"/>
-      <c r="O374" s="23"/>
+      <c r="M374" s="15"/>
+      <c r="N374" s="16"/>
+      <c r="O374" s="17"/>
     </row>
     <row r="375" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G375" s="2">
@@ -10324,9 +10364,9 @@
       <c r="L375" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M375" s="21"/>
-      <c r="N375" s="22"/>
-      <c r="O375" s="23"/>
+      <c r="M375" s="15"/>
+      <c r="N375" s="16"/>
+      <c r="O375" s="17"/>
     </row>
     <row r="376" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G376" s="2">
@@ -10346,9 +10386,9 @@
       <c r="L376" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M376" s="21"/>
-      <c r="N376" s="22"/>
-      <c r="O376" s="23"/>
+      <c r="M376" s="15"/>
+      <c r="N376" s="16"/>
+      <c r="O376" s="17"/>
     </row>
     <row r="377" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G377" s="2">
@@ -10368,9 +10408,9 @@
       <c r="L377" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M377" s="21"/>
-      <c r="N377" s="22"/>
-      <c r="O377" s="23"/>
+      <c r="M377" s="15"/>
+      <c r="N377" s="16"/>
+      <c r="O377" s="17"/>
     </row>
     <row r="378" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G378" s="2">
@@ -10390,9 +10430,9 @@
       <c r="L378" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M378" s="21"/>
-      <c r="N378" s="22"/>
-      <c r="O378" s="23"/>
+      <c r="M378" s="15"/>
+      <c r="N378" s="16"/>
+      <c r="O378" s="17"/>
     </row>
     <row r="379" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G379" s="2">
@@ -10412,9 +10452,9 @@
       <c r="L379" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M379" s="21"/>
-      <c r="N379" s="22"/>
-      <c r="O379" s="23"/>
+      <c r="M379" s="15"/>
+      <c r="N379" s="16"/>
+      <c r="O379" s="17"/>
     </row>
     <row r="380" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G380" s="2">
@@ -10434,9 +10474,9 @@
       <c r="L380" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M380" s="21"/>
-      <c r="N380" s="22"/>
-      <c r="O380" s="23"/>
+      <c r="M380" s="15"/>
+      <c r="N380" s="16"/>
+      <c r="O380" s="17"/>
     </row>
     <row r="381" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G381" s="2">
@@ -10456,9 +10496,9 @@
       <c r="L381" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M381" s="21"/>
-      <c r="N381" s="22"/>
-      <c r="O381" s="23"/>
+      <c r="M381" s="15"/>
+      <c r="N381" s="16"/>
+      <c r="O381" s="17"/>
     </row>
     <row r="382" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G382" s="2">
@@ -10478,9 +10518,9 @@
       <c r="L382" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M382" s="21"/>
-      <c r="N382" s="22"/>
-      <c r="O382" s="23"/>
+      <c r="M382" s="15"/>
+      <c r="N382" s="16"/>
+      <c r="O382" s="17"/>
     </row>
     <row r="383" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G383" s="2">
@@ -10500,9 +10540,9 @@
       <c r="L383" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M383" s="21"/>
-      <c r="N383" s="22"/>
-      <c r="O383" s="23"/>
+      <c r="M383" s="15"/>
+      <c r="N383" s="16"/>
+      <c r="O383" s="17"/>
     </row>
     <row r="384" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G384" s="2">
@@ -10522,9 +10562,9 @@
       <c r="L384" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M384" s="21"/>
-      <c r="N384" s="22"/>
-      <c r="O384" s="23"/>
+      <c r="M384" s="15"/>
+      <c r="N384" s="16"/>
+      <c r="O384" s="17"/>
     </row>
     <row r="385" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G385" s="2">
@@ -10544,9 +10584,9 @@
       <c r="L385" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M385" s="21"/>
-      <c r="N385" s="22"/>
-      <c r="O385" s="23"/>
+      <c r="M385" s="15"/>
+      <c r="N385" s="16"/>
+      <c r="O385" s="17"/>
     </row>
     <row r="386" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G386" s="2">
@@ -10566,9 +10606,9 @@
       <c r="L386" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M386" s="21"/>
-      <c r="N386" s="22"/>
-      <c r="O386" s="23"/>
+      <c r="M386" s="15"/>
+      <c r="N386" s="16"/>
+      <c r="O386" s="17"/>
     </row>
     <row r="387" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G387" s="2">
@@ -10588,9 +10628,9 @@
       <c r="L387" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M387" s="21"/>
-      <c r="N387" s="22"/>
-      <c r="O387" s="23"/>
+      <c r="M387" s="15"/>
+      <c r="N387" s="16"/>
+      <c r="O387" s="17"/>
     </row>
     <row r="388" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G388" s="2">
@@ -10610,9 +10650,9 @@
       <c r="L388" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M388" s="21"/>
-      <c r="N388" s="22"/>
-      <c r="O388" s="23"/>
+      <c r="M388" s="15"/>
+      <c r="N388" s="16"/>
+      <c r="O388" s="17"/>
     </row>
     <row r="389" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G389" s="2">
@@ -10632,9 +10672,9 @@
       <c r="L389" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M389" s="21"/>
-      <c r="N389" s="22"/>
-      <c r="O389" s="23"/>
+      <c r="M389" s="15"/>
+      <c r="N389" s="16"/>
+      <c r="O389" s="17"/>
     </row>
     <row r="390" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G390" s="2">
@@ -10654,9 +10694,9 @@
       <c r="L390" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M390" s="21"/>
-      <c r="N390" s="22"/>
-      <c r="O390" s="23"/>
+      <c r="M390" s="15"/>
+      <c r="N390" s="16"/>
+      <c r="O390" s="17"/>
     </row>
     <row r="391" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G391" s="2">
@@ -10676,9 +10716,9 @@
       <c r="L391" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M391" s="21"/>
-      <c r="N391" s="22"/>
-      <c r="O391" s="23"/>
+      <c r="M391" s="15"/>
+      <c r="N391" s="16"/>
+      <c r="O391" s="17"/>
     </row>
     <row r="392" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G392" s="2">
@@ -10698,9 +10738,9 @@
       <c r="L392" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M392" s="21"/>
-      <c r="N392" s="22"/>
-      <c r="O392" s="23"/>
+      <c r="M392" s="15"/>
+      <c r="N392" s="16"/>
+      <c r="O392" s="17"/>
     </row>
     <row r="393" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G393" s="2">
@@ -10720,9 +10760,9 @@
       <c r="L393" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M393" s="21"/>
-      <c r="N393" s="22"/>
-      <c r="O393" s="23"/>
+      <c r="M393" s="15"/>
+      <c r="N393" s="16"/>
+      <c r="O393" s="17"/>
     </row>
     <row r="394" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G394" s="2">
@@ -10742,9 +10782,9 @@
       <c r="L394" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M394" s="21"/>
-      <c r="N394" s="22"/>
-      <c r="O394" s="23"/>
+      <c r="M394" s="15"/>
+      <c r="N394" s="16"/>
+      <c r="O394" s="17"/>
     </row>
     <row r="395" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G395" s="2">
@@ -10764,9 +10804,9 @@
       <c r="L395" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M395" s="21"/>
-      <c r="N395" s="22"/>
-      <c r="O395" s="23"/>
+      <c r="M395" s="15"/>
+      <c r="N395" s="16"/>
+      <c r="O395" s="17"/>
     </row>
     <row r="396" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G396" s="2">
@@ -10786,9 +10826,9 @@
       <c r="L396" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M396" s="21"/>
-      <c r="N396" s="22"/>
-      <c r="O396" s="23"/>
+      <c r="M396" s="15"/>
+      <c r="N396" s="16"/>
+      <c r="O396" s="17"/>
     </row>
     <row r="397" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G397" s="2">
@@ -10808,9 +10848,9 @@
       <c r="L397" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M397" s="21"/>
-      <c r="N397" s="22"/>
-      <c r="O397" s="23"/>
+      <c r="M397" s="15"/>
+      <c r="N397" s="16"/>
+      <c r="O397" s="17"/>
     </row>
     <row r="398" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G398" s="2">
@@ -10830,9 +10870,9 @@
       <c r="L398" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M398" s="21"/>
-      <c r="N398" s="22"/>
-      <c r="O398" s="23"/>
+      <c r="M398" s="15"/>
+      <c r="N398" s="16"/>
+      <c r="O398" s="17"/>
     </row>
     <row r="399" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G399" s="2">
@@ -10852,9 +10892,9 @@
       <c r="L399" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M399" s="21"/>
-      <c r="N399" s="22"/>
-      <c r="O399" s="23"/>
+      <c r="M399" s="15"/>
+      <c r="N399" s="16"/>
+      <c r="O399" s="17"/>
     </row>
     <row r="400" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G400" s="2">
@@ -10874,9 +10914,9 @@
       <c r="L400" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M400" s="21"/>
-      <c r="N400" s="22"/>
-      <c r="O400" s="23"/>
+      <c r="M400" s="15"/>
+      <c r="N400" s="16"/>
+      <c r="O400" s="17"/>
     </row>
     <row r="401" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G401" s="2">
@@ -10896,9 +10936,9 @@
       <c r="L401" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M401" s="21"/>
-      <c r="N401" s="22"/>
-      <c r="O401" s="23"/>
+      <c r="M401" s="15"/>
+      <c r="N401" s="16"/>
+      <c r="O401" s="17"/>
     </row>
     <row r="402" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G402" s="2">
@@ -10918,9 +10958,9 @@
       <c r="L402" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M402" s="21"/>
-      <c r="N402" s="22"/>
-      <c r="O402" s="23"/>
+      <c r="M402" s="15"/>
+      <c r="N402" s="16"/>
+      <c r="O402" s="17"/>
     </row>
     <row r="403" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G403" s="2">
@@ -10940,9 +10980,9 @@
       <c r="L403" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M403" s="21"/>
-      <c r="N403" s="22"/>
-      <c r="O403" s="23"/>
+      <c r="M403" s="15"/>
+      <c r="N403" s="16"/>
+      <c r="O403" s="17"/>
     </row>
     <row r="404" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G404" s="2">
@@ -10962,9 +11002,9 @@
       <c r="L404" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M404" s="21"/>
-      <c r="N404" s="22"/>
-      <c r="O404" s="23"/>
+      <c r="M404" s="15"/>
+      <c r="N404" s="16"/>
+      <c r="O404" s="17"/>
     </row>
     <row r="405" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G405" s="2">
@@ -10984,9 +11024,9 @@
       <c r="L405" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M405" s="21"/>
-      <c r="N405" s="22"/>
-      <c r="O405" s="23"/>
+      <c r="M405" s="15"/>
+      <c r="N405" s="16"/>
+      <c r="O405" s="17"/>
     </row>
     <row r="406" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G406" s="2">
@@ -11006,9 +11046,9 @@
       <c r="L406" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M406" s="21"/>
-      <c r="N406" s="22"/>
-      <c r="O406" s="23"/>
+      <c r="M406" s="15"/>
+      <c r="N406" s="16"/>
+      <c r="O406" s="17"/>
     </row>
     <row r="407" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G407" s="2">
@@ -11028,9 +11068,9 @@
       <c r="L407" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M407" s="21"/>
-      <c r="N407" s="22"/>
-      <c r="O407" s="23"/>
+      <c r="M407" s="15"/>
+      <c r="N407" s="16"/>
+      <c r="O407" s="17"/>
     </row>
     <row r="408" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G408" s="2">
@@ -11050,9 +11090,9 @@
       <c r="L408" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M408" s="21"/>
-      <c r="N408" s="22"/>
-      <c r="O408" s="23"/>
+      <c r="M408" s="15"/>
+      <c r="N408" s="16"/>
+      <c r="O408" s="17"/>
     </row>
     <row r="409" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G409" s="2"/>
@@ -11061,9 +11101,9 @@
       <c r="J409" s="2"/>
       <c r="K409" s="2"/>
       <c r="L409" s="2"/>
-      <c r="M409" s="21"/>
-      <c r="N409" s="22"/>
-      <c r="O409" s="23"/>
+      <c r="M409" s="15"/>
+      <c r="N409" s="16"/>
+      <c r="O409" s="17"/>
     </row>
     <row r="410" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G410" s="2"/>
@@ -11072,9 +11112,9 @@
       <c r="J410" s="2"/>
       <c r="K410" s="2"/>
       <c r="L410" s="2"/>
-      <c r="M410" s="21"/>
-      <c r="N410" s="22"/>
-      <c r="O410" s="23"/>
+      <c r="M410" s="15"/>
+      <c r="N410" s="16"/>
+      <c r="O410" s="17"/>
     </row>
     <row r="411" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G411" s="2"/>
@@ -11083,9 +11123,9 @@
       <c r="J411" s="2"/>
       <c r="K411" s="2"/>
       <c r="L411" s="2"/>
-      <c r="M411" s="21"/>
-      <c r="N411" s="22"/>
-      <c r="O411" s="23"/>
+      <c r="M411" s="15"/>
+      <c r="N411" s="16"/>
+      <c r="O411" s="17"/>
     </row>
     <row r="412" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G412" s="2"/>
@@ -11094,9 +11134,9 @@
       <c r="J412" s="2"/>
       <c r="K412" s="2"/>
       <c r="L412" s="2"/>
-      <c r="M412" s="21"/>
-      <c r="N412" s="22"/>
-      <c r="O412" s="23"/>
+      <c r="M412" s="15"/>
+      <c r="N412" s="16"/>
+      <c r="O412" s="17"/>
     </row>
     <row r="413" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G413" s="2"/>
@@ -11105,9 +11145,9 @@
       <c r="J413" s="2"/>
       <c r="K413" s="2"/>
       <c r="L413" s="2"/>
-      <c r="M413" s="21"/>
-      <c r="N413" s="22"/>
-      <c r="O413" s="23"/>
+      <c r="M413" s="15"/>
+      <c r="N413" s="16"/>
+      <c r="O413" s="17"/>
     </row>
     <row r="414" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G414" s="2"/>
@@ -11116,9 +11156,9 @@
       <c r="J414" s="2"/>
       <c r="K414" s="2"/>
       <c r="L414" s="2"/>
-      <c r="M414" s="21"/>
-      <c r="N414" s="22"/>
-      <c r="O414" s="23"/>
+      <c r="M414" s="15"/>
+      <c r="N414" s="16"/>
+      <c r="O414" s="17"/>
     </row>
     <row r="415" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G415" s="2"/>
@@ -11127,9 +11167,9 @@
       <c r="J415" s="2"/>
       <c r="K415" s="2"/>
       <c r="L415" s="2"/>
-      <c r="M415" s="21"/>
-      <c r="N415" s="22"/>
-      <c r="O415" s="23"/>
+      <c r="M415" s="15"/>
+      <c r="N415" s="16"/>
+      <c r="O415" s="17"/>
     </row>
     <row r="416" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G416" s="2"/>
@@ -11138,9 +11178,9 @@
       <c r="J416" s="2"/>
       <c r="K416" s="2"/>
       <c r="L416" s="2"/>
-      <c r="M416" s="21"/>
-      <c r="N416" s="22"/>
-      <c r="O416" s="23"/>
+      <c r="M416" s="15"/>
+      <c r="N416" s="16"/>
+      <c r="O416" s="17"/>
     </row>
     <row r="417" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G417" s="2"/>
@@ -11149,9 +11189,9 @@
       <c r="J417" s="2"/>
       <c r="K417" s="2"/>
       <c r="L417" s="2"/>
-      <c r="M417" s="21"/>
-      <c r="N417" s="22"/>
-      <c r="O417" s="23"/>
+      <c r="M417" s="15"/>
+      <c r="N417" s="16"/>
+      <c r="O417" s="17"/>
     </row>
     <row r="418" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G418" s="2"/>
@@ -11160,9 +11200,9 @@
       <c r="J418" s="2"/>
       <c r="K418" s="2"/>
       <c r="L418" s="2"/>
-      <c r="M418" s="21"/>
-      <c r="N418" s="22"/>
-      <c r="O418" s="23"/>
+      <c r="M418" s="15"/>
+      <c r="N418" s="16"/>
+      <c r="O418" s="17"/>
     </row>
     <row r="419" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G419" s="2"/>
@@ -11171,9 +11211,9 @@
       <c r="J419" s="2"/>
       <c r="K419" s="2"/>
       <c r="L419" s="2"/>
-      <c r="M419" s="21"/>
-      <c r="N419" s="22"/>
-      <c r="O419" s="23"/>
+      <c r="M419" s="15"/>
+      <c r="N419" s="16"/>
+      <c r="O419" s="17"/>
     </row>
     <row r="420" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G420" s="2"/>
@@ -11182,9 +11222,9 @@
       <c r="J420" s="2"/>
       <c r="K420" s="2"/>
       <c r="L420" s="2"/>
-      <c r="M420" s="21"/>
-      <c r="N420" s="22"/>
-      <c r="O420" s="23"/>
+      <c r="M420" s="15"/>
+      <c r="N420" s="16"/>
+      <c r="O420" s="17"/>
     </row>
     <row r="421" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G421" s="2"/>
@@ -11193,9 +11233,9 @@
       <c r="J421" s="2"/>
       <c r="K421" s="2"/>
       <c r="L421" s="2"/>
-      <c r="M421" s="21"/>
-      <c r="N421" s="22"/>
-      <c r="O421" s="23"/>
+      <c r="M421" s="15"/>
+      <c r="N421" s="16"/>
+      <c r="O421" s="17"/>
     </row>
     <row r="422" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G422" s="2"/>
@@ -11204,9 +11244,9 @@
       <c r="J422" s="2"/>
       <c r="K422" s="2"/>
       <c r="L422" s="2"/>
-      <c r="M422" s="21"/>
-      <c r="N422" s="22"/>
-      <c r="O422" s="23"/>
+      <c r="M422" s="15"/>
+      <c r="N422" s="16"/>
+      <c r="O422" s="17"/>
     </row>
     <row r="423" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G423" s="2"/>
@@ -11215,9 +11255,9 @@
       <c r="J423" s="2"/>
       <c r="K423" s="2"/>
       <c r="L423" s="2"/>
-      <c r="M423" s="21"/>
-      <c r="N423" s="22"/>
-      <c r="O423" s="23"/>
+      <c r="M423" s="15"/>
+      <c r="N423" s="16"/>
+      <c r="O423" s="17"/>
     </row>
     <row r="424" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G424" s="2"/>
@@ -11226,9 +11266,9 @@
       <c r="J424" s="2"/>
       <c r="K424" s="2"/>
       <c r="L424" s="2"/>
-      <c r="M424" s="21"/>
-      <c r="N424" s="22"/>
-      <c r="O424" s="23"/>
+      <c r="M424" s="15"/>
+      <c r="N424" s="16"/>
+      <c r="O424" s="17"/>
     </row>
     <row r="425" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G425" s="2"/>
@@ -11237,9 +11277,9 @@
       <c r="J425" s="2"/>
       <c r="K425" s="2"/>
       <c r="L425" s="2"/>
-      <c r="M425" s="21"/>
-      <c r="N425" s="22"/>
-      <c r="O425" s="23"/>
+      <c r="M425" s="15"/>
+      <c r="N425" s="16"/>
+      <c r="O425" s="17"/>
     </row>
     <row r="426" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G426" s="2"/>
@@ -11248,9 +11288,9 @@
       <c r="J426" s="2"/>
       <c r="K426" s="2"/>
       <c r="L426" s="2"/>
-      <c r="M426" s="21"/>
-      <c r="N426" s="22"/>
-      <c r="O426" s="23"/>
+      <c r="M426" s="15"/>
+      <c r="N426" s="16"/>
+      <c r="O426" s="17"/>
     </row>
     <row r="427" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G427" s="2"/>
@@ -11259,9 +11299,9 @@
       <c r="J427" s="2"/>
       <c r="K427" s="2"/>
       <c r="L427" s="2"/>
-      <c r="M427" s="21"/>
-      <c r="N427" s="22"/>
-      <c r="O427" s="23"/>
+      <c r="M427" s="15"/>
+      <c r="N427" s="16"/>
+      <c r="O427" s="17"/>
     </row>
     <row r="428" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G428" s="2"/>
@@ -11270,9 +11310,9 @@
       <c r="J428" s="2"/>
       <c r="K428" s="2"/>
       <c r="L428" s="2"/>
-      <c r="M428" s="21"/>
-      <c r="N428" s="22"/>
-      <c r="O428" s="23"/>
+      <c r="M428" s="15"/>
+      <c r="N428" s="16"/>
+      <c r="O428" s="17"/>
     </row>
     <row r="429" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G429" s="2"/>
@@ -11281,9 +11321,9 @@
       <c r="J429" s="2"/>
       <c r="K429" s="2"/>
       <c r="L429" s="2"/>
-      <c r="M429" s="21"/>
-      <c r="N429" s="22"/>
-      <c r="O429" s="23"/>
+      <c r="M429" s="15"/>
+      <c r="N429" s="16"/>
+      <c r="O429" s="17"/>
     </row>
     <row r="430" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G430" s="2"/>
@@ -11292,9 +11332,9 @@
       <c r="J430" s="2"/>
       <c r="K430" s="2"/>
       <c r="L430" s="2"/>
-      <c r="M430" s="21"/>
-      <c r="N430" s="22"/>
-      <c r="O430" s="23"/>
+      <c r="M430" s="15"/>
+      <c r="N430" s="16"/>
+      <c r="O430" s="17"/>
     </row>
     <row r="431" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G431" s="2"/>
@@ -11303,9 +11343,9 @@
       <c r="J431" s="2"/>
       <c r="K431" s="2"/>
       <c r="L431" s="2"/>
-      <c r="M431" s="21"/>
-      <c r="N431" s="22"/>
-      <c r="O431" s="23"/>
+      <c r="M431" s="15"/>
+      <c r="N431" s="16"/>
+      <c r="O431" s="17"/>
     </row>
     <row r="432" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G432" s="2"/>
@@ -11314,9 +11354,9 @@
       <c r="J432" s="2"/>
       <c r="K432" s="2"/>
       <c r="L432" s="2"/>
-      <c r="M432" s="21"/>
-      <c r="N432" s="22"/>
-      <c r="O432" s="23"/>
+      <c r="M432" s="15"/>
+      <c r="N432" s="16"/>
+      <c r="O432" s="17"/>
     </row>
     <row r="433" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G433" s="2"/>
@@ -11325,9 +11365,9 @@
       <c r="J433" s="2"/>
       <c r="K433" s="2"/>
       <c r="L433" s="2"/>
-      <c r="M433" s="21"/>
-      <c r="N433" s="22"/>
-      <c r="O433" s="23"/>
+      <c r="M433" s="15"/>
+      <c r="N433" s="16"/>
+      <c r="O433" s="17"/>
     </row>
     <row r="434" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G434" s="2"/>
@@ -11336,9 +11376,9 @@
       <c r="J434" s="2"/>
       <c r="K434" s="2"/>
       <c r="L434" s="2"/>
-      <c r="M434" s="21"/>
-      <c r="N434" s="22"/>
-      <c r="O434" s="23"/>
+      <c r="M434" s="15"/>
+      <c r="N434" s="16"/>
+      <c r="O434" s="17"/>
     </row>
     <row r="435" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G435" s="2"/>
@@ -11347,9 +11387,9 @@
       <c r="J435" s="2"/>
       <c r="K435" s="2"/>
       <c r="L435" s="2"/>
-      <c r="M435" s="21"/>
-      <c r="N435" s="22"/>
-      <c r="O435" s="23"/>
+      <c r="M435" s="15"/>
+      <c r="N435" s="16"/>
+      <c r="O435" s="17"/>
     </row>
     <row r="436" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G436" s="2"/>
@@ -11358,9 +11398,9 @@
       <c r="J436" s="2"/>
       <c r="K436" s="2"/>
       <c r="L436" s="2"/>
-      <c r="M436" s="21"/>
-      <c r="N436" s="22"/>
-      <c r="O436" s="23"/>
+      <c r="M436" s="15"/>
+      <c r="N436" s="16"/>
+      <c r="O436" s="17"/>
     </row>
     <row r="437" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G437" s="2"/>
@@ -11369,9 +11409,9 @@
       <c r="J437" s="2"/>
       <c r="K437" s="2"/>
       <c r="L437" s="2"/>
-      <c r="M437" s="21"/>
-      <c r="N437" s="22"/>
-      <c r="O437" s="23"/>
+      <c r="M437" s="15"/>
+      <c r="N437" s="16"/>
+      <c r="O437" s="17"/>
     </row>
     <row r="438" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G438" s="2"/>
@@ -11380,9 +11420,9 @@
       <c r="J438" s="2"/>
       <c r="K438" s="2"/>
       <c r="L438" s="2"/>
-      <c r="M438" s="21"/>
-      <c r="N438" s="22"/>
-      <c r="O438" s="23"/>
+      <c r="M438" s="15"/>
+      <c r="N438" s="16"/>
+      <c r="O438" s="17"/>
     </row>
     <row r="439" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G439" s="2"/>
@@ -11391,9 +11431,9 @@
       <c r="J439" s="2"/>
       <c r="K439" s="2"/>
       <c r="L439" s="2"/>
-      <c r="M439" s="21"/>
-      <c r="N439" s="22"/>
-      <c r="O439" s="23"/>
+      <c r="M439" s="15"/>
+      <c r="N439" s="16"/>
+      <c r="O439" s="17"/>
     </row>
     <row r="440" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G440" s="2"/>
@@ -11402,9 +11442,9 @@
       <c r="J440" s="2"/>
       <c r="K440" s="2"/>
       <c r="L440" s="2"/>
-      <c r="M440" s="21"/>
-      <c r="N440" s="22"/>
-      <c r="O440" s="23"/>
+      <c r="M440" s="15"/>
+      <c r="N440" s="16"/>
+      <c r="O440" s="17"/>
     </row>
     <row r="441" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G441" s="2"/>
@@ -11413,9 +11453,9 @@
       <c r="J441" s="2"/>
       <c r="K441" s="2"/>
       <c r="L441" s="2"/>
-      <c r="M441" s="21"/>
-      <c r="N441" s="22"/>
-      <c r="O441" s="23"/>
+      <c r="M441" s="15"/>
+      <c r="N441" s="16"/>
+      <c r="O441" s="17"/>
     </row>
     <row r="442" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G442" s="2"/>
@@ -11424,9 +11464,9 @@
       <c r="J442" s="2"/>
       <c r="K442" s="2"/>
       <c r="L442" s="2"/>
-      <c r="M442" s="21"/>
-      <c r="N442" s="22"/>
-      <c r="O442" s="23"/>
+      <c r="M442" s="15"/>
+      <c r="N442" s="16"/>
+      <c r="O442" s="17"/>
     </row>
     <row r="443" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G443" s="2"/>
@@ -11435,9 +11475,9 @@
       <c r="J443" s="2"/>
       <c r="K443" s="2"/>
       <c r="L443" s="2"/>
-      <c r="M443" s="21"/>
-      <c r="N443" s="22"/>
-      <c r="O443" s="23"/>
+      <c r="M443" s="15"/>
+      <c r="N443" s="16"/>
+      <c r="O443" s="17"/>
     </row>
     <row r="444" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G444" s="2"/>
@@ -11446,9 +11486,9 @@
       <c r="J444" s="2"/>
       <c r="K444" s="2"/>
       <c r="L444" s="2"/>
-      <c r="M444" s="21"/>
-      <c r="N444" s="22"/>
-      <c r="O444" s="23"/>
+      <c r="M444" s="15"/>
+      <c r="N444" s="16"/>
+      <c r="O444" s="17"/>
     </row>
     <row r="445" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G445" s="2"/>
@@ -11457,9 +11497,9 @@
       <c r="J445" s="2"/>
       <c r="K445" s="2"/>
       <c r="L445" s="2"/>
-      <c r="M445" s="21"/>
-      <c r="N445" s="22"/>
-      <c r="O445" s="23"/>
+      <c r="M445" s="15"/>
+      <c r="N445" s="16"/>
+      <c r="O445" s="17"/>
     </row>
     <row r="446" spans="7:15" x14ac:dyDescent="0.3">
       <c r="G446" s="2"/>
@@ -11468,9 +11508,9 @@
       <c r="J446" s="2"/>
       <c r="K446" s="2"/>
       <c r="L446" s="2"/>
-      <c r="M446" s="21"/>
-      <c r="N446" s="22"/>
-      <c r="O446" s="23"/>
+      <c r="M446" s="15"/>
+      <c r="N446" s="16"/>
+      <c r="O446" s="17"/>
     </row>
   </sheetData>
   <autoFilter ref="G12:O207" xr:uid="{C4A4A34A-4054-4754-923E-12CA6BF1DEB9}">
@@ -11478,401 +11518,23 @@
     <filterColumn colId="7" showButton="0"/>
   </autoFilter>
   <mergeCells count="436">
-    <mergeCell ref="M446:O446"/>
-    <mergeCell ref="M437:O437"/>
-    <mergeCell ref="M438:O438"/>
-    <mergeCell ref="M439:O439"/>
-    <mergeCell ref="M440:O440"/>
-    <mergeCell ref="M441:O441"/>
-    <mergeCell ref="M442:O442"/>
-    <mergeCell ref="M443:O443"/>
-    <mergeCell ref="M444:O444"/>
-    <mergeCell ref="M445:O445"/>
-    <mergeCell ref="M428:O428"/>
-    <mergeCell ref="M429:O429"/>
-    <mergeCell ref="M430:O430"/>
-    <mergeCell ref="M431:O431"/>
-    <mergeCell ref="M432:O432"/>
-    <mergeCell ref="M433:O433"/>
-    <mergeCell ref="M434:O434"/>
-    <mergeCell ref="M435:O435"/>
-    <mergeCell ref="M436:O436"/>
-    <mergeCell ref="M419:O419"/>
-    <mergeCell ref="M420:O420"/>
-    <mergeCell ref="M421:O421"/>
-    <mergeCell ref="M422:O422"/>
-    <mergeCell ref="M423:O423"/>
-    <mergeCell ref="M424:O424"/>
-    <mergeCell ref="M425:O425"/>
-    <mergeCell ref="M426:O426"/>
-    <mergeCell ref="M427:O427"/>
-    <mergeCell ref="M410:O410"/>
-    <mergeCell ref="M411:O411"/>
-    <mergeCell ref="M412:O412"/>
-    <mergeCell ref="M413:O413"/>
-    <mergeCell ref="M414:O414"/>
-    <mergeCell ref="M415:O415"/>
-    <mergeCell ref="M416:O416"/>
-    <mergeCell ref="M417:O417"/>
-    <mergeCell ref="M418:O418"/>
-    <mergeCell ref="M401:O401"/>
-    <mergeCell ref="M402:O402"/>
-    <mergeCell ref="M403:O403"/>
-    <mergeCell ref="M404:O404"/>
-    <mergeCell ref="M405:O405"/>
-    <mergeCell ref="M406:O406"/>
-    <mergeCell ref="M407:O407"/>
-    <mergeCell ref="M408:O408"/>
-    <mergeCell ref="M409:O409"/>
-    <mergeCell ref="M392:O392"/>
-    <mergeCell ref="M393:O393"/>
-    <mergeCell ref="M394:O394"/>
-    <mergeCell ref="M395:O395"/>
-    <mergeCell ref="M396:O396"/>
-    <mergeCell ref="M397:O397"/>
-    <mergeCell ref="M398:O398"/>
-    <mergeCell ref="M399:O399"/>
-    <mergeCell ref="M400:O400"/>
-    <mergeCell ref="M383:O383"/>
-    <mergeCell ref="M384:O384"/>
-    <mergeCell ref="M385:O385"/>
-    <mergeCell ref="M386:O386"/>
-    <mergeCell ref="M387:O387"/>
-    <mergeCell ref="M388:O388"/>
-    <mergeCell ref="M389:O389"/>
-    <mergeCell ref="M390:O390"/>
-    <mergeCell ref="M391:O391"/>
-    <mergeCell ref="M374:O374"/>
-    <mergeCell ref="M375:O375"/>
-    <mergeCell ref="M376:O376"/>
-    <mergeCell ref="M377:O377"/>
-    <mergeCell ref="M378:O378"/>
-    <mergeCell ref="M379:O379"/>
-    <mergeCell ref="M380:O380"/>
-    <mergeCell ref="M381:O381"/>
-    <mergeCell ref="M382:O382"/>
-    <mergeCell ref="M365:O365"/>
-    <mergeCell ref="M366:O366"/>
-    <mergeCell ref="M367:O367"/>
-    <mergeCell ref="M368:O368"/>
-    <mergeCell ref="M369:O369"/>
-    <mergeCell ref="M370:O370"/>
-    <mergeCell ref="M371:O371"/>
-    <mergeCell ref="M372:O372"/>
-    <mergeCell ref="M373:O373"/>
-    <mergeCell ref="M356:O356"/>
-    <mergeCell ref="M357:O357"/>
-    <mergeCell ref="M358:O358"/>
-    <mergeCell ref="M359:O359"/>
-    <mergeCell ref="M360:O360"/>
-    <mergeCell ref="M361:O361"/>
-    <mergeCell ref="M362:O362"/>
-    <mergeCell ref="M363:O363"/>
-    <mergeCell ref="M364:O364"/>
-    <mergeCell ref="M347:O347"/>
-    <mergeCell ref="M348:O348"/>
-    <mergeCell ref="M349:O349"/>
-    <mergeCell ref="M350:O350"/>
-    <mergeCell ref="M351:O351"/>
-    <mergeCell ref="M352:O352"/>
-    <mergeCell ref="M353:O353"/>
-    <mergeCell ref="M354:O354"/>
-    <mergeCell ref="M355:O355"/>
-    <mergeCell ref="M338:O338"/>
-    <mergeCell ref="M339:O339"/>
-    <mergeCell ref="M340:O340"/>
-    <mergeCell ref="M341:O341"/>
-    <mergeCell ref="M342:O342"/>
-    <mergeCell ref="M343:O343"/>
-    <mergeCell ref="M344:O344"/>
-    <mergeCell ref="M345:O345"/>
-    <mergeCell ref="M346:O346"/>
-    <mergeCell ref="M329:O329"/>
-    <mergeCell ref="M330:O330"/>
-    <mergeCell ref="M331:O331"/>
-    <mergeCell ref="M332:O332"/>
-    <mergeCell ref="M333:O333"/>
-    <mergeCell ref="M334:O334"/>
-    <mergeCell ref="M335:O335"/>
-    <mergeCell ref="M336:O336"/>
-    <mergeCell ref="M337:O337"/>
-    <mergeCell ref="M320:O320"/>
-    <mergeCell ref="M321:O321"/>
-    <mergeCell ref="M322:O322"/>
-    <mergeCell ref="M323:O323"/>
-    <mergeCell ref="M324:O324"/>
-    <mergeCell ref="M325:O325"/>
-    <mergeCell ref="M326:O326"/>
-    <mergeCell ref="M327:O327"/>
-    <mergeCell ref="M328:O328"/>
-    <mergeCell ref="M311:O311"/>
-    <mergeCell ref="M312:O312"/>
-    <mergeCell ref="M313:O313"/>
-    <mergeCell ref="M314:O314"/>
-    <mergeCell ref="M315:O315"/>
-    <mergeCell ref="M316:O316"/>
-    <mergeCell ref="M317:O317"/>
-    <mergeCell ref="M318:O318"/>
-    <mergeCell ref="M319:O319"/>
-    <mergeCell ref="M302:O302"/>
-    <mergeCell ref="M303:O303"/>
-    <mergeCell ref="M304:O304"/>
-    <mergeCell ref="M305:O305"/>
-    <mergeCell ref="M306:O306"/>
-    <mergeCell ref="M307:O307"/>
-    <mergeCell ref="M308:O308"/>
-    <mergeCell ref="M309:O309"/>
-    <mergeCell ref="M310:O310"/>
-    <mergeCell ref="M293:O293"/>
-    <mergeCell ref="M294:O294"/>
-    <mergeCell ref="M295:O295"/>
-    <mergeCell ref="M296:O296"/>
-    <mergeCell ref="M297:O297"/>
-    <mergeCell ref="M298:O298"/>
-    <mergeCell ref="M299:O299"/>
-    <mergeCell ref="M300:O300"/>
-    <mergeCell ref="M301:O301"/>
-    <mergeCell ref="M284:O284"/>
-    <mergeCell ref="M285:O285"/>
-    <mergeCell ref="M286:O286"/>
-    <mergeCell ref="M287:O287"/>
-    <mergeCell ref="M288:O288"/>
-    <mergeCell ref="M289:O289"/>
-    <mergeCell ref="M290:O290"/>
-    <mergeCell ref="M291:O291"/>
-    <mergeCell ref="M292:O292"/>
-    <mergeCell ref="M275:O275"/>
-    <mergeCell ref="M276:O276"/>
-    <mergeCell ref="M277:O277"/>
-    <mergeCell ref="M278:O278"/>
-    <mergeCell ref="M279:O279"/>
-    <mergeCell ref="M280:O280"/>
-    <mergeCell ref="M281:O281"/>
-    <mergeCell ref="M282:O282"/>
-    <mergeCell ref="M283:O283"/>
-    <mergeCell ref="M266:O266"/>
-    <mergeCell ref="M267:O267"/>
-    <mergeCell ref="M268:O268"/>
-    <mergeCell ref="M269:O269"/>
-    <mergeCell ref="M270:O270"/>
-    <mergeCell ref="M271:O271"/>
-    <mergeCell ref="M272:O272"/>
-    <mergeCell ref="M273:O273"/>
-    <mergeCell ref="M274:O274"/>
-    <mergeCell ref="M257:O257"/>
-    <mergeCell ref="M258:O258"/>
-    <mergeCell ref="M259:O259"/>
-    <mergeCell ref="M260:O260"/>
-    <mergeCell ref="M261:O261"/>
-    <mergeCell ref="M262:O262"/>
-    <mergeCell ref="M263:O263"/>
-    <mergeCell ref="M264:O264"/>
-    <mergeCell ref="M265:O265"/>
-    <mergeCell ref="M248:O248"/>
-    <mergeCell ref="M249:O249"/>
-    <mergeCell ref="M250:O250"/>
-    <mergeCell ref="M251:O251"/>
-    <mergeCell ref="M252:O252"/>
-    <mergeCell ref="M253:O253"/>
-    <mergeCell ref="M254:O254"/>
-    <mergeCell ref="M255:O255"/>
-    <mergeCell ref="M256:O256"/>
-    <mergeCell ref="M239:O239"/>
-    <mergeCell ref="M240:O240"/>
-    <mergeCell ref="M241:O241"/>
-    <mergeCell ref="M242:O242"/>
-    <mergeCell ref="M243:O243"/>
-    <mergeCell ref="M244:O244"/>
-    <mergeCell ref="M245:O245"/>
-    <mergeCell ref="M246:O246"/>
-    <mergeCell ref="M247:O247"/>
-    <mergeCell ref="M230:O230"/>
-    <mergeCell ref="M231:O231"/>
-    <mergeCell ref="M232:O232"/>
-    <mergeCell ref="M233:O233"/>
-    <mergeCell ref="M234:O234"/>
-    <mergeCell ref="M235:O235"/>
-    <mergeCell ref="M236:O236"/>
-    <mergeCell ref="M237:O237"/>
-    <mergeCell ref="M238:O238"/>
-    <mergeCell ref="M212:O212"/>
-    <mergeCell ref="M213:O213"/>
-    <mergeCell ref="M214:O214"/>
-    <mergeCell ref="M215:O215"/>
-    <mergeCell ref="M216:O216"/>
-    <mergeCell ref="M226:O226"/>
-    <mergeCell ref="M227:O227"/>
-    <mergeCell ref="M228:O228"/>
-    <mergeCell ref="M229:O229"/>
-    <mergeCell ref="M221:O221"/>
-    <mergeCell ref="M222:O222"/>
-    <mergeCell ref="M223:O223"/>
-    <mergeCell ref="M224:O224"/>
-    <mergeCell ref="M225:O225"/>
-    <mergeCell ref="M217:O217"/>
-    <mergeCell ref="M218:O218"/>
-    <mergeCell ref="M219:O219"/>
-    <mergeCell ref="M220:O220"/>
-    <mergeCell ref="M193:O193"/>
-    <mergeCell ref="M194:O194"/>
-    <mergeCell ref="M195:O195"/>
-    <mergeCell ref="M196:O196"/>
-    <mergeCell ref="M197:O197"/>
-    <mergeCell ref="M208:O208"/>
-    <mergeCell ref="M209:O209"/>
-    <mergeCell ref="M210:O210"/>
-    <mergeCell ref="M211:O211"/>
-    <mergeCell ref="M203:O203"/>
-    <mergeCell ref="M204:O204"/>
-    <mergeCell ref="M205:O205"/>
-    <mergeCell ref="M206:O206"/>
-    <mergeCell ref="M207:O207"/>
-    <mergeCell ref="M198:O198"/>
-    <mergeCell ref="M199:O199"/>
-    <mergeCell ref="M200:O200"/>
-    <mergeCell ref="M201:O201"/>
-    <mergeCell ref="M202:O202"/>
-    <mergeCell ref="M188:O188"/>
-    <mergeCell ref="M189:O189"/>
-    <mergeCell ref="M190:O190"/>
-    <mergeCell ref="M191:O191"/>
-    <mergeCell ref="M192:O192"/>
-    <mergeCell ref="M183:O183"/>
-    <mergeCell ref="M184:O184"/>
-    <mergeCell ref="M185:O185"/>
-    <mergeCell ref="M186:O186"/>
-    <mergeCell ref="M187:O187"/>
-    <mergeCell ref="M178:O178"/>
-    <mergeCell ref="M179:O179"/>
-    <mergeCell ref="M180:O180"/>
-    <mergeCell ref="M181:O181"/>
-    <mergeCell ref="M182:O182"/>
-    <mergeCell ref="M173:O173"/>
-    <mergeCell ref="M174:O174"/>
-    <mergeCell ref="M175:O175"/>
-    <mergeCell ref="M176:O176"/>
-    <mergeCell ref="M177:O177"/>
-    <mergeCell ref="M168:O168"/>
-    <mergeCell ref="M169:O169"/>
-    <mergeCell ref="M170:O170"/>
-    <mergeCell ref="M171:O171"/>
-    <mergeCell ref="M172:O172"/>
-    <mergeCell ref="M163:O163"/>
-    <mergeCell ref="M164:O164"/>
-    <mergeCell ref="M165:O165"/>
-    <mergeCell ref="M166:O166"/>
-    <mergeCell ref="M167:O167"/>
-    <mergeCell ref="M158:O158"/>
-    <mergeCell ref="M159:O159"/>
-    <mergeCell ref="M160:O160"/>
-    <mergeCell ref="M161:O161"/>
-    <mergeCell ref="M162:O162"/>
-    <mergeCell ref="M153:O153"/>
-    <mergeCell ref="M154:O154"/>
-    <mergeCell ref="M155:O155"/>
-    <mergeCell ref="M156:O156"/>
-    <mergeCell ref="M157:O157"/>
-    <mergeCell ref="M148:O148"/>
-    <mergeCell ref="M149:O149"/>
-    <mergeCell ref="M150:O150"/>
-    <mergeCell ref="M151:O151"/>
-    <mergeCell ref="M152:O152"/>
-    <mergeCell ref="M143:O143"/>
-    <mergeCell ref="M144:O144"/>
-    <mergeCell ref="M145:O145"/>
-    <mergeCell ref="M146:O146"/>
-    <mergeCell ref="M147:O147"/>
-    <mergeCell ref="M138:O138"/>
-    <mergeCell ref="M139:O139"/>
-    <mergeCell ref="M140:O140"/>
-    <mergeCell ref="M141:O141"/>
-    <mergeCell ref="M142:O142"/>
-    <mergeCell ref="M133:O133"/>
-    <mergeCell ref="M134:O134"/>
-    <mergeCell ref="M135:O135"/>
-    <mergeCell ref="M136:O136"/>
-    <mergeCell ref="M137:O137"/>
-    <mergeCell ref="M128:O128"/>
-    <mergeCell ref="M129:O129"/>
-    <mergeCell ref="M130:O130"/>
-    <mergeCell ref="M131:O131"/>
-    <mergeCell ref="M132:O132"/>
-    <mergeCell ref="M123:O123"/>
-    <mergeCell ref="M124:O124"/>
-    <mergeCell ref="M125:O125"/>
-    <mergeCell ref="M126:O126"/>
-    <mergeCell ref="M127:O127"/>
-    <mergeCell ref="M118:O118"/>
-    <mergeCell ref="M119:O119"/>
-    <mergeCell ref="M120:O120"/>
-    <mergeCell ref="M121:O121"/>
-    <mergeCell ref="M122:O122"/>
-    <mergeCell ref="M113:O113"/>
-    <mergeCell ref="M114:O114"/>
-    <mergeCell ref="M115:O115"/>
-    <mergeCell ref="M116:O116"/>
-    <mergeCell ref="M117:O117"/>
-    <mergeCell ref="M108:O108"/>
-    <mergeCell ref="M109:O109"/>
-    <mergeCell ref="M110:O110"/>
-    <mergeCell ref="M111:O111"/>
-    <mergeCell ref="M112:O112"/>
-    <mergeCell ref="M103:O103"/>
-    <mergeCell ref="M104:O104"/>
-    <mergeCell ref="M105:O105"/>
-    <mergeCell ref="M106:O106"/>
-    <mergeCell ref="M107:O107"/>
-    <mergeCell ref="M98:O98"/>
-    <mergeCell ref="M99:O99"/>
-    <mergeCell ref="M100:O100"/>
-    <mergeCell ref="M101:O101"/>
-    <mergeCell ref="M102:O102"/>
-    <mergeCell ref="M93:O93"/>
-    <mergeCell ref="M94:O94"/>
-    <mergeCell ref="M95:O95"/>
-    <mergeCell ref="M96:O96"/>
-    <mergeCell ref="M97:O97"/>
-    <mergeCell ref="M88:O88"/>
-    <mergeCell ref="M89:O89"/>
-    <mergeCell ref="M90:O90"/>
-    <mergeCell ref="M91:O91"/>
-    <mergeCell ref="M92:O92"/>
-    <mergeCell ref="M83:O83"/>
-    <mergeCell ref="M84:O84"/>
-    <mergeCell ref="M85:O85"/>
-    <mergeCell ref="M86:O86"/>
-    <mergeCell ref="M87:O87"/>
-    <mergeCell ref="M78:O78"/>
-    <mergeCell ref="M79:O79"/>
-    <mergeCell ref="M80:O80"/>
-    <mergeCell ref="M81:O81"/>
-    <mergeCell ref="M82:O82"/>
-    <mergeCell ref="M73:O73"/>
-    <mergeCell ref="M74:O74"/>
-    <mergeCell ref="M75:O75"/>
-    <mergeCell ref="M76:O76"/>
-    <mergeCell ref="M77:O77"/>
-    <mergeCell ref="M70:O70"/>
-    <mergeCell ref="M71:O71"/>
-    <mergeCell ref="M72:O72"/>
-    <mergeCell ref="M38:O38"/>
-    <mergeCell ref="M40:O40"/>
-    <mergeCell ref="M44:O44"/>
-    <mergeCell ref="M64:O64"/>
-    <mergeCell ref="M66:O66"/>
-    <mergeCell ref="M67:O67"/>
-    <mergeCell ref="M68:O68"/>
-    <mergeCell ref="M69:O69"/>
-    <mergeCell ref="M59:O59"/>
-    <mergeCell ref="M60:O60"/>
-    <mergeCell ref="M61:O61"/>
-    <mergeCell ref="M62:O62"/>
-    <mergeCell ref="M63:O63"/>
-    <mergeCell ref="M52:O52"/>
-    <mergeCell ref="M53:O53"/>
-    <mergeCell ref="M54:O54"/>
-    <mergeCell ref="M65:O65"/>
-    <mergeCell ref="M47:O47"/>
+    <mergeCell ref="M21:O21"/>
+    <mergeCell ref="M22:O22"/>
+    <mergeCell ref="M23:O23"/>
+    <mergeCell ref="M39:O39"/>
+    <mergeCell ref="M57:O57"/>
+    <mergeCell ref="M58:O58"/>
+    <mergeCell ref="M55:O55"/>
+    <mergeCell ref="M56:O56"/>
+    <mergeCell ref="M12:O12"/>
+    <mergeCell ref="M13:O13"/>
+    <mergeCell ref="M14:O14"/>
+    <mergeCell ref="M15:O15"/>
+    <mergeCell ref="M16:O16"/>
+    <mergeCell ref="M17:O17"/>
+    <mergeCell ref="M18:O18"/>
+    <mergeCell ref="M19:O19"/>
+    <mergeCell ref="M20:O20"/>
     <mergeCell ref="G4:O8"/>
     <mergeCell ref="M48:O48"/>
     <mergeCell ref="M49:O49"/>
@@ -11897,23 +11559,401 @@
     <mergeCell ref="M36:O36"/>
     <mergeCell ref="M37:O37"/>
     <mergeCell ref="M46:O46"/>
-    <mergeCell ref="M21:O21"/>
-    <mergeCell ref="M22:O22"/>
-    <mergeCell ref="M23:O23"/>
-    <mergeCell ref="M39:O39"/>
-    <mergeCell ref="M57:O57"/>
-    <mergeCell ref="M58:O58"/>
-    <mergeCell ref="M55:O55"/>
-    <mergeCell ref="M56:O56"/>
-    <mergeCell ref="M12:O12"/>
-    <mergeCell ref="M13:O13"/>
-    <mergeCell ref="M14:O14"/>
-    <mergeCell ref="M15:O15"/>
-    <mergeCell ref="M16:O16"/>
-    <mergeCell ref="M17:O17"/>
-    <mergeCell ref="M18:O18"/>
-    <mergeCell ref="M19:O19"/>
-    <mergeCell ref="M20:O20"/>
+    <mergeCell ref="M70:O70"/>
+    <mergeCell ref="M71:O71"/>
+    <mergeCell ref="M72:O72"/>
+    <mergeCell ref="M38:O38"/>
+    <mergeCell ref="M40:O40"/>
+    <mergeCell ref="M44:O44"/>
+    <mergeCell ref="M64:O64"/>
+    <mergeCell ref="M66:O66"/>
+    <mergeCell ref="M67:O67"/>
+    <mergeCell ref="M68:O68"/>
+    <mergeCell ref="M69:O69"/>
+    <mergeCell ref="M59:O59"/>
+    <mergeCell ref="M60:O60"/>
+    <mergeCell ref="M61:O61"/>
+    <mergeCell ref="M62:O62"/>
+    <mergeCell ref="M63:O63"/>
+    <mergeCell ref="M52:O52"/>
+    <mergeCell ref="M53:O53"/>
+    <mergeCell ref="M54:O54"/>
+    <mergeCell ref="M65:O65"/>
+    <mergeCell ref="M47:O47"/>
+    <mergeCell ref="M78:O78"/>
+    <mergeCell ref="M79:O79"/>
+    <mergeCell ref="M80:O80"/>
+    <mergeCell ref="M81:O81"/>
+    <mergeCell ref="M82:O82"/>
+    <mergeCell ref="M73:O73"/>
+    <mergeCell ref="M74:O74"/>
+    <mergeCell ref="M75:O75"/>
+    <mergeCell ref="M76:O76"/>
+    <mergeCell ref="M77:O77"/>
+    <mergeCell ref="M88:O88"/>
+    <mergeCell ref="M89:O89"/>
+    <mergeCell ref="M90:O90"/>
+    <mergeCell ref="M91:O91"/>
+    <mergeCell ref="M92:O92"/>
+    <mergeCell ref="M83:O83"/>
+    <mergeCell ref="M84:O84"/>
+    <mergeCell ref="M85:O85"/>
+    <mergeCell ref="M86:O86"/>
+    <mergeCell ref="M87:O87"/>
+    <mergeCell ref="M98:O98"/>
+    <mergeCell ref="M99:O99"/>
+    <mergeCell ref="M100:O100"/>
+    <mergeCell ref="M101:O101"/>
+    <mergeCell ref="M102:O102"/>
+    <mergeCell ref="M93:O93"/>
+    <mergeCell ref="M94:O94"/>
+    <mergeCell ref="M95:O95"/>
+    <mergeCell ref="M96:O96"/>
+    <mergeCell ref="M97:O97"/>
+    <mergeCell ref="M108:O108"/>
+    <mergeCell ref="M109:O109"/>
+    <mergeCell ref="M110:O110"/>
+    <mergeCell ref="M111:O111"/>
+    <mergeCell ref="M112:O112"/>
+    <mergeCell ref="M103:O103"/>
+    <mergeCell ref="M104:O104"/>
+    <mergeCell ref="M105:O105"/>
+    <mergeCell ref="M106:O106"/>
+    <mergeCell ref="M107:O107"/>
+    <mergeCell ref="M118:O118"/>
+    <mergeCell ref="M119:O119"/>
+    <mergeCell ref="M120:O120"/>
+    <mergeCell ref="M121:O121"/>
+    <mergeCell ref="M122:O122"/>
+    <mergeCell ref="M113:O113"/>
+    <mergeCell ref="M114:O114"/>
+    <mergeCell ref="M115:O115"/>
+    <mergeCell ref="M116:O116"/>
+    <mergeCell ref="M117:O117"/>
+    <mergeCell ref="M128:O128"/>
+    <mergeCell ref="M129:O129"/>
+    <mergeCell ref="M130:O130"/>
+    <mergeCell ref="M131:O131"/>
+    <mergeCell ref="M132:O132"/>
+    <mergeCell ref="M123:O123"/>
+    <mergeCell ref="M124:O124"/>
+    <mergeCell ref="M125:O125"/>
+    <mergeCell ref="M126:O126"/>
+    <mergeCell ref="M127:O127"/>
+    <mergeCell ref="M138:O138"/>
+    <mergeCell ref="M139:O139"/>
+    <mergeCell ref="M140:O140"/>
+    <mergeCell ref="M141:O141"/>
+    <mergeCell ref="M142:O142"/>
+    <mergeCell ref="M133:O133"/>
+    <mergeCell ref="M134:O134"/>
+    <mergeCell ref="M135:O135"/>
+    <mergeCell ref="M136:O136"/>
+    <mergeCell ref="M137:O137"/>
+    <mergeCell ref="M148:O148"/>
+    <mergeCell ref="M149:O149"/>
+    <mergeCell ref="M150:O150"/>
+    <mergeCell ref="M151:O151"/>
+    <mergeCell ref="M152:O152"/>
+    <mergeCell ref="M143:O143"/>
+    <mergeCell ref="M144:O144"/>
+    <mergeCell ref="M145:O145"/>
+    <mergeCell ref="M146:O146"/>
+    <mergeCell ref="M147:O147"/>
+    <mergeCell ref="M158:O158"/>
+    <mergeCell ref="M159:O159"/>
+    <mergeCell ref="M160:O160"/>
+    <mergeCell ref="M161:O161"/>
+    <mergeCell ref="M162:O162"/>
+    <mergeCell ref="M153:O153"/>
+    <mergeCell ref="M154:O154"/>
+    <mergeCell ref="M155:O155"/>
+    <mergeCell ref="M156:O156"/>
+    <mergeCell ref="M157:O157"/>
+    <mergeCell ref="M168:O168"/>
+    <mergeCell ref="M169:O169"/>
+    <mergeCell ref="M170:O170"/>
+    <mergeCell ref="M171:O171"/>
+    <mergeCell ref="M172:O172"/>
+    <mergeCell ref="M163:O163"/>
+    <mergeCell ref="M164:O164"/>
+    <mergeCell ref="M165:O165"/>
+    <mergeCell ref="M166:O166"/>
+    <mergeCell ref="M167:O167"/>
+    <mergeCell ref="M178:O178"/>
+    <mergeCell ref="M179:O179"/>
+    <mergeCell ref="M180:O180"/>
+    <mergeCell ref="M181:O181"/>
+    <mergeCell ref="M182:O182"/>
+    <mergeCell ref="M173:O173"/>
+    <mergeCell ref="M174:O174"/>
+    <mergeCell ref="M175:O175"/>
+    <mergeCell ref="M176:O176"/>
+    <mergeCell ref="M177:O177"/>
+    <mergeCell ref="M188:O188"/>
+    <mergeCell ref="M189:O189"/>
+    <mergeCell ref="M190:O190"/>
+    <mergeCell ref="M191:O191"/>
+    <mergeCell ref="M192:O192"/>
+    <mergeCell ref="M183:O183"/>
+    <mergeCell ref="M184:O184"/>
+    <mergeCell ref="M185:O185"/>
+    <mergeCell ref="M186:O186"/>
+    <mergeCell ref="M187:O187"/>
+    <mergeCell ref="M193:O193"/>
+    <mergeCell ref="M194:O194"/>
+    <mergeCell ref="M195:O195"/>
+    <mergeCell ref="M196:O196"/>
+    <mergeCell ref="M197:O197"/>
+    <mergeCell ref="M208:O208"/>
+    <mergeCell ref="M209:O209"/>
+    <mergeCell ref="M210:O210"/>
+    <mergeCell ref="M211:O211"/>
+    <mergeCell ref="M203:O203"/>
+    <mergeCell ref="M204:O204"/>
+    <mergeCell ref="M205:O205"/>
+    <mergeCell ref="M206:O206"/>
+    <mergeCell ref="M207:O207"/>
+    <mergeCell ref="M198:O198"/>
+    <mergeCell ref="M199:O199"/>
+    <mergeCell ref="M200:O200"/>
+    <mergeCell ref="M201:O201"/>
+    <mergeCell ref="M202:O202"/>
+    <mergeCell ref="M212:O212"/>
+    <mergeCell ref="M213:O213"/>
+    <mergeCell ref="M214:O214"/>
+    <mergeCell ref="M215:O215"/>
+    <mergeCell ref="M216:O216"/>
+    <mergeCell ref="M226:O226"/>
+    <mergeCell ref="M227:O227"/>
+    <mergeCell ref="M228:O228"/>
+    <mergeCell ref="M229:O229"/>
+    <mergeCell ref="M221:O221"/>
+    <mergeCell ref="M222:O222"/>
+    <mergeCell ref="M223:O223"/>
+    <mergeCell ref="M224:O224"/>
+    <mergeCell ref="M225:O225"/>
+    <mergeCell ref="M217:O217"/>
+    <mergeCell ref="M218:O218"/>
+    <mergeCell ref="M219:O219"/>
+    <mergeCell ref="M220:O220"/>
+    <mergeCell ref="M230:O230"/>
+    <mergeCell ref="M231:O231"/>
+    <mergeCell ref="M232:O232"/>
+    <mergeCell ref="M233:O233"/>
+    <mergeCell ref="M234:O234"/>
+    <mergeCell ref="M235:O235"/>
+    <mergeCell ref="M236:O236"/>
+    <mergeCell ref="M237:O237"/>
+    <mergeCell ref="M238:O238"/>
+    <mergeCell ref="M239:O239"/>
+    <mergeCell ref="M240:O240"/>
+    <mergeCell ref="M241:O241"/>
+    <mergeCell ref="M242:O242"/>
+    <mergeCell ref="M243:O243"/>
+    <mergeCell ref="M244:O244"/>
+    <mergeCell ref="M245:O245"/>
+    <mergeCell ref="M246:O246"/>
+    <mergeCell ref="M247:O247"/>
+    <mergeCell ref="M248:O248"/>
+    <mergeCell ref="M249:O249"/>
+    <mergeCell ref="M250:O250"/>
+    <mergeCell ref="M251:O251"/>
+    <mergeCell ref="M252:O252"/>
+    <mergeCell ref="M253:O253"/>
+    <mergeCell ref="M254:O254"/>
+    <mergeCell ref="M255:O255"/>
+    <mergeCell ref="M256:O256"/>
+    <mergeCell ref="M257:O257"/>
+    <mergeCell ref="M258:O258"/>
+    <mergeCell ref="M259:O259"/>
+    <mergeCell ref="M260:O260"/>
+    <mergeCell ref="M261:O261"/>
+    <mergeCell ref="M262:O262"/>
+    <mergeCell ref="M263:O263"/>
+    <mergeCell ref="M264:O264"/>
+    <mergeCell ref="M265:O265"/>
+    <mergeCell ref="M266:O266"/>
+    <mergeCell ref="M267:O267"/>
+    <mergeCell ref="M268:O268"/>
+    <mergeCell ref="M269:O269"/>
+    <mergeCell ref="M270:O270"/>
+    <mergeCell ref="M271:O271"/>
+    <mergeCell ref="M272:O272"/>
+    <mergeCell ref="M273:O273"/>
+    <mergeCell ref="M274:O274"/>
+    <mergeCell ref="M275:O275"/>
+    <mergeCell ref="M276:O276"/>
+    <mergeCell ref="M277:O277"/>
+    <mergeCell ref="M278:O278"/>
+    <mergeCell ref="M279:O279"/>
+    <mergeCell ref="M280:O280"/>
+    <mergeCell ref="M281:O281"/>
+    <mergeCell ref="M282:O282"/>
+    <mergeCell ref="M283:O283"/>
+    <mergeCell ref="M284:O284"/>
+    <mergeCell ref="M285:O285"/>
+    <mergeCell ref="M286:O286"/>
+    <mergeCell ref="M287:O287"/>
+    <mergeCell ref="M288:O288"/>
+    <mergeCell ref="M289:O289"/>
+    <mergeCell ref="M290:O290"/>
+    <mergeCell ref="M291:O291"/>
+    <mergeCell ref="M292:O292"/>
+    <mergeCell ref="M293:O293"/>
+    <mergeCell ref="M294:O294"/>
+    <mergeCell ref="M295:O295"/>
+    <mergeCell ref="M296:O296"/>
+    <mergeCell ref="M297:O297"/>
+    <mergeCell ref="M298:O298"/>
+    <mergeCell ref="M299:O299"/>
+    <mergeCell ref="M300:O300"/>
+    <mergeCell ref="M301:O301"/>
+    <mergeCell ref="M302:O302"/>
+    <mergeCell ref="M303:O303"/>
+    <mergeCell ref="M304:O304"/>
+    <mergeCell ref="M305:O305"/>
+    <mergeCell ref="M306:O306"/>
+    <mergeCell ref="M307:O307"/>
+    <mergeCell ref="M308:O308"/>
+    <mergeCell ref="M309:O309"/>
+    <mergeCell ref="M310:O310"/>
+    <mergeCell ref="M311:O311"/>
+    <mergeCell ref="M312:O312"/>
+    <mergeCell ref="M313:O313"/>
+    <mergeCell ref="M314:O314"/>
+    <mergeCell ref="M315:O315"/>
+    <mergeCell ref="M316:O316"/>
+    <mergeCell ref="M317:O317"/>
+    <mergeCell ref="M318:O318"/>
+    <mergeCell ref="M319:O319"/>
+    <mergeCell ref="M320:O320"/>
+    <mergeCell ref="M321:O321"/>
+    <mergeCell ref="M322:O322"/>
+    <mergeCell ref="M323:O323"/>
+    <mergeCell ref="M324:O324"/>
+    <mergeCell ref="M325:O325"/>
+    <mergeCell ref="M326:O326"/>
+    <mergeCell ref="M327:O327"/>
+    <mergeCell ref="M328:O328"/>
+    <mergeCell ref="M329:O329"/>
+    <mergeCell ref="M330:O330"/>
+    <mergeCell ref="M331:O331"/>
+    <mergeCell ref="M332:O332"/>
+    <mergeCell ref="M333:O333"/>
+    <mergeCell ref="M334:O334"/>
+    <mergeCell ref="M335:O335"/>
+    <mergeCell ref="M336:O336"/>
+    <mergeCell ref="M337:O337"/>
+    <mergeCell ref="M338:O338"/>
+    <mergeCell ref="M339:O339"/>
+    <mergeCell ref="M340:O340"/>
+    <mergeCell ref="M341:O341"/>
+    <mergeCell ref="M342:O342"/>
+    <mergeCell ref="M343:O343"/>
+    <mergeCell ref="M344:O344"/>
+    <mergeCell ref="M345:O345"/>
+    <mergeCell ref="M346:O346"/>
+    <mergeCell ref="M347:O347"/>
+    <mergeCell ref="M348:O348"/>
+    <mergeCell ref="M349:O349"/>
+    <mergeCell ref="M350:O350"/>
+    <mergeCell ref="M351:O351"/>
+    <mergeCell ref="M352:O352"/>
+    <mergeCell ref="M353:O353"/>
+    <mergeCell ref="M354:O354"/>
+    <mergeCell ref="M355:O355"/>
+    <mergeCell ref="M356:O356"/>
+    <mergeCell ref="M357:O357"/>
+    <mergeCell ref="M358:O358"/>
+    <mergeCell ref="M359:O359"/>
+    <mergeCell ref="M360:O360"/>
+    <mergeCell ref="M361:O361"/>
+    <mergeCell ref="M362:O362"/>
+    <mergeCell ref="M363:O363"/>
+    <mergeCell ref="M364:O364"/>
+    <mergeCell ref="M365:O365"/>
+    <mergeCell ref="M366:O366"/>
+    <mergeCell ref="M367:O367"/>
+    <mergeCell ref="M368:O368"/>
+    <mergeCell ref="M369:O369"/>
+    <mergeCell ref="M370:O370"/>
+    <mergeCell ref="M371:O371"/>
+    <mergeCell ref="M372:O372"/>
+    <mergeCell ref="M373:O373"/>
+    <mergeCell ref="M374:O374"/>
+    <mergeCell ref="M375:O375"/>
+    <mergeCell ref="M376:O376"/>
+    <mergeCell ref="M377:O377"/>
+    <mergeCell ref="M378:O378"/>
+    <mergeCell ref="M379:O379"/>
+    <mergeCell ref="M380:O380"/>
+    <mergeCell ref="M381:O381"/>
+    <mergeCell ref="M382:O382"/>
+    <mergeCell ref="M383:O383"/>
+    <mergeCell ref="M384:O384"/>
+    <mergeCell ref="M385:O385"/>
+    <mergeCell ref="M386:O386"/>
+    <mergeCell ref="M387:O387"/>
+    <mergeCell ref="M388:O388"/>
+    <mergeCell ref="M389:O389"/>
+    <mergeCell ref="M390:O390"/>
+    <mergeCell ref="M391:O391"/>
+    <mergeCell ref="M392:O392"/>
+    <mergeCell ref="M393:O393"/>
+    <mergeCell ref="M394:O394"/>
+    <mergeCell ref="M395:O395"/>
+    <mergeCell ref="M396:O396"/>
+    <mergeCell ref="M397:O397"/>
+    <mergeCell ref="M398:O398"/>
+    <mergeCell ref="M399:O399"/>
+    <mergeCell ref="M400:O400"/>
+    <mergeCell ref="M401:O401"/>
+    <mergeCell ref="M402:O402"/>
+    <mergeCell ref="M403:O403"/>
+    <mergeCell ref="M404:O404"/>
+    <mergeCell ref="M405:O405"/>
+    <mergeCell ref="M406:O406"/>
+    <mergeCell ref="M407:O407"/>
+    <mergeCell ref="M408:O408"/>
+    <mergeCell ref="M409:O409"/>
+    <mergeCell ref="M410:O410"/>
+    <mergeCell ref="M411:O411"/>
+    <mergeCell ref="M412:O412"/>
+    <mergeCell ref="M413:O413"/>
+    <mergeCell ref="M414:O414"/>
+    <mergeCell ref="M415:O415"/>
+    <mergeCell ref="M416:O416"/>
+    <mergeCell ref="M417:O417"/>
+    <mergeCell ref="M418:O418"/>
+    <mergeCell ref="M419:O419"/>
+    <mergeCell ref="M420:O420"/>
+    <mergeCell ref="M421:O421"/>
+    <mergeCell ref="M422:O422"/>
+    <mergeCell ref="M423:O423"/>
+    <mergeCell ref="M424:O424"/>
+    <mergeCell ref="M425:O425"/>
+    <mergeCell ref="M426:O426"/>
+    <mergeCell ref="M427:O427"/>
+    <mergeCell ref="M428:O428"/>
+    <mergeCell ref="M429:O429"/>
+    <mergeCell ref="M430:O430"/>
+    <mergeCell ref="M431:O431"/>
+    <mergeCell ref="M432:O432"/>
+    <mergeCell ref="M433:O433"/>
+    <mergeCell ref="M434:O434"/>
+    <mergeCell ref="M435:O435"/>
+    <mergeCell ref="M436:O436"/>
+    <mergeCell ref="M446:O446"/>
+    <mergeCell ref="M437:O437"/>
+    <mergeCell ref="M438:O438"/>
+    <mergeCell ref="M439:O439"/>
+    <mergeCell ref="M440:O440"/>
+    <mergeCell ref="M441:O441"/>
+    <mergeCell ref="M442:O442"/>
+    <mergeCell ref="M443:O443"/>
+    <mergeCell ref="M444:O444"/>
+    <mergeCell ref="M445:O445"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
